--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="24960" windowHeight="12840"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="601">
   <si>
     <t>date</t>
   </si>
@@ -56,15 +56,27 @@
     <t>links_json</t>
   </si>
   <si>
+    <t>Talk</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at Hebei University (HBU).</t>
+  </si>
+  <si>
+    <t>http://dm-dut.github.io/images/hbu.jpg</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at Nanjing University of Information Science and Technology (NUIST).</t>
+  </si>
+  <si>
+    <t>https://smse.nuist.edu.cn/info/1081/7426.htm</t>
+  </si>
+  <si>
     <t>Award</t>
   </si>
   <si>
     <t>I was awarded the Springer Nature Editor of Distinction Award 2026 — Author Service Award.</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>2026-04-18</t>
   </si>
   <si>
@@ -104,7 +116,7 @@
     <t>I was invited to join in the editorial board of Systems (SSCI, IF: 3.1) as an editorial board member.</t>
   </si>
   <si>
-    <t>https://www.mdpi.com/journal/systems</t>
+    <t>https://www.mdpi.com/journal/systems/editors?search=zhen+zhang</t>
   </si>
   <si>
     <t>["https://www.mdpi.com/journal/systems"]</t>
@@ -131,7 +143,7 @@
     <t>Call For Papers &amp; Abstracts for the Special Session: Artificial Intelligence for Optimization and Decision Making in FLINS-ISKE 2026, July 15-19, 2026, Sydney, Australia.</t>
   </si>
   <si>
-    <t>https://2026.flins.cc/</t>
+    <t>https://2026.flins.cc; https://mp.weixin.qq.com/s/GUZPlg6vh_RwemYuF6XweQ</t>
   </si>
   <si>
     <t>["https://2026.flins.cc/"]</t>
@@ -143,7 +155,7 @@
     <t>Call For Papers &amp; Abstracts for the Stream: Intelligent Group Decision Making and Consensus Process in GDN 2026, Katowice, Poland, June 28 – July 1, 2026.</t>
   </si>
   <si>
-    <t>https://gdnconference.org/</t>
+    <t>http://gdnconference.org/gdn2026/streams/?sessionid=-391327434; https://mp.weixin.qq.com/s/w84ZGOoEh2Ok39vvi-dpjQ</t>
   </si>
   <si>
     <t>["https://gdnconference.org/"]</t>
@@ -152,9 +164,6 @@
     <t>2025-12-15</t>
   </si>
   <si>
-    <t>Talk</t>
-  </si>
-  <si>
     <t>I was invited to deliver a talk entitled "An Incremental Preference Elicitation-Based Approach to Learning Potentially Non-Monotonic Preferences in Multi-Criteria Sorting" at South China Normal University.</t>
   </si>
   <si>
@@ -194,633 +203,633 @@
     <t>https://shxy.wh.sdu.edu.cn/info/1006/26883.htm</t>
   </si>
   <si>
+    <t>["https://shxy.wh.sdu.edu.cn/info/1006/26883.htm"]</t>
+  </si>
+  <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at University of Shanghai for Science and Technology (USST).</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2025-12-06</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Incremental Preference Elicitation-Based Approach to Learning Potentially Non-Monotonic Preferences in Multi-Criteria Sorting" at the 2nd Symposium on Digital Decision-Making, hosted by Shanghai University.</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/R4Ugr5Srivu8rRrIzh5fug</t>
+  </si>
+  <si>
+    <t>["https://mp.weixin.qq.com/s/R4Ugr5Srivu8rRrIzh5fug"]</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>Our paper titled "Integrating machine learning models to learn potentially non-monotonic preferences for multi-criteria sorting from large-scale assignment examples" has been selected as one of the recipients of the 2025 Best Paper Award.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.omega.2024.103219</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.omega.2024.103219", "https://mp.weixin.qq.com/s/Liq8EAxapEYQYNvHwTHHiA"]</t>
+  </si>
+  <si>
+    <t>2025-11-13</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Congratulations to Zhuolin Li on successfully completing her Ph.D. thesis defense.</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/GyFnl6HYnp43uVc8vZzroA</t>
+  </si>
+  <si>
+    <t>["https://mp.weixin.qq.com/s/GyFnl6HYnp43uVc8vZzroA"]</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at Zhejiang Gongshang University.</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/Hh7PnDXhOo5fzGd_rze09g</t>
+  </si>
+  <si>
+    <t>["https://mp.weixin.qq.com/s/Hh7PnDXhOo5fzGd_rze09g"]</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Non-Monotonic Preference Learning for Multi-Criteria Sorting" at the Second Forum on Intelligent Management, hosted by Shanghai University of Finance and Economics Zhejiang College.</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/18rIJnSriWPEOhUmGIad4g</t>
+  </si>
+  <si>
+    <t>["https://mp.weixin.qq.com/s/18rIJnSriWPEOhUmGIad4g"]</t>
+  </si>
+  <si>
+    <t>2025-11-07</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at Shanghai Maritime University.</t>
+  </si>
+  <si>
+    <t>https://sem.shmtu.edu.cn/2025/1030/c7485a281201/page.htm</t>
+  </si>
+  <si>
+    <t>["https://sem.shmtu.edu.cn/2025/1030/c7485a281201/page.htm"]</t>
+  </si>
+  <si>
+    <t>2025-11-01</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at the Forum on Game Theory and Intelligent Decision Making, hosted by Northwestern Polytechnical University.</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/Vt4Wy0A7quXG9JPOOVX1dQ</t>
+  </si>
+  <si>
+    <t>["https://mp.weixin.qq.com/s/Vt4Wy0A7quXG9JPOOVX1dQ"]</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at Xidian University.</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at Xi'an University of Technology.</t>
+  </si>
+  <si>
+    <t>https://sba.xaut.edu.cn/info/1142/7123.htm</t>
+  </si>
+  <si>
+    <t>["https://sba.xaut.edu.cn/info/1142/7123.htm"]</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by Annals of Operations Research (SCI, IF: 4.5).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10479-025-06832-0</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1007/s10479-025-06832-0"]</t>
+  </si>
+  <si>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at the 27th Chinese Conference on Management Sciences, Harbin.</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by IEEE Transactions on Systems, Man, and Cybernetics: Systems (SCI, IF: 8.7).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TSMC.2025.3597963</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1109/TSMC.2025.3597963"]</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by Chinese Journal of Management Science (FMS T1).</t>
+  </si>
+  <si>
+    <t>https://link.cnki.net/doi/10.16381/j.cnki.issn1003-207x.2024.1896</t>
+  </si>
+  <si>
+    <t>["https://link.cnki.net/doi/10.16381/j.cnki.issn1003-207x.2024.1896"]</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
+    <t>I will serve as an editor for the newly launched book series by Springer Nature, entitled "Artificial Intelligence and Decision Making."</t>
+  </si>
+  <si>
+    <t>2025-06-17</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by Information Fusion (SCI, IF: 14.8).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.inffus.2025.103443</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.inffus.2025.103443"]</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>I was awarded the Springer Nature Editor of Distinction Award 2025 — Author Service Award.</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/jxDvUlkNr-VsZ7J5sA4k5g</t>
+  </si>
+  <si>
+    <t>["https://mp.weixin.qq.com/s/jxDvUlkNr-VsZ7J5sA4k5g"]</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Incremental Preference Elicitation-Based Approach to Learning Potentially Non-Monotonic Preferences in Multi-Criteria Sorting" at the Sixth Annual Conference of Intelligent Decision Making and Game Branch, CSOOPEM, Hefei.</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Modeling Personalized Individual Semantics in Multi-Criteria Decision Making" at Nanjing University of Information Science and Technology.</t>
+  </si>
+  <si>
+    <t>https://smse.nuist.edu.cn/info/1081/6992.htm</t>
+  </si>
+  <si>
+    <t>["https://smse.nuist.edu.cn/info/1081/6992.htm"]</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by Information Sciences (SCI, IF: 8.1).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ins.2025.122222</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.ins.2025.122222"]</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.inffus.2025.103107</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.inffus.2025.103107"]</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by IEEE Transactions on Cybernetics (SCI, IF: 9.4, ABS 3).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TCYB.2025.3534195</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1109/TCYB.2025.3534195"]</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.inffus.2024.102926</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.inffus.2024.102926"]</t>
+  </si>
+  <si>
+    <t>2024-11-28</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by European Journal of Operational Research (SCI, IF: 6.0, ABS 4).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ejor.2024.11.047</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.ejor.2024.11.047"]</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by Computers &amp; Operations Research (SCI, IF: 4.1).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.cor.2024.106917</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.cor.2024.106917"]</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by Omega: The International Journal of Management Science (SCI, IF: 6.7).</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.omega.2024.103219"]</t>
+  </si>
+  <si>
+    <t>2024-09-30</t>
+  </si>
+  <si>
+    <t>A new paper was accepted by IEEE Transactions on Systems, Man, and Cybernetics: Systems (SCI, IF: 8.6).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TSMC.2024.3472699</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1109/TSMC.2024.3472699"]</t>
+  </si>
+  <si>
+    <t>2024-09-24</t>
+  </si>
+  <si>
+    <t>I will be a guest editor for the special issue "AI-supported Decision Making and Recommender Systems" on Applied Sciences Journal (SCI, IF: 2.5).</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/applsci/special_issues/9FBJS45XR9</t>
+  </si>
+  <si>
+    <t>["https://www.mdpi.com/journal/applsci/special_issues/9FBJS45XR9"]</t>
+  </si>
+  <si>
+    <t>2024-09-01</t>
+  </si>
+  <si>
+    <t>Grant</t>
+  </si>
+  <si>
+    <t>A new project was granted by the Natural Science Foundation of Liaoning Province.</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>I was invited to join in the editorial board of International Journal of Computational Intelligence Systems (SCI, IF: 2.5) as an Area Editor.</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/journal/44196/editors</t>
+  </si>
+  <si>
+    <t>["https://link.springer.com/journal/44196/editors"]</t>
+  </si>
+  <si>
+    <t>2024-04-29</t>
+  </si>
+  <si>
+    <t>A monograph entitled "Modeling Complex Linguistic Information to Support Group Decision Making Under Uncertainty" will be published by Springer Nature.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/978-981-97-3584-6</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1007/978-981-97-3584-6"]</t>
+  </si>
+  <si>
+    <t>2024-04-23</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Engineering Applications of Artificial Intelligence (2022 IF: 8).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.engappai.2024.108509</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.engappai.2024.108509"]</t>
+  </si>
+  <si>
+    <t>2024-03-08</t>
+  </si>
+  <si>
+    <t>A paper was accepted by IEEE Transactions on Fuzzy Systems (2022 IF: 11.9).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TFUZZ.2024.3375863</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1109/TFUZZ.2024.3375863"]</t>
+  </si>
+  <si>
+    <t>2024-01-24</t>
+  </si>
+  <si>
+    <t>I joined in the editorial review board of IEEE Transactions on Engineering Management (ABS 3, FMS-A, SCI/SSCI, IF: 5.8).</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/stamp/stamp.jsp?arnumber=10356850&amp;tp=</t>
+  </si>
+  <si>
+    <t>["https://ieeexplore.ieee.org/stamp/stamp.jsp?arnumber=10356850&amp;tp="]</t>
+  </si>
+  <si>
+    <t>2023-12-19</t>
+  </si>
+  <si>
+    <t>I was selected as an outstanding reviewer of Journal of the Operational Research Society for the second time.</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tjor20</t>
+  </si>
+  <si>
+    <t>["https://www.tandfonline.com/journals/tjor20"]</t>
+  </si>
+  <si>
+    <t>2023-11-16</t>
+  </si>
+  <si>
+    <t>I was invited to join in the editorial board of Group Decision &amp; Negotiation as an Associate Editor from 1 January 2024.</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/journal/10726/editorial-board</t>
+  </si>
+  <si>
+    <t>["https://link.springer.com/journal/10726/editorial-board"]</t>
+  </si>
+  <si>
+    <t>2023-10-11</t>
+  </si>
+  <si>
+    <t>I was elevated to be a senior member of IEEE.</t>
+  </si>
+  <si>
+    <t>2023-08-24</t>
+  </si>
+  <si>
+    <t>A new research project was granted by the National Natural Science Foundation of China (NSFC).</t>
+  </si>
+  <si>
+    <t>2023-07-10</t>
+  </si>
+  <si>
+    <t>I was invited to join in the editorial board of Information Fusion Journal (2022 IF: 18.6).</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/information-fusion/about/editorial-board</t>
+  </si>
+  <si>
+    <t>["https://www.sciencedirect.com/journal/information-fusion/about/editorial-board"]</t>
+  </si>
+  <si>
+    <t>2023-04-26</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Information Fusion (2022 IF: 18.6).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.inffus.2023.101825</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1016/j.inffus.2023.101825"]</t>
+  </si>
+  <si>
+    <t>2023-02-26</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Journal of the Operational Research Society (2022 IF: 3.6).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/01605682.2023.2186806</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1080/01605682.2023.2186806"]</t>
+  </si>
+  <si>
+    <t>2023-02-24</t>
+  </si>
+  <si>
+    <t>A paper was accepted by IEEE Transactions on Computational Social Systems (2022 IF: 5).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TCSS.2023.3251351</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1109/TCSS.2023.3251351"]</t>
+  </si>
+  <si>
+    <t>2023-01-29</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Systems Journal (2022 IF: 1.9).</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2079-8954/11/2/69</t>
+  </si>
+  <si>
+    <t>["https://www.mdpi.com/2079-8954/11/2/69"]</t>
+  </si>
+  <si>
+    <t>2023-01-23</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Applied Intelligence (2022 IF: 5.3).</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10489-023-04485-9</t>
+  </si>
+  <si>
+    <t>["https://doi.org/10.1007/s10489-023-04485-9"]</t>
+  </si>
+  <si>
+    <t>2022-12-20</t>
+  </si>
+  <si>
+    <t>I was selected as an outstanding reviewer for Journal of the Operational Research Society.</t>
+  </si>
+  <si>
+    <t>2022-11-28</t>
+  </si>
+  <si>
+    <t>I will organize a special issue entitled "Preference and Consensus Modeling in Group Decision Making under Complex Contexts" in Systems with Prof. Jian Wu, Prof. Hengjie Zhang and Dr. Wenyu Yu.</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/journal/systems/special_issues/ZN51HVWR9N</t>
+  </si>
+  <si>
+    <t>["https://www.mdpi.com/journal/systems/special_issues/ZN51HVWR9N"]</t>
+  </si>
+  <si>
+    <t>2022-11-11</t>
+  </si>
+  <si>
+    <t>I will organize a special issue entitled "New Trends in Intelligent Group Decision Making and Consensus Modelling (IGDM-CM)" in Group Decision and Negotiation with Prof. Francisco Chiclana, Prof. Yucheng Dong, Prof. Enrique Herrera-Viedma and Dr. Congcong Li.</t>
+  </si>
+  <si>
+    <t>2022-10-28</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Managing personalized individual semantics and non-cooperative behaviors in social network group decision making" at the First Symposium on Complex Management Systems hosted by Tianjin University.</t>
+  </si>
+  <si>
+    <t>2022-09-06</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Annals of Operations Research (SCI, 2022 IF: 4.8).</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/10.1007/s10479-022-04985-w</t>
+  </si>
+  <si>
+    <t>["https://link.springer.com/10.1007/s10479-022-04985-w"]</t>
+  </si>
+  <si>
+    <t>2022-08-24</t>
+  </si>
+  <si>
+    <t>A paper was accepted by Group Decision and Negotiation (SSCI, 2022 IF: 3.0).</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/10.1007/s10726-022-09798-7</t>
+  </si>
+  <si>
+    <t>["https://link.springer.com/10.1007/s10726-022-09798-7"]</t>
+  </si>
+  <si>
+    <t>2022-04-21</t>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "Modeling consensus in linguistic group decision making: A personalized individual semantics-based perspective" at Anhui University.</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t>Springer Nature Editor of Distinction Award — Author Service Award</t>
+  </si>
+  <si>
+    <t>Springer Nature</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2025 Best Paper Award of Omega Journal</t>
+  </si>
+  <si>
+    <t>Omega Journal</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Xingliao Talent Program - Young Talents for Cultural Luminaries and the “Four Batches” Program</t>
+  </si>
+  <si>
+    <t>Outstanding Reviewer</t>
+  </si>
+  <si>
+    <t>Journal of Systems Science &amp; Complexity</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Senior Member</t>
+  </si>
+  <si>
+    <t>IEEE</t>
+  </si>
+  <si>
+    <t>2022-2024</t>
+  </si>
+  <si>
+    <t>Journal of the Operational Research Society</t>
+  </si>
+  <si>
+    <t>2020-2025</t>
+  </si>
+  <si>
+    <t>World’s Top 2% Scientists</t>
+  </si>
+  <si>
+    <t>Stanford University</t>
+  </si>
+  <si>
+    <t>2021-2023</t>
+  </si>
+  <si>
+    <t>Journal of Industrial Engineering and Engineering Management</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Xinghai Outstanding Young Talents</t>
+  </si>
+  <si>
+    <t>Dalian University of Technology</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>Publons Global Peer Review Awards, top 1% of reviewers in Computer Science and Cross-Field</t>
+  </si>
+  <si>
+    <t>Clarivate Analytics / Publons</t>
+  </si>
+  <si>
+    <t>Systems Engineering — Theory &amp; Practice</t>
+  </si>
+  <si>
     <t>no</t>
   </si>
   <si>
-    <t>["https://shxy.wh.sdu.edu.cn/info/1006/26883.htm"]</t>
-  </si>
-  <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at University of Shanghai for Science and Technology (USST).</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "An Incremental Preference Elicitation-Based Approach to Learning Potentially Non-Monotonic Preferences in Multi-Criteria Sorting" at the 2nd Symposium on Digital Decision-Making, hosted by Shanghai University.</t>
-  </si>
-  <si>
-    <t>https://mp.weixin.qq.com/s/R4Ugr5Srivu8rRrIzh5fug</t>
-  </si>
-  <si>
-    <t>["https://mp.weixin.qq.com/s/R4Ugr5Srivu8rRrIzh5fug"]</t>
-  </si>
-  <si>
-    <t>2025-11-21</t>
-  </si>
-  <si>
-    <t>Our paper titled "Integrating machine learning models to learn potentially non-monotonic preferences for multi-criteria sorting from large-scale assignment examples" has been selected as one of the recipients of the 2025 Best Paper Award.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.omega.2024.103219</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.omega.2024.103219", "https://mp.weixin.qq.com/s/Liq8EAxapEYQYNvHwTHHiA"]</t>
-  </si>
-  <si>
-    <t>2025-11-13</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Congratulations to Zhuolin Li on successfully completing her Ph.D. thesis defense.</t>
-  </si>
-  <si>
-    <t>https://mp.weixin.qq.com/s/GyFnl6HYnp43uVc8vZzroA</t>
-  </si>
-  <si>
-    <t>["https://mp.weixin.qq.com/s/GyFnl6HYnp43uVc8vZzroA"]</t>
-  </si>
-  <si>
-    <t>2025-11-10</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at Zhejiang Gongshang University.</t>
-  </si>
-  <si>
-    <t>https://mp.weixin.qq.com/s/Hh7PnDXhOo5fzGd_rze09g</t>
-  </si>
-  <si>
-    <t>["https://mp.weixin.qq.com/s/Hh7PnDXhOo5fzGd_rze09g"]</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Non-Monotonic Preference Learning for Multi-Criteria Sorting" at the Second Forum on Intelligent Management, hosted by Shanghai University of Finance and Economics Zhejiang College.</t>
-  </si>
-  <si>
-    <t>https://mp.weixin.qq.com/s/18rIJnSriWPEOhUmGIad4g</t>
-  </si>
-  <si>
-    <t>["https://mp.weixin.qq.com/s/18rIJnSriWPEOhUmGIad4g"]</t>
-  </si>
-  <si>
-    <t>2025-11-07</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at Shanghai Maritime University.</t>
-  </si>
-  <si>
-    <t>https://sem.shmtu.edu.cn/2025/1030/c7485a281201/page.htm</t>
-  </si>
-  <si>
-    <t>["https://sem.shmtu.edu.cn/2025/1030/c7485a281201/page.htm"]</t>
-  </si>
-  <si>
-    <t>2025-11-01</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at the Forum on Game Theory and Intelligent Decision Making, hosted by Northwestern Polytechnical University.</t>
-  </si>
-  <si>
-    <t>https://mp.weixin.qq.com/s/Vt4Wy0A7quXG9JPOOVX1dQ</t>
-  </si>
-  <si>
-    <t>["https://mp.weixin.qq.com/s/Vt4Wy0A7quXG9JPOOVX1dQ"]</t>
-  </si>
-  <si>
-    <t>2025-10-31</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at Xidian University.</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at Xi'an University of Technology.</t>
-  </si>
-  <si>
-    <t>https://sba.xaut.edu.cn/info/1142/7123.htm</t>
-  </si>
-  <si>
-    <t>["https://sba.xaut.edu.cn/info/1142/7123.htm"]</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by Annals of Operations Research (SCI, IF: 4.5).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10479-025-06832-0</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1007/s10479-025-06832-0"]</t>
-  </si>
-  <si>
-    <t>2025-08-17</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Data-Driven Preference Learning for Multi-Criteria Sorting Considering Criteria Interactions" at the 27th Chinese Conference on Management Sciences, Harbin.</t>
-  </si>
-  <si>
-    <t>2025-08-10</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by IEEE Transactions on Systems, Man, and Cybernetics: Systems (SCI, IF: 8.7).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/TSMC.2025.3597963</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1109/TSMC.2025.3597963"]</t>
-  </si>
-  <si>
-    <t>2025-08-01</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by Chinese Journal of Management Science (FMS T1).</t>
-  </si>
-  <si>
-    <t>https://link.cnki.net/doi/10.16381/j.cnki.issn1003-207x.2024.1896</t>
-  </si>
-  <si>
-    <t>["https://link.cnki.net/doi/10.16381/j.cnki.issn1003-207x.2024.1896"]</t>
-  </si>
-  <si>
-    <t>2025-07-08</t>
-  </si>
-  <si>
-    <t>I will serve as an editor for the newly launched book series by Springer Nature, entitled "Artificial Intelligence and Decision Making."</t>
-  </si>
-  <si>
-    <t>2025-06-17</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by Information Fusion (SCI, IF: 14.8).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.inffus.2025.103443</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.inffus.2025.103443"]</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>I was awarded the Springer Nature Editor of Distinction Award 2025 — Author Service Award.</t>
-  </si>
-  <si>
-    <t>https://mp.weixin.qq.com/s/jxDvUlkNr-VsZ7J5sA4k5g</t>
-  </si>
-  <si>
-    <t>["https://mp.weixin.qq.com/s/jxDvUlkNr-VsZ7J5sA4k5g"]</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "An Incremental Preference Elicitation-Based Approach to Learning Potentially Non-Monotonic Preferences in Multi-Criteria Sorting" at the Sixth Annual Conference of Intelligent Decision Making and Game Branch, CSOOPEM, Hefei.</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Modeling Personalized Individual Semantics in Multi-Criteria Decision Making" at Nanjing University of Information Science and Technology.</t>
-  </si>
-  <si>
-    <t>https://smse.nuist.edu.cn/info/1081/6992.htm</t>
-  </si>
-  <si>
-    <t>["https://smse.nuist.edu.cn/info/1081/6992.htm"]</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by Information Sciences (SCI, IF: 8.1).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.ins.2025.122222</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.ins.2025.122222"]</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.inffus.2025.103107</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.inffus.2025.103107"]</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by IEEE Transactions on Cybernetics (SCI, IF: 9.4, ABS 3).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/TCYB.2025.3534195</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1109/TCYB.2025.3534195"]</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.inffus.2024.102926</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.inffus.2024.102926"]</t>
-  </si>
-  <si>
-    <t>2024-11-28</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by European Journal of Operational Research (SCI, IF: 6.0, ABS 4).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.ejor.2024.11.047</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.ejor.2024.11.047"]</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by Computers &amp; Operations Research (SCI, IF: 4.1).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.cor.2024.106917</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.cor.2024.106917"]</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by Omega: The International Journal of Management Science (SCI, IF: 6.7).</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.omega.2024.103219"]</t>
-  </si>
-  <si>
-    <t>2024-09-30</t>
-  </si>
-  <si>
-    <t>A new paper was accepted by IEEE Transactions on Systems, Man, and Cybernetics: Systems (SCI, IF: 8.6).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/TSMC.2024.3472699</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1109/TSMC.2024.3472699"]</t>
-  </si>
-  <si>
-    <t>2024-09-24</t>
-  </si>
-  <si>
-    <t>I will be a guest editor for the special issue "AI-supported Decision Making and Recommender Systems" on Applied Sciences Journal (SCI, IF: 2.5).</t>
-  </si>
-  <si>
-    <t>https://www.mdpi.com/journal/applsci/special_issues/9FBJS45XR9</t>
-  </si>
-  <si>
-    <t>["https://www.mdpi.com/journal/applsci/special_issues/9FBJS45XR9"]</t>
-  </si>
-  <si>
-    <t>2024-09-01</t>
-  </si>
-  <si>
-    <t>Grant</t>
-  </si>
-  <si>
-    <t>A new project was granted by the Natural Science Foundation of Liaoning Province.</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>I was invited to join in the editorial board of International Journal of Computational Intelligence Systems (SCI, IF: 2.5) as an Area Editor.</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/journal/44196/editors</t>
-  </si>
-  <si>
-    <t>["https://link.springer.com/journal/44196/editors"]</t>
-  </si>
-  <si>
-    <t>2024-04-29</t>
-  </si>
-  <si>
-    <t>A monograph entitled "Modeling Complex Linguistic Information to Support Group Decision Making Under Uncertainty" will be published by Springer Nature.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/978-981-97-3584-6</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1007/978-981-97-3584-6"]</t>
-  </si>
-  <si>
-    <t>2024-04-23</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Engineering Applications of Artificial Intelligence (2022 IF: 8).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.engappai.2024.108509</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.engappai.2024.108509"]</t>
-  </si>
-  <si>
-    <t>2024-03-08</t>
-  </si>
-  <si>
-    <t>A paper was accepted by IEEE Transactions on Fuzzy Systems (2022 IF: 11.9).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/TFUZZ.2024.3375863</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1109/TFUZZ.2024.3375863"]</t>
-  </si>
-  <si>
-    <t>2024-01-24</t>
-  </si>
-  <si>
-    <t>I joined in the editorial review board of IEEE Transactions on Engineering Management (ABS 3, FMS-A, SCI/SSCI, IF: 5.8).</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/stamp/stamp.jsp?arnumber=10356850&amp;tp=</t>
-  </si>
-  <si>
-    <t>["https://ieeexplore.ieee.org/stamp/stamp.jsp?arnumber=10356850&amp;tp="]</t>
-  </si>
-  <si>
-    <t>2023-12-19</t>
-  </si>
-  <si>
-    <t>I was selected as an outstanding reviewer of Journal of the Operational Research Society for the second time.</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/journals/tjor20</t>
-  </si>
-  <si>
-    <t>["https://www.tandfonline.com/journals/tjor20"]</t>
-  </si>
-  <si>
-    <t>2023-11-16</t>
-  </si>
-  <si>
-    <t>I was invited to join in the editorial board of Group Decision &amp; Negotiation as an Associate Editor from 1 January 2024.</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/journal/10726/editorial-board</t>
-  </si>
-  <si>
-    <t>["https://link.springer.com/journal/10726/editorial-board"]</t>
-  </si>
-  <si>
-    <t>2023-10-11</t>
-  </si>
-  <si>
-    <t>I was elevated to be a senior member of IEEE.</t>
-  </si>
-  <si>
-    <t>2023-08-24</t>
-  </si>
-  <si>
-    <t>A new research project was granted by the National Natural Science Foundation of China (NSFC).</t>
-  </si>
-  <si>
-    <t>2023-07-10</t>
-  </si>
-  <si>
-    <t>I was invited to join in the editorial board of Information Fusion Journal (2022 IF: 18.6).</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/journal/information-fusion/about/editorial-board</t>
-  </si>
-  <si>
-    <t>["https://www.sciencedirect.com/journal/information-fusion/about/editorial-board"]</t>
-  </si>
-  <si>
-    <t>2023-04-26</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Information Fusion (2022 IF: 18.6).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.inffus.2023.101825</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1016/j.inffus.2023.101825"]</t>
-  </si>
-  <si>
-    <t>2023-02-26</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Journal of the Operational Research Society (2022 IF: 3.6).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1080/01605682.2023.2186806</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1080/01605682.2023.2186806"]</t>
-  </si>
-  <si>
-    <t>2023-02-24</t>
-  </si>
-  <si>
-    <t>A paper was accepted by IEEE Transactions on Computational Social Systems (2022 IF: 5).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/TCSS.2023.3251351</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1109/TCSS.2023.3251351"]</t>
-  </si>
-  <si>
-    <t>2023-01-29</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Systems Journal (2022 IF: 1.9).</t>
-  </si>
-  <si>
-    <t>https://www.mdpi.com/2079-8954/11/2/69</t>
-  </si>
-  <si>
-    <t>["https://www.mdpi.com/2079-8954/11/2/69"]</t>
-  </si>
-  <si>
-    <t>2023-01-23</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Applied Intelligence (2022 IF: 5.3).</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10489-023-04485-9</t>
-  </si>
-  <si>
-    <t>["https://doi.org/10.1007/s10489-023-04485-9"]</t>
-  </si>
-  <si>
-    <t>2022-12-20</t>
-  </si>
-  <si>
-    <t>I was selected as an outstanding reviewer for Journal of the Operational Research Society.</t>
-  </si>
-  <si>
-    <t>2022-11-28</t>
-  </si>
-  <si>
-    <t>I will organize a special issue entitled "Preference and Consensus Modeling in Group Decision Making under Complex Contexts" in Systems with Prof. Jian Wu, Prof. Hengjie Zhang and Dr. Wenyu Yu.</t>
-  </si>
-  <si>
-    <t>https://www.mdpi.com/journal/systems/special_issues/ZN51HVWR9N</t>
-  </si>
-  <si>
-    <t>["https://www.mdpi.com/journal/systems/special_issues/ZN51HVWR9N"]</t>
-  </si>
-  <si>
-    <t>2022-11-11</t>
-  </si>
-  <si>
-    <t>I will organize a special issue entitled "New Trends in Intelligent Group Decision Making and Consensus Modelling (IGDM-CM)" in Group Decision and Negotiation with Prof. Francisco Chiclana, Prof. Yucheng Dong, Prof. Enrique Herrera-Viedma and Dr. Congcong Li.</t>
-  </si>
-  <si>
-    <t>2022-10-28</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Managing personalized individual semantics and non-cooperative behaviors in social network group decision making" at the First Symposium on Complex Management Systems hosted by Tianjin University.</t>
-  </si>
-  <si>
-    <t>2022-09-06</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Annals of Operations Research (SCI, 2022 IF: 4.8).</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/10.1007/s10479-022-04985-w</t>
-  </si>
-  <si>
-    <t>["https://link.springer.com/10.1007/s10479-022-04985-w"]</t>
-  </si>
-  <si>
-    <t>2022-08-24</t>
-  </si>
-  <si>
-    <t>A paper was accepted by Group Decision and Negotiation (SSCI, 2022 IF: 3.0).</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/10.1007/s10726-022-09798-7</t>
-  </si>
-  <si>
-    <t>["https://link.springer.com/10.1007/s10726-022-09798-7"]</t>
-  </si>
-  <si>
-    <t>2022-04-21</t>
-  </si>
-  <si>
-    <t>I was invited to deliver a talk entitled "Modeling consensus in linguistic group decision making: A personalized individual semantics-based perspective" at Anhui University.</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>organization</t>
-  </si>
-  <si>
-    <t>Springer Nature Editor of Distinction Award — Author Service Award</t>
-  </si>
-  <si>
-    <t>Springer Nature</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2025 Best Paper Award of Omega Journal</t>
-  </si>
-  <si>
-    <t>Omega Journal</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Xingliao Talent Program - Young Talents for Cultural Luminaries and the “Four Batches” Program</t>
-  </si>
-  <si>
-    <t>Outstanding Reviewer</t>
-  </si>
-  <si>
-    <t>Journal of Systems Science &amp; Complexity</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>Senior Member</t>
-  </si>
-  <si>
-    <t>IEEE</t>
-  </si>
-  <si>
-    <t>2022-2024</t>
-  </si>
-  <si>
-    <t>Journal of the Operational Research Society</t>
-  </si>
-  <si>
-    <t>2020-2025</t>
-  </si>
-  <si>
-    <t>World’s Top 2% Scientists</t>
-  </si>
-  <si>
-    <t>Stanford University</t>
-  </si>
-  <si>
-    <t>2021-2023</t>
-  </si>
-  <si>
-    <t>Journal of Industrial Engineering and Engineering Management</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>Xinghai Outstanding Young Talents</t>
-  </si>
-  <si>
-    <t>Dalian University of Technology</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>Publons Global Peer Review Awards, top 1% of reviewers in Computer Science and Cross-Field</t>
-  </si>
-  <si>
-    <t>Clarivate Analytics / Publons</t>
-  </si>
-  <si>
-    <t>Systems Engineering — Theory &amp; Practice</t>
-  </si>
-  <si>
     <t>role</t>
   </si>
   <si>
@@ -1682,7 +1691,7 @@
     <t>A/Prof., School of Data Science and Artificial Intelligence, DUFE</t>
   </si>
   <si>
-    <t>https://scholar.google.com/</t>
+    <t>https://scholar.google.com/citations?user=O1SESW8AAAAJ</t>
   </si>
   <si>
     <t>PhD Students</t>
@@ -2312,7 +2321,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2461,8 +2470,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2472,14 +2481,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2534,7 +2556,33 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="41">
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2728,25 +2776,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="30"/>
+      <tableStyleElement type="headerRow" dxfId="29"/>
+      <tableStyleElement type="totalRow" dxfId="28"/>
+      <tableStyleElement type="firstColumn" dxfId="27"/>
+      <tableStyleElement type="lastColumn" dxfId="26"/>
+      <tableStyleElement type="firstRowStripe" dxfId="25"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="24"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="totalRow" dxfId="39"/>
+      <tableStyleElement type="firstRowStripe" dxfId="38"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="37"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="36"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="35"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="34"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="33"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="32"/>
+      <tableStyleElement type="pageFieldValues" dxfId="31"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2758,13 +2806,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsTable" displayName="NewsTable" ref="A1:E63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsTable" displayName="NewsTable" ref="A1:E65">
   <tableColumns count="5">
-    <tableColumn id="1" name="date"/>
-    <tableColumn id="2" name="category"/>
-    <tableColumn id="3" name="content"/>
-    <tableColumn id="4" name="link"/>
-    <tableColumn id="5" name="show_on_home"/>
+    <tableColumn id="1" name="date" dataDxfId="0"/>
+    <tableColumn id="2" name="category" dataDxfId="1"/>
+    <tableColumn id="3" name="content" dataDxfId="2"/>
+    <tableColumn id="4" name="link" dataDxfId="3"/>
+    <tableColumn id="5" name="show_on_home" dataDxfId="4">
+      <calculatedColumnFormula>IF(ROW()-1&lt;11,"yes","no")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2773,9 +2823,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AwardsTable" displayName="AwardsTable" ref="A1:C13">
   <tableColumns count="3">
-    <tableColumn id="1" name="year"/>
-    <tableColumn id="2" name="title"/>
-    <tableColumn id="3" name="organization"/>
+    <tableColumn id="1" name="year" dataDxfId="5"/>
+    <tableColumn id="2" name="title" dataDxfId="6"/>
+    <tableColumn id="3" name="organization" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2784,13 +2834,13 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="GrantsTable" displayName="GrantsTable" ref="A1:G23">
   <tableColumns count="7">
-    <tableColumn id="1" name="no"/>
-    <tableColumn id="2" name="role"/>
-    <tableColumn id="3" name="title"/>
-    <tableColumn id="4" name="funder"/>
-    <tableColumn id="5" name="grant_no"/>
-    <tableColumn id="6" name="amount"/>
-    <tableColumn id="7" name="period"/>
+    <tableColumn id="1" name="no" dataDxfId="8"/>
+    <tableColumn id="2" name="role" dataDxfId="9"/>
+    <tableColumn id="3" name="title" dataDxfId="10"/>
+    <tableColumn id="4" name="funder" dataDxfId="11"/>
+    <tableColumn id="5" name="grant_no" dataDxfId="12"/>
+    <tableColumn id="6" name="amount" dataDxfId="13"/>
+    <tableColumn id="7" name="period" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2799,11 +2849,11 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ServicesTable" displayName="ServicesTable" ref="A1:E125">
   <tableColumns count="5">
-    <tableColumn id="1" name="category"/>
-    <tableColumn id="2" name="role"/>
-    <tableColumn id="3" name="organization"/>
-    <tableColumn id="4" name="item"/>
-    <tableColumn id="5" name="period"/>
+    <tableColumn id="1" name="category" dataDxfId="15"/>
+    <tableColumn id="2" name="role" dataDxfId="16"/>
+    <tableColumn id="3" name="organization" dataDxfId="17"/>
+    <tableColumn id="4" name="item" dataDxfId="18"/>
+    <tableColumn id="5" name="period" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2812,10 +2862,10 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="GroupTable" displayName="GroupTable" ref="A1:D26">
   <tableColumns count="4">
-    <tableColumn id="1" name="category"/>
-    <tableColumn id="2" name="name"/>
-    <tableColumn id="3" name="note"/>
-    <tableColumn id="4" name="link"/>
+    <tableColumn id="1" name="category" dataDxfId="20"/>
+    <tableColumn id="2" name="name" dataDxfId="21"/>
+    <tableColumn id="3" name="note" dataDxfId="22"/>
+    <tableColumn id="4" name="link" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2970,12 +3020,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2991,7 +3042,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3001,9 +3052,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="27.6" spans="1:7">
-      <c r="A2" s="6">
-        <v>46168</v>
+    <row r="2" ht="41" customHeight="1" spans="1:7">
+      <c r="A2" s="9">
+        <v>46184</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -3011,1412 +3062,1510 @@
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" ht="69" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="10" t="str">
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="3" ht="41" customHeight="1" spans="1:7">
+      <c r="A3" s="9">
+        <v>46177</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="10" t="str">
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:7">
+      <c r="A4" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="10" t="str">
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="5" ht="70" spans="1:7">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" ht="69" spans="1:7">
-      <c r="A4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E5" s="10" t="str">
+        <f t="shared" ref="E5:E14" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="27.6" spans="1:7">
-      <c r="A5" s="2" t="s">
+    <row r="6" ht="70" spans="1:7">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yes</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="7" ht="42" spans="1:7">
+      <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" ht="55.2" spans="1:7">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="E7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yes</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" ht="55.2" spans="1:7">
-      <c r="A7" s="2" t="s">
+    <row r="8" ht="56" spans="1:7">
+      <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yes</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
+    </row>
+    <row r="9" ht="56" spans="1:7">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" ht="55.2" spans="1:7">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="E9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yes</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" ht="69" spans="1:7">
-      <c r="A9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" ht="55.2" spans="1:7">
+    <row r="10" ht="98" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yes</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="70" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="E11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yes</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" ht="55.2" spans="1:7">
-      <c r="A11" s="2" t="s">
+    <row r="12" ht="56" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>no</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
+    </row>
+    <row r="13" ht="56" spans="1:7">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" ht="69" spans="1:7">
-      <c r="A12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>no</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="2" t="s">
+    </row>
+    <row r="14" ht="70" spans="1:7">
+      <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" ht="69" spans="1:7">
-      <c r="A13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>no</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="2" t="s">
+    </row>
+    <row r="15" ht="70" spans="1:7">
+      <c r="A15" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" ht="82.8" spans="1:7">
-      <c r="A14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" ht="69" spans="1:7">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="10" t="str">
+        <f t="shared" ref="E15:E24" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>no</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="84" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="2" t="s">
+    </row>
+    <row r="17" ht="70" spans="1:7">
+      <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="16" ht="41.4" spans="1:7">
-      <c r="A16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="E17" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="18" ht="42" spans="1:7">
+      <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="C18" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" ht="55.2" spans="1:7">
-      <c r="A17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="E18" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="2" t="s">
+    </row>
+    <row r="19" ht="56" spans="1:7">
+      <c r="A19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" ht="69" spans="1:7">
-      <c r="A18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E19" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="20" ht="70" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" ht="55.2" spans="1:7">
-      <c r="A19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="E20" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="2" t="s">
+    </row>
+    <row r="21" ht="56" spans="1:7">
+      <c r="A21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" ht="69" spans="1:7">
-      <c r="A20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="E21" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="2" t="s">
+    </row>
+    <row r="22" ht="70" spans="1:7">
+      <c r="A22" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="21" ht="55.2" spans="1:7">
-      <c r="A21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="E22" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" ht="55.2" spans="1:7">
-      <c r="A22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="23" ht="56" spans="1:7">
+      <c r="A23" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="D23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" ht="56" spans="1:7">
+      <c r="A24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="23" ht="41.4" spans="1:7">
-      <c r="A23" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="E24" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>no</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="2" t="s">
+    </row>
+    <row r="25" ht="42" spans="1:7">
+      <c r="A25" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="24" ht="69" spans="1:7">
-      <c r="A24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E25" s="10" t="str">
+        <f t="shared" ref="E25:E34" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>no</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" ht="41.4" spans="1:7">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="26" ht="70" spans="1:7">
+      <c r="A26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" ht="42" spans="1:7">
+      <c r="A27" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" ht="55.2" spans="1:7">
-      <c r="A26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="E27" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="2" t="s">
+    </row>
+    <row r="28" ht="42" spans="1:7">
+      <c r="A28" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="27" ht="41.4" spans="1:7">
-      <c r="A27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="E28" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" ht="41.4" spans="1:7">
-      <c r="A28" s="2" t="s">
+    </row>
+    <row r="29" ht="42" spans="1:7">
+      <c r="A29" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" ht="42" spans="1:7">
+      <c r="A30" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="29" ht="41.4" spans="1:7">
-      <c r="A29" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="E30" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" ht="42" spans="1:7">
+      <c r="A31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" ht="84" spans="1:7">
+      <c r="A32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" ht="82.8" spans="1:7">
-      <c r="A30" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" ht="55.2" spans="1:7">
-      <c r="A31" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" ht="56" spans="1:7">
+      <c r="A33" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="B33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="32" ht="27.6" spans="1:7">
-      <c r="A32" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="E33" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
         <v>122</v>
       </c>
-      <c r="D32" s="2" t="s">
+    </row>
+    <row r="34" ht="28" spans="1:7">
+      <c r="A34" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="B34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="33" ht="41.4" spans="1:7">
-      <c r="A33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="E34" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
         <v>126</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" t="s">
+    </row>
+    <row r="35" ht="42" spans="1:7">
+      <c r="A35" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="34" ht="41.4" spans="1:7">
-      <c r="A34" s="2" t="s">
+      <c r="B35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="E35" s="10" t="str">
+        <f t="shared" ref="E35:E44" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>no</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
         <v>129</v>
       </c>
-      <c r="D34" s="2" t="s">
+    </row>
+    <row r="36" ht="42" spans="1:7">
+      <c r="A36" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="35" ht="41.4" spans="1:7">
-      <c r="A35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="E36" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" t="s">
+    </row>
+    <row r="37" ht="42" spans="1:7">
+      <c r="A37" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="36" ht="27.6" spans="1:7">
-      <c r="A36" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E37" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="2" t="s">
+    </row>
+    <row r="38" ht="28" spans="1:7">
+      <c r="A38" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="B38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="37" ht="27.6" spans="1:7">
-      <c r="A37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="E38" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
         <v>140</v>
       </c>
-      <c r="D37" s="2" t="s">
+    </row>
+    <row r="39" ht="28" spans="1:7">
+      <c r="A39" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="B39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="38" ht="41.4" spans="1:7">
-      <c r="A38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="E39" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" t="s">
+    </row>
+    <row r="40" ht="42" spans="1:7">
+      <c r="A40" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="39" ht="41.4" spans="1:7">
-      <c r="A39" s="2" t="s">
+      <c r="B40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="2" t="s">
+    </row>
+    <row r="41" ht="42" spans="1:7">
+      <c r="A41" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="B41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="40" ht="55.2" spans="1:7">
-      <c r="A40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="E41" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="2" t="s">
+    </row>
+    <row r="42" ht="56" spans="1:7">
+      <c r="A42" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="B42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="41" ht="27.6" spans="1:7">
-      <c r="A41" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="E42" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
         <v>155</v>
       </c>
-      <c r="C41" s="2" t="s">
+    </row>
+    <row r="43" ht="28" spans="1:7">
+      <c r="A43" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" ht="41.4" spans="1:7">
-      <c r="A42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F43" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" ht="42" spans="1:7">
+      <c r="A44" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="B44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="43" ht="55.2" spans="1:7">
-      <c r="A43" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="E44" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>no</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="2" t="s">
+    </row>
+    <row r="45" ht="56" spans="1:7">
+      <c r="A45" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="B45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="44" ht="41.4" spans="1:7">
-      <c r="A44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="E45" s="10" t="str">
+        <f t="shared" ref="E45:E54" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>no</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
         <v>166</v>
       </c>
-      <c r="D44" s="2" t="s">
+    </row>
+    <row r="46" ht="42" spans="1:7">
+      <c r="A46" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="45" ht="41.4" spans="1:7">
-      <c r="A45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="E46" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
         <v>170</v>
       </c>
-      <c r="D45" s="2" t="s">
+    </row>
+    <row r="47" ht="42" spans="1:7">
+      <c r="A47" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="B47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="46" ht="55.2" spans="1:7">
-      <c r="A46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="E47" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
         <v>174</v>
       </c>
-      <c r="D46" s="2" t="s">
+    </row>
+    <row r="48" ht="56" spans="1:7">
+      <c r="A48" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" t="s">
-        <v>14</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="B48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="47" ht="41.4" spans="1:7">
-      <c r="A47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="E48" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" ht="42" spans="1:7">
+      <c r="A49" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" ht="42" spans="1:7">
+      <c r="A50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G51" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" ht="28" spans="1:7">
+      <c r="A52" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" ht="70" spans="1:7">
+      <c r="A53" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" ht="42" spans="1:7">
+      <c r="A54" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E54" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" ht="42" spans="1:7">
+      <c r="A55" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="10" t="str">
+        <f t="shared" ref="E55:E65" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
+        <v>no</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" ht="42" spans="1:7">
+      <c r="A56" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E56" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" ht="28" spans="1:7">
+      <c r="A57" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E57" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" ht="42" spans="1:7">
+      <c r="A58" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E58" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" ht="28" spans="1:7">
+      <c r="A59" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="60" ht="56" spans="1:7">
+      <c r="A60" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E60" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" ht="84" spans="1:7">
+      <c r="A61" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F61" t="s">
+        <v>59</v>
+      </c>
+      <c r="G61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" ht="84" spans="1:7">
+      <c r="A62" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" ht="41.4" spans="1:7">
-      <c r="A48" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B49" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E62" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F62" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" ht="42" spans="1:7">
+      <c r="A63" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E63" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" ht="42" spans="1:7">
+      <c r="A64" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E64" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" ht="56" spans="1:7">
+      <c r="A65" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" t="s">
-        <v>57</v>
-      </c>
-      <c r="G49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" ht="27.6" spans="1:7">
-      <c r="A50" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F50" t="s">
-        <v>57</v>
-      </c>
-      <c r="G50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" ht="69" spans="1:7">
-      <c r="A51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="52" ht="41.4" spans="1:7">
-      <c r="A52" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F52" t="s">
-        <v>14</v>
-      </c>
-      <c r="G52" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="53" ht="41.4" spans="1:7">
-      <c r="A53" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F53" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="54" ht="41.4" spans="1:7">
-      <c r="A54" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="55" ht="27.6" spans="1:7">
-      <c r="A55" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="56" ht="41.4" spans="1:7">
-      <c r="A56" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F56" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="57" ht="41.4" spans="1:7">
-      <c r="A57" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58" ht="69" spans="1:7">
-      <c r="A58" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="59" ht="82.8" spans="1:7">
-      <c r="A59" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F59" t="s">
-        <v>57</v>
-      </c>
-      <c r="G59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" ht="82.8" spans="1:7">
-      <c r="A60" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-      <c r="G60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" ht="41.4" spans="1:7">
-      <c r="A61" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F61" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="62" ht="41.4" spans="1:7">
-      <c r="A62" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F62" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="63" ht="55.2" spans="1:7">
-      <c r="A63" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F63" t="s">
-        <v>57</v>
-      </c>
-      <c r="G63" t="s">
-        <v>57</v>
+      <c r="C65" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+      <c r="F65" t="s">
+        <v>59</v>
+      </c>
+      <c r="G65" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4432,7 +4581,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -4441,145 +4590,145 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="2" s="4" customFormat="1" ht="27.6" spans="1:3">
-      <c r="A2" s="5">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="28" spans="1:3">
+      <c r="A2" s="6">
         <v>2026</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>237</v>
+      <c r="B2" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" ht="27.6" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" ht="41.4" spans="1:3">
+    </row>
+    <row r="5" ht="28" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" ht="27.6" spans="1:3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" ht="27.6" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10" ht="27.6" spans="1:3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="12" ht="27.6" spans="1:3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:3">
+      <c r="A13" s="2" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="13" ht="27.6" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="B13" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4595,7 +4744,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -4605,531 +4754,531 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>264</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" ht="41.4" spans="1:7">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" ht="42" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" ht="42" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="3" ht="41.4" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="4" ht="27.6" spans="1:7">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" ht="27.6" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" ht="27.6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="9" ht="42" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="10" ht="42" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" ht="42" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" ht="56" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" ht="41.4" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14" ht="42" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" ht="42" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="8" ht="27.6" spans="1:7">
-      <c r="A8" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" ht="28" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18" ht="42" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" ht="41.4" spans="1:7">
-      <c r="A9" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="10" ht="41.4" spans="1:7">
-      <c r="A10" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="11" ht="27.6" spans="1:7">
-      <c r="A11" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="12" ht="41.4" spans="1:7">
-      <c r="A12" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="13" ht="55.2" spans="1:7">
-      <c r="A13" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="14" ht="41.4" spans="1:7">
-      <c r="A14" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="15" ht="41.4" spans="1:7">
-      <c r="A15" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="16" ht="27.6" spans="1:7">
-      <c r="A16" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="17" ht="27.6" spans="1:7">
-      <c r="A17" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="18" ht="41.4" spans="1:7">
-      <c r="A18" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19" ht="27.6" spans="1:7">
-      <c r="A19" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="20" ht="27.6" spans="1:7">
-      <c r="A20" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="21" ht="27.6" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="22" ht="27.6" spans="1:7">
-      <c r="A22" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="23" ht="27.6" spans="1:7">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -5145,7 +5294,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E125"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
@@ -5158,2124 +5307,2124 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" ht="27.6" spans="1:5">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="3" ht="56" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="3" ht="55.2" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="4" ht="27.6" spans="1:5">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" ht="70" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="5" ht="69" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="6" ht="27.6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="7" ht="41.4" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="8" ht="41.4" spans="1:5">
+    <row r="8" ht="42" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" ht="27.6" spans="1:5">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="11" ht="27.6" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="B11" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="12" ht="41.4" spans="1:5">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" ht="42" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="14" ht="27.6" spans="1:5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="15" ht="27.6" spans="1:5">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="17" ht="82.8" spans="1:5">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" ht="84" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="18" ht="27.6" spans="1:5">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="19" ht="27.6" spans="1:5">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="21" ht="27.6" spans="1:5">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="22" ht="27.6" spans="1:5">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="23" ht="69" spans="1:5">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="23" ht="70" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" ht="28" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" ht="28" spans="1:5">
+      <c r="A27" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" ht="27.6" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="B27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" ht="28" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" ht="28" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" ht="28" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" ht="28" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" ht="28" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" ht="42" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" ht="28" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" ht="28" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" ht="28" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" ht="42" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" ht="28" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" ht="28" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" ht="28" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" ht="28" spans="1:5">
+      <c r="A42" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" ht="27.6" spans="1:5">
-      <c r="A42" s="2" t="s">
-        <v>453</v>
-      </c>
       <c r="B42" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" ht="28" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" ht="28" spans="1:5">
       <c r="A44" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" ht="28" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" ht="28" spans="1:5">
       <c r="A46" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" ht="28" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" ht="28" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" ht="28" spans="1:5">
       <c r="A49" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" ht="28" spans="1:5">
       <c r="A50" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" ht="28" spans="1:5">
       <c r="A51" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" ht="28" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" ht="28" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" ht="28" spans="1:5">
       <c r="A54" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" ht="28" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" ht="28" spans="1:5">
       <c r="A56" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" ht="28" spans="1:5">
       <c r="A57" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" ht="28" spans="1:5">
       <c r="A58" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" ht="28" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" ht="28" spans="1:5">
       <c r="A60" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" ht="28" spans="1:5">
       <c r="A61" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" ht="28" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" ht="28" spans="1:5">
       <c r="A63" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" ht="28" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" ht="28" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" ht="28" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" ht="28" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" ht="28" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" ht="28" spans="1:5">
       <c r="A69" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" ht="28" spans="1:5">
       <c r="A70" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" ht="28" spans="1:5">
       <c r="A71" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72" ht="28" spans="1:5">
       <c r="A72" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" ht="28" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" ht="28" spans="1:5">
       <c r="A74" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" ht="28" spans="1:5">
       <c r="A75" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="76" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" ht="28" spans="1:5">
       <c r="A76" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" ht="28" spans="1:5">
       <c r="A77" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="78" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78" ht="28" spans="1:5">
       <c r="A78" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="79" ht="28" spans="1:5">
       <c r="A79" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="80" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80" ht="28" spans="1:5">
       <c r="A80" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="81" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" ht="28" spans="1:5">
       <c r="A81" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" ht="28" spans="1:5">
       <c r="A82" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="83" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" ht="28" spans="1:5">
       <c r="A83" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="84" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" ht="28" spans="1:5">
       <c r="A84" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="85" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" ht="28" spans="1:5">
       <c r="A85" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="86" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" ht="28" spans="1:5">
       <c r="A86" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="87" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="87" ht="28" spans="1:5">
       <c r="A87" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="88" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="88" ht="28" spans="1:5">
       <c r="A88" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="89" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="89" ht="28" spans="1:5">
       <c r="A89" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" ht="28" spans="1:5">
       <c r="A90" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="91" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" ht="28" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="92" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92" ht="28" spans="1:5">
       <c r="A92" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" ht="27.6" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" ht="28" spans="1:5">
       <c r="A93" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="94" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" ht="42" spans="1:5">
       <c r="A94" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="95" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95" ht="42" spans="1:5">
       <c r="A95" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" ht="42" spans="1:5">
       <c r="A96" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="97" ht="42" spans="1:5">
+      <c r="A97" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="97" ht="41.4" spans="1:5">
-      <c r="A97" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="B97" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="98" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" ht="42" spans="1:5">
       <c r="A98" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="99" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="99" ht="42" spans="1:5">
       <c r="A99" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="100" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="100" ht="42" spans="1:5">
       <c r="A100" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="101" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" ht="42" spans="1:5">
       <c r="A101" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="102" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="102" ht="42" spans="1:5">
       <c r="A102" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="103" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="103" ht="42" spans="1:5">
       <c r="A103" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="104" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="104" ht="42" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="105" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="105" ht="42" spans="1:5">
       <c r="A105" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="106" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="106" ht="42" spans="1:5">
       <c r="A106" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="107" ht="55.2" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="107" ht="56" spans="1:5">
       <c r="A107" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="108" ht="55.2" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="108" ht="56" spans="1:5">
       <c r="A108" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="109" ht="42" spans="1:5">
       <c r="A109" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="110" ht="69" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="110" ht="70" spans="1:5">
       <c r="A110" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="111" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="111" ht="42" spans="1:5">
       <c r="A111" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="112" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="112" ht="42" spans="1:5">
       <c r="A112" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="113" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="113" ht="42" spans="1:5">
       <c r="A113" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="114" ht="42" spans="1:5">
       <c r="A114" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="115" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="115" ht="42" spans="1:5">
       <c r="A115" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="116" ht="55.2" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="116" ht="56" spans="1:5">
       <c r="A116" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="117" ht="69" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" ht="70" spans="1:5">
       <c r="A117" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="118" ht="69" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" ht="70" spans="1:5">
       <c r="A118" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="119" ht="56" spans="1:5">
+      <c r="A119" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="119" ht="55.2" spans="1:5">
-      <c r="A119" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="B119" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="120" ht="55.2" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" ht="56" spans="1:5">
       <c r="A120" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="121" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="121" ht="42" spans="1:5">
       <c r="A121" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="122" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" ht="42" spans="1:5">
       <c r="A122" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="123" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="123" ht="42" spans="1:5">
       <c r="A123" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="124" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="124" ht="42" spans="1:5">
       <c r="A124" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="125" ht="41.4" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" ht="42" spans="1:5">
       <c r="A125" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7291,7 +7440,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -7303,363 +7452,363 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="27.6" spans="1:4">
+    <row r="2" ht="28" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="3" ht="27.6" spans="1:4">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" ht="41.4" spans="1:4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" ht="42" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" ht="70" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" ht="69" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" ht="69" spans="1:4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" ht="70" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" ht="55.2" spans="1:4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" ht="56" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" ht="69" spans="1:4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" ht="70" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7675,7 +7824,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -7690,25 +7839,25 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -7721,7 +7870,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
@@ -7729,50 +7878,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="3" ht="27.6" spans="1:2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="5" ht="27.6" spans="1:2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CE0E00-10F4-4D0F-BA6B-CAB249D5DFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6E4F82-F07F-454B-9785-F554ECD641EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="570">
   <si>
     <t>date</t>
   </si>
@@ -1085,9 +1085,6 @@
     <t>International Journal of Computational Intelligence Systems (SCI)</t>
   </si>
   <si>
-    <t>since Feb. 2026; Area editor, Jul. 2024 - Feb. 2026; Editorial Board Member, Nov. 2019 - Jul. 2024</t>
-  </si>
-  <si>
     <t>Journal of Ambient Intelligence and Humanized Computing</t>
   </si>
   <si>
@@ -1550,30 +1547,18 @@
     <t>Qianqian Chen</t>
   </si>
   <si>
-    <t>1 Multimedia Systems, 1 TEM, 1 INS</t>
-  </si>
-  <si>
     <t>Yuan Gao</t>
   </si>
   <si>
-    <t>1 TFS, 1 KBS, 2 JORS, 1 ASOC, 2 INFFUS, 1 ESWA, excellent graduate of Dalian City, and excellent master thesis of Liaoning Province</t>
-  </si>
-  <si>
     <t>Zhuolin Li</t>
   </si>
   <si>
-    <t>1 EJOR, 3 TSMC, 1 Omega, 1 TCSS, 1 COR, 1 JORS, 1 ANOR, 1 KBS, 2 INFFUS, 1 CAIE, 4 National Scholarships, excellent graduate of Dalian City, and excellent master thesis of Liaoning Province</t>
-  </si>
-  <si>
     <t>https://lzlloveys.github.io/</t>
   </si>
   <si>
     <t>Zihang Jia</t>
   </si>
   <si>
-    <t>1 TCYB, 1 FSS, 1 ESWA, 1 AIRE, 1 SOCO, 1 IJFS</t>
-  </si>
-  <si>
     <t>Master Students</t>
   </si>
   <si>
@@ -1595,18 +1580,12 @@
     <t>Ziyu Xu</t>
   </si>
   <si>
-    <t>1 ANOR, 1 National Scholarship</t>
-  </si>
-  <si>
     <t>Yuan Jin</t>
   </si>
   <si>
     <t>Jize Luo</t>
   </si>
   <si>
-    <t>1 TSMC</t>
-  </si>
-  <si>
     <t>Yimingxuan Zhou</t>
   </si>
   <si>
@@ -1625,31 +1604,13 @@
     <t>Siyuan Ji</t>
   </si>
   <si>
-    <t>currently working in Tencent</t>
-  </si>
-  <si>
-    <t>1 EJOR, 2 TSMC, 1 Omega, 1 TCSS, 1 COR, 1 JORS, 1 ANOR, 1 KBS, 2 INFFUS, 1 CAIE, 3 National Scholarships, excellent graduate of Dalian City, and excellent master thesis of Liaoning Province</t>
-  </si>
-  <si>
     <t>Nan Wang</t>
   </si>
   <si>
-    <t>Ph. D. student in DUT</t>
-  </si>
-  <si>
-    <t>1 TFS, 1 KBS, 2 JORS, 1 ASOC, 1 INFFUS, 1 ESWA, excellent graduate of Dalian City, and excellent master thesis of Liaoning Province, Ph. D. student in DUT</t>
-  </si>
-  <si>
     <t>Junliang Gao</t>
   </si>
   <si>
-    <t>1 ESWA, 1 ASOC, currently working in ICBC</t>
-  </si>
-  <si>
     <t>Xinyue Kou</t>
-  </si>
-  <si>
-    <t>1 JORS 1 KBS, 1 ESWA, 1 ASOC, National Scholarship, Master Student Academic Star of DUT, excellent graduate and excellent master thesis of Liaoning Province, currently working in China UnionPay</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1777,6 +1738,50 @@
   </si>
   <si>
     <t>http://glgcxb.zju.edu.cn/home/content/82nce</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>since Feb. 2026; Area editor, Jul. 2024 - Feb. 2026; Editorial Board Member, Nov. 2019 - Jul. 2024</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yijun Chen</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Professor, Institute of Systems Engineering, DUT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PhD Students</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assitant Professor, School of Econimics and Management, SWJTU; Former PhD Student and Master Student</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shufei Peng</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xu Zou</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luanyu Kong</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhihe Yu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fu Xing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xiaoqi Zhai</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1849,7 +1854,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1859,9 +1864,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1896,12 +1898,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="40">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1914,6 +1932,210 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1956,7 +2178,6 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2208,25 +2429,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="24"/>
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="totalRow" dxfId="22"/>
-      <tableStyleElement type="firstColumn" dxfId="21"/>
-      <tableStyleElement type="lastColumn" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="18"/>
+      <tableStyleElement type="wholeTable" dxfId="39"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="totalRow" dxfId="37"/>
+      <tableStyleElement type="firstColumn" dxfId="36"/>
+      <tableStyleElement type="lastColumn" dxfId="35"/>
+      <tableStyleElement type="firstRowStripe" dxfId="34"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="33"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="32"/>
+      <tableStyleElement type="totalRow" dxfId="31"/>
+      <tableStyleElement type="firstRowStripe" dxfId="30"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="29"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="28"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="27"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="26"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="25"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="24"/>
+      <tableStyleElement type="pageFieldValues" dxfId="23"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2241,13 +2462,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E78" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E78" headerRowDxfId="22" dataDxfId="21" totalsRowDxfId="20">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="15">
       <calculatedColumnFormula>IF(ROW()-1&lt;11,"yes","no")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2282,25 +2503,25 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E125" headerRowDxfId="9" dataDxfId="7" totalsRowDxfId="8">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="GroupTable" displayName="GroupTable" ref="A1:D26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="GroupTable" displayName="GroupTable" ref="A1:D33" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2458,1400 +2679,1400 @@
   <dimension ref="A1:E78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.5" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="18" style="9" customWidth="1"/>
-    <col min="3" max="3" width="71.36328125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="18" style="9" customWidth="1"/>
-    <col min="5" max="5" width="18" style="15" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="9"/>
+    <col min="1" max="2" width="18" style="8" customWidth="1"/>
+    <col min="3" max="3" width="71.36328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18" style="14" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>46184</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="12" t="str">
+      <c r="E2" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>46177</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12" t="str">
+      <c r="E3" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>46168</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="str">
+      <c r="D4" s="10"/>
+      <c r="E4" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="12" t="str">
+      <c r="E5" s="11" t="str">
         <f t="shared" ref="E5:E14" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="12" t="str">
+      <c r="E6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="12" t="str">
+      <c r="E7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="str">
+      <c r="E8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="12" t="str">
+      <c r="E9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="12" t="str">
+      <c r="E10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="12" t="str">
+      <c r="E11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="12" t="str">
+      <c r="E12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>no</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12" t="str">
+      <c r="E13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>no</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="12" t="str">
+      <c r="E14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>no</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="12" t="str">
+      <c r="D15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="11" t="str">
         <f t="shared" ref="E15:E24" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="12" t="str">
+      <c r="E16" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="12" t="str">
+      <c r="E17" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="12" t="str">
+      <c r="E18" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="12" t="str">
+      <c r="E19" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="12" t="str">
+      <c r="E20" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="12" t="str">
+      <c r="E21" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="12" t="str">
+      <c r="E22" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="12" t="str">
+      <c r="D23" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="12" t="str">
+      <c r="E24" s="11" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="12" t="str">
+      <c r="E25" s="11" t="str">
         <f t="shared" ref="E25:E34" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="12" t="str">
+      <c r="D26" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="12" t="str">
+      <c r="E27" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="12" t="str">
+      <c r="E28" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" s="12" t="str">
+      <c r="D29" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E30" s="12" t="str">
+      <c r="E30" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="12" t="str">
+      <c r="E31" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="12" t="str">
+      <c r="D32" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="12" t="str">
+      <c r="E33" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E34" s="12" t="str">
+      <c r="E34" s="11" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="12" t="str">
+      <c r="E35" s="11" t="str">
         <f t="shared" ref="E35:E52" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="12" t="str">
+      <c r="E36" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="12" t="str">
+      <c r="E37" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E38" s="12" t="str">
+      <c r="E38" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="12" t="str">
+      <c r="E39" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A40" s="14">
+      <c r="A40" s="13">
         <v>45597</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="E40" s="12" t="str">
+      <c r="B40" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="E40" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A41" s="14">
+      <c r="A41" s="13">
         <v>45593</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="12" t="str">
+      <c r="B41" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="D41" s="10"/>
+      <c r="E41" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A42" s="14">
+      <c r="A42" s="13">
         <v>45585</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>553</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="E42" s="12" t="str">
+      <c r="B42" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E42" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A43" s="14">
+      <c r="A43" s="13">
         <v>45584</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>556</v>
-      </c>
-      <c r="E43" s="12" t="str">
+      <c r="B43" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="E43" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A44" s="14">
+      <c r="A44" s="13">
         <v>45583</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="E44" s="12" t="str">
+      <c r="B44" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="E44" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="12" t="str">
+      <c r="E45" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A46" s="14">
+      <c r="A46" s="13">
         <v>45580</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="12" t="str">
+      <c r="B46" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="D46" s="10"/>
+      <c r="E46" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="12" t="str">
+      <c r="E47" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="12" t="str">
+      <c r="E48" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E49" s="12" t="str">
+      <c r="D49" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A50" s="14">
+      <c r="A50" s="13">
         <v>45514</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="E50" s="12" t="str">
+      <c r="B50" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="E50" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E51" s="12" t="str">
+      <c r="E51" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A52" s="14">
+      <c r="A52" s="13">
         <v>45432</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="E52" s="12" t="str">
+      <c r="C52" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="E52" s="11" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E53" s="12" t="str">
+      <c r="E53" s="11" t="str">
         <f t="shared" ref="E53:E64" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E54" s="12" t="str">
+      <c r="E54" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E55" s="12" t="str">
+      <c r="E55" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E56" s="12" t="str">
+      <c r="E56" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E57" s="12" t="str">
+      <c r="E57" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A58" s="14">
+      <c r="A58" s="13">
         <v>45264</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="12" t="str">
+      <c r="B58" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="D58" s="10"/>
+      <c r="E58" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E59" s="12" t="str">
+      <c r="E59" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" s="12" t="str">
+      <c r="D60" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E61" s="12" t="str">
+      <c r="D61" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A62" s="14">
+      <c r="A62" s="13">
         <v>45118</v>
       </c>
-      <c r="B62" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="E62" s="12" t="str">
+      <c r="B62" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="E62" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E63" s="12" t="str">
+      <c r="E63" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E64" s="12" t="str">
+      <c r="E64" s="11" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A65" s="14">
+      <c r="A65" s="13">
         <v>45023</v>
       </c>
-      <c r="B65" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>567</v>
-      </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="12" t="str">
+      <c r="B65" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="D65" s="10"/>
+      <c r="E65" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A66" s="14">
+      <c r="A66" s="13">
         <v>45006</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="D66" s="11"/>
-      <c r="E66" s="12" t="str">
+      <c r="B66" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="D66" s="10"/>
+      <c r="E66" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E67" s="12" t="str">
+      <c r="E67" s="11" t="str">
         <f t="shared" ref="E67:E78" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="E68" s="12" t="str">
+      <c r="E68" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E69" s="12" t="str">
+      <c r="E69" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="E70" s="12" t="str">
+      <c r="E70" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A71" s="14">
+      <c r="A71" s="13">
         <v>44945</v>
       </c>
-      <c r="B71" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="E71" s="12" t="str">
+      <c r="B71" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="E71" s="11" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E72" s="12" t="str">
+      <c r="E72" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="12" t="str">
+      <c r="E73" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D74" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E74" s="12" t="str">
+      <c r="D74" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D75" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E75" s="12" t="str">
+      <c r="D75" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E76" s="12" t="str">
+      <c r="E76" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E77" s="12" t="str">
+      <c r="E77" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="54.5" customHeight="1">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D78" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E78" s="12" t="str">
+      <c r="D78" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E78" s="11" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
@@ -3886,14 +4107,14 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="5" customFormat="1" ht="28">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" s="4" customFormat="1" ht="28">
+      <c r="A2" s="5">
         <v>2026</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>187</v>
       </c>
     </row>
@@ -4579,2136 +4800,2137 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E125"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="2" width="18" style="16" customWidth="1"/>
+    <col min="3" max="3" width="32" style="16" customWidth="1"/>
+    <col min="4" max="4" width="42" style="16" customWidth="1"/>
+    <col min="5" max="5" width="32.90625" style="16" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="39" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="15" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="42">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" ht="39" customHeight="1">
+      <c r="A2" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="17" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="56">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5" ht="39" customHeight="1">
+      <c r="A3" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="17" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:5" ht="39" customHeight="1">
+      <c r="A4" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="17" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="84">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:5" ht="39" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="39" customHeight="1">
+      <c r="A6" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="28">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="39" customHeight="1">
+      <c r="A7" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="C7" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="39" customHeight="1">
+      <c r="A8" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="39" customHeight="1">
+      <c r="A9" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="39" customHeight="1">
+      <c r="A10" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="42">
-      <c r="A7" s="2" t="s">
+      <c r="C10" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="39" customHeight="1">
+      <c r="A11" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B11" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="39" customHeight="1">
+      <c r="A12" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="56">
-      <c r="A8" s="2" t="s">
+      <c r="C12" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="39" customHeight="1">
+      <c r="A13" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="B13" s="17" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="C13" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="39" customHeight="1">
+      <c r="A14" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="B14" s="17" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="28">
-      <c r="A10" s="2" t="s">
+      <c r="C14" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="39" customHeight="1">
+      <c r="A15" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B15" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="39" customHeight="1">
+      <c r="A16" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="39" customHeight="1">
+      <c r="A17" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="39" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="39" customHeight="1">
+      <c r="A19" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="39" customHeight="1">
+      <c r="A20" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="39" customHeight="1">
+      <c r="A21" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="39" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="39" customHeight="1">
+      <c r="A23" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="39" customHeight="1">
+      <c r="A24" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="39" customHeight="1">
+      <c r="A25" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="39" customHeight="1">
+      <c r="A26" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="39" customHeight="1">
+      <c r="A27" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="39" customHeight="1">
+      <c r="A28" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="39" customHeight="1">
+      <c r="A29" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="39" customHeight="1">
+      <c r="A30" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="39" customHeight="1">
+      <c r="A31" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="39" customHeight="1">
+      <c r="A32" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="39" customHeight="1">
+      <c r="A33" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="39" customHeight="1">
+      <c r="A34" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="39" customHeight="1">
+      <c r="A35" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="39" customHeight="1">
+      <c r="A36" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="39" customHeight="1">
+      <c r="A37" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="39" customHeight="1">
+      <c r="A38" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="39" customHeight="1">
+      <c r="A39" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="39" customHeight="1">
+      <c r="A40" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="39" customHeight="1">
+      <c r="A41" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="39" customHeight="1">
+      <c r="A42" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="28">
-      <c r="A11" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="42">
-      <c r="A12" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="28">
-      <c r="A13" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="42">
-      <c r="A14" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="42">
-      <c r="A15" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="112">
-      <c r="A17" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="28">
-      <c r="A18" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="28">
-      <c r="A19" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="28">
-      <c r="A20" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="28">
-      <c r="A21" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="28">
-      <c r="A22" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="84">
-      <c r="A23" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="28">
-      <c r="A24" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28">
-      <c r="A25" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="28">
-      <c r="A26" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="28">
-      <c r="A27" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="28">
-      <c r="A28" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="28">
-      <c r="A29" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="28">
-      <c r="A30" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="28">
-      <c r="A31" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="42">
-      <c r="A32" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="28">
-      <c r="A33" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="42">
-      <c r="A34" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="28">
-      <c r="A35" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="28">
-      <c r="A36" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="28">
-      <c r="A37" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="56">
-      <c r="A38" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="E42" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="39" customHeight="1">
+      <c r="A43" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="28">
-      <c r="A39" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="28">
-      <c r="A40" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="28">
-      <c r="A41" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="B43" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="28">
-      <c r="A42" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="28">
-      <c r="A43" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="39" customHeight="1">
+      <c r="A44" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="28">
-      <c r="A44" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="39" customHeight="1">
+      <c r="A45" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="28">
-      <c r="A45" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="39" customHeight="1">
+      <c r="A46" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="28">
-      <c r="A46" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="39" customHeight="1">
+      <c r="A47" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="28">
-      <c r="A47" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="39" customHeight="1">
+      <c r="A48" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="28">
-      <c r="A48" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="39" customHeight="1">
+      <c r="A49" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="28">
-      <c r="A49" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="39" customHeight="1">
+      <c r="A50" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="28">
-      <c r="A50" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="39" customHeight="1">
+      <c r="A51" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="28">
-      <c r="A51" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="39" customHeight="1">
+      <c r="A52" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="28">
-      <c r="A52" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="39" customHeight="1">
+      <c r="A53" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="28">
-      <c r="A53" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="39" customHeight="1">
+      <c r="A54" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="28">
-      <c r="A54" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="39" customHeight="1">
+      <c r="A55" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="28">
-      <c r="A55" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="39" customHeight="1">
+      <c r="A56" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="28">
-      <c r="A56" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="39" customHeight="1">
+      <c r="A57" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="28">
-      <c r="A57" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="39" customHeight="1">
+      <c r="A58" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="28">
-      <c r="A58" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="39" customHeight="1">
+      <c r="A59" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="28">
-      <c r="A59" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="39" customHeight="1">
+      <c r="A60" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="28">
-      <c r="A60" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="39" customHeight="1">
+      <c r="A61" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="28">
-      <c r="A61" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="39" customHeight="1">
+      <c r="A62" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="28">
-      <c r="A62" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="39" customHeight="1">
+      <c r="A63" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="28">
-      <c r="A63" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D63" s="2" t="s">
+      <c r="E63" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="39" customHeight="1">
+      <c r="A64" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="28">
-      <c r="A64" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="39" customHeight="1">
+      <c r="A65" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="28">
-      <c r="A65" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="39" customHeight="1">
+      <c r="A66" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="17" t="s">
         <v>430</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="28">
-      <c r="A66" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="39" customHeight="1">
+      <c r="A67" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="28">
-      <c r="A67" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="39" customHeight="1">
+      <c r="A68" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="28">
-      <c r="A68" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="39" customHeight="1">
+      <c r="A69" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="28">
-      <c r="A69" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="39" customHeight="1">
+      <c r="A70" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="39" customHeight="1">
+      <c r="A71" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="28">
-      <c r="A70" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="28">
-      <c r="A71" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="39" customHeight="1">
+      <c r="A72" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="28">
-      <c r="A72" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="39" customHeight="1">
+      <c r="A73" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="28">
-      <c r="A73" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="39" customHeight="1">
+      <c r="A74" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D74" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="28">
-      <c r="A74" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="39" customHeight="1">
+      <c r="A75" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D75" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="28">
-      <c r="A75" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="39" customHeight="1">
+      <c r="A76" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="28">
-      <c r="A76" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D76" s="2" t="s">
+      <c r="E76" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="39" customHeight="1">
+      <c r="A77" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="28">
-      <c r="A77" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D77" s="2" t="s">
+      <c r="E77" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="39" customHeight="1">
+      <c r="A78" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D78" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="28">
-      <c r="A78" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D78" s="2" t="s">
+      <c r="E78" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="39" customHeight="1">
+      <c r="A79" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="28">
-      <c r="A79" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="39" customHeight="1">
+      <c r="A80" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D80" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="28">
-      <c r="A80" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D80" s="2" t="s">
+      <c r="E80" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="39" customHeight="1">
+      <c r="A81" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D81" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="28">
-      <c r="A81" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="39" customHeight="1">
+      <c r="A82" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="28">
-      <c r="A82" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D82" s="2" t="s">
+      <c r="E82" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="39" customHeight="1">
+      <c r="A83" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="17" t="s">
         <v>446</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="28">
-      <c r="A83" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D83" s="2" t="s">
+      <c r="E83" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="39" customHeight="1">
+      <c r="A84" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="28">
-      <c r="A84" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D84" s="2" t="s">
+      <c r="E84" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="39" customHeight="1">
+      <c r="A85" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="28">
-      <c r="A85" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D85" s="2" t="s">
+      <c r="E85" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="39" customHeight="1">
+      <c r="A86" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="28">
-      <c r="A86" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D86" s="2" t="s">
+      <c r="E86" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="39" customHeight="1">
+      <c r="A87" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B87" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D87" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="28">
-      <c r="A87" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D87" s="2" t="s">
+      <c r="E87" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="39" customHeight="1">
+      <c r="A88" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D88" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="28">
-      <c r="A88" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="39" customHeight="1">
+      <c r="A89" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D89" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="28">
-      <c r="A89" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D89" s="2" t="s">
+      <c r="E89" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="39" customHeight="1">
+      <c r="A90" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D90" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="28">
-      <c r="A90" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D90" s="2" t="s">
+      <c r="E90" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="39" customHeight="1">
+      <c r="A91" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D91" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="28">
-      <c r="A91" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D91" s="2" t="s">
+      <c r="E91" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="39" customHeight="1">
+      <c r="A92" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B92" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D92" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="28">
-      <c r="A92" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D92" s="2" t="s">
+      <c r="E92" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="39" customHeight="1">
+      <c r="A93" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B93" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D93" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="28">
-      <c r="A93" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D93" s="2" t="s">
+      <c r="E93" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="39" customHeight="1">
+      <c r="A94" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="42">
-      <c r="A94" s="2" t="s">
+      <c r="B94" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D94" s="17" t="s">
         <v>458</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D94" s="2" t="s">
+      <c r="E94" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="39" customHeight="1">
+      <c r="A95" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B95" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="42">
-      <c r="A95" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="E95" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="39" customHeight="1">
+      <c r="A96" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D96" s="17" t="s">
         <v>460</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="42">
-      <c r="A96" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="39" customHeight="1">
+      <c r="A97" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B97" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D97" s="17" t="s">
         <v>461</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="42">
-      <c r="A97" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D97" s="2" t="s">
+      <c r="E97" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="39" customHeight="1">
+      <c r="A98" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D98" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="42">
-      <c r="A98" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D98" s="2" t="s">
+      <c r="E98" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="39" customHeight="1">
+      <c r="A99" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D99" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="42">
-      <c r="A99" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D99" s="2" t="s">
+      <c r="E99" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="39" customHeight="1">
+      <c r="A100" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D100" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="42">
-      <c r="A100" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D100" s="2" t="s">
+      <c r="E100" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="39" customHeight="1">
+      <c r="A101" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B101" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="42">
-      <c r="A101" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="39" customHeight="1">
+      <c r="A102" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B102" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" s="17" t="s">
         <v>466</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="42">
-      <c r="A102" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D102" s="2" t="s">
+      <c r="E102" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="39" customHeight="1">
+      <c r="A103" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B103" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="42">
-      <c r="A103" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D103" s="2" t="s">
+      <c r="E103" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="39" customHeight="1">
+      <c r="A104" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B104" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="42">
-      <c r="A104" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="E104" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="39" customHeight="1">
+      <c r="A105" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D105" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="42">
-      <c r="A105" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="39" customHeight="1">
+      <c r="A106" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="42">
-      <c r="A106" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="E106" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="39" customHeight="1">
+      <c r="A107" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="70">
-      <c r="A107" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D107" s="2" t="s">
+      <c r="E107" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="39" customHeight="1">
+      <c r="A108" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D108" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="70">
-      <c r="A108" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D108" s="2" t="s">
+      <c r="E108" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="39" customHeight="1">
+      <c r="A109" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="17" t="s">
         <v>473</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="42">
-      <c r="A109" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D109" s="2" t="s">
+      <c r="E109" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="39" customHeight="1">
+      <c r="A110" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="17" t="s">
         <v>474</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="84">
-      <c r="A110" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D110" s="2" t="s">
+      <c r="E110" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="39" customHeight="1">
+      <c r="A111" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B111" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="42">
-      <c r="A111" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D111" s="2" t="s">
+      <c r="E111" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="39" customHeight="1">
+      <c r="A112" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="42">
-      <c r="A112" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D112" s="2" t="s">
+      <c r="E112" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="39" customHeight="1">
+      <c r="A113" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C113" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="42">
-      <c r="A113" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D113" s="2" t="s">
+      <c r="E113" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="39" customHeight="1">
+      <c r="A114" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D114" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="42">
-      <c r="A114" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="39" customHeight="1">
+      <c r="A115" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D115" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="42">
-      <c r="A115" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D115" s="2" t="s">
+      <c r="E115" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="39" customHeight="1">
+      <c r="A116" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="56">
-      <c r="A116" s="2" t="s">
+      <c r="B116" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D116" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D116" s="2" t="s">
+      <c r="E116" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="39" customHeight="1">
+      <c r="A117" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D117" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="84">
-      <c r="A117" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="39" customHeight="1">
+      <c r="A118" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D118" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="84">
-      <c r="A118" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D118" s="2" t="s">
+      <c r="E118" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="39" customHeight="1">
+      <c r="A119" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D119" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="70">
-      <c r="A119" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D119" s="2" t="s">
+      <c r="E119" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="39" customHeight="1">
+      <c r="A120" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C120" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D120" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="56">
-      <c r="A120" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D120" s="2" t="s">
+      <c r="E120" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="39" customHeight="1">
+      <c r="A121" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D121" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="56">
-      <c r="A121" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D121" s="2" t="s">
+      <c r="E121" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="39" customHeight="1">
+      <c r="A122" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B122" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D122" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="56">
-      <c r="A122" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D122" s="2" t="s">
+      <c r="E122" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="39" customHeight="1">
+      <c r="A123" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D123" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="56">
-      <c r="A123" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D123" s="2" t="s">
+      <c r="E123" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="39" customHeight="1">
+      <c r="A124" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D124" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="56">
-      <c r="A124" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D124" s="2" t="s">
+      <c r="E124" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="39" customHeight="1">
+      <c r="A125" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="56">
-      <c r="A125" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="17" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6723,375 +6945,402 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="1" max="2" width="18" style="18" customWidth="1"/>
+    <col min="3" max="3" width="42" style="18" customWidth="1"/>
+    <col min="4" max="4" width="18" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28">
+      <c r="A2" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="28">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="19" t="s">
         <v>494</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="28">
+      <c r="A3" s="19" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="28">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="19" t="s">
         <v>498</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="20" t="s">
         <v>499</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="42">
+      <c r="A4" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="19" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="B6" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>502</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B29" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="56">
-      <c r="A5" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="70">
-      <c r="A6" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="19" t="s">
         <v>506</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28">
-      <c r="A7" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B30" s="19" t="s">
         <v>521</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B32" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B33" s="19" t="s">
         <v>523</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="70">
-      <c r="A22" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="56">
-      <c r="A24" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="70">
-      <c r="A26" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7140,7 +7389,7 @@
         <v>217</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -7160,50 +7409,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28">
       <c r="A2" s="2" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28">
       <c r="A3" s="2" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28">
       <c r="A5" s="2" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28">
       <c r="A6" s="2" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D86604-9819-4064-8841-92024B21B4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="566">
   <si>
     <t>date</t>
   </si>
@@ -1490,9 +1496,6 @@
     <t>The IEEE World Congress on Computational Intelligence (WCCI, 2016, 2018, 2020)</t>
   </si>
   <si>
-    <t>The IEEE International Conference on Systems, Man, and Cybernetics (SMC 2018, 2025)</t>
-  </si>
-  <si>
     <t>The 15th International FLINS Conference on Machine learning, Multi agent and Cyber physical systems (FLINS 2022)</t>
   </si>
   <si>
@@ -1502,245 +1505,251 @@
     <t>The 13th International FLINS Conference on Data Science and Knowledge Engineering for Sensing Decision Support (FLINS 2018)</t>
   </si>
   <si>
-    <t>The 12th International FLINS Conference on Decision Making and Soft Computing (FLINS 2016)</t>
-  </si>
-  <si>
-    <t>The 11th International FLINS Conference on Decision Making and Soft Computing (FLINS 2014)</t>
+    <t>The 16th World Congress of the International Fuzzy Systems Association and the 9th Conference of the European Society for Fuzzy Logic and Technology (IFSA-EUSFLAT 2015)</t>
+  </si>
+  <si>
+    <t>The 15th IFSA World Congress and 32nd Annual Meeting of NAFIPS (IFSA-NAFIPS 2013)</t>
+  </si>
+  <si>
+    <t>Joint 10th International Conference on Soft Computing and Intelligent Systems and 19th International Symposium on Advanced Intelligent Systems in conjunction with Intelligent Systems Workshop 2018 (SCIS-ISIS2018)</t>
+  </si>
+  <si>
+    <t>The 1st International Alan Turing Conference on Decision Support and Recommender Systems (DSRS-Turing 2019)</t>
+  </si>
+  <si>
+    <t>The 37th North American Fuzzy Information Processing Society Annual Conference (NAFIPS 2018)</t>
+  </si>
+  <si>
+    <t>The 2013 International Conference on Knowledge Science, Engineering and Management (KSEM 2013)</t>
+  </si>
+  <si>
+    <t>The 12th International Workshop on Meta-synthesis &amp; Complex Systems (MCS 2012)</t>
+  </si>
+  <si>
+    <t>Special Session Organizers</t>
+  </si>
+  <si>
+    <t>"Artificial Intelligence for Optimization and Decision Making", in FLINS-ISKE 2026, co-organized by Zhen Zhang, Lijun Sun, Jiapeng Liu and Yucheng Dong.</t>
+  </si>
+  <si>
+    <t>"Intelligent Group Decision Making and Consensus Process", in GDN 2021, GDN 2022, GDN 2023, GDN 2025, GDN 2026, co-organized by Zhen Zhang, Yucheng Dong, Francisco Chiclana and Enrique Herrera-Viedma.</t>
+  </si>
+  <si>
+    <t>"Data and Network-Driven Decision Analysis", in Annual Conference on Data Science and Knowledge Systems Engineering, SESC, 2022, 2025, co-organized by Zhen Zhang, Jian Wu and Yucheng Dong.</t>
+  </si>
+  <si>
+    <t>"Data and Network-Driven Decision Analysis", in the 2021 Annual Conference on Data Science and Knowledge Systems Engineering, SESC, co-organized by Zhen Zhang and Yucheng Dong.</t>
+  </si>
+  <si>
+    <t>"Consensus for large-scale Group Decision Making", in ICSSE 2020, co-organized by Jian Wu, Yucheng Dong, Zaiwu Gong, Yejun Xu, and Zhen Zhang.</t>
+  </si>
+  <si>
+    <t>"Managing Uncertainty in Data-Driven Decision Making", in FLINS 2020, co-organized by Zhen Zhang, Yucheng Dong and Yejun Xu.</t>
+  </si>
+  <si>
+    <t>"Data-Driven Decision Making with Uncertainty", in ISKE 2019, co-organized by Luis Martínez, Yucheng Dong and Zhen Zhang.</t>
+  </si>
+  <si>
+    <t>"Group Decision Making in Social Networks", in CIE 49, co-organized by Jian Wu, Yucheng Dong, Zaiwu Gong, Yejun Xu and Zhen Zhang.</t>
+  </si>
+  <si>
+    <t>"Consensus Process Decision Making", in GDN 2018, co-organized by Yucheng Dong, Zaiwu Gong, Jian Wu, Zhen Zhang and Haiming Liang.</t>
+  </si>
+  <si>
+    <t>"Intelligent Decision Support Systems: Models, Methods and Applications", in ISKE 2017, co-organized by Zhen Zhang and Jialin Han.</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Zhen Zhang</t>
+  </si>
+  <si>
+    <t>Professor, Institute of Systems Engineering, DUT</t>
+  </si>
+  <si>
+    <t>https://dm-dut.github.io/</t>
+  </si>
+  <si>
+    <t>Core Member</t>
+  </si>
+  <si>
+    <t>Wenyu Yu</t>
+  </si>
+  <si>
+    <t>Associate Professor, School of Data Science and Artificial Intelligence, DUFE</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=O1SESW8AAAAJ</t>
+  </si>
+  <si>
+    <t>Zhuolin Li</t>
+  </si>
+  <si>
+    <t>Assitant Professor, School of Econimics and Management, SWJTU; Former PhD Student and Master Student</t>
+  </si>
+  <si>
+    <t>https://lzlloveys.github.io/</t>
+  </si>
+  <si>
+    <t>PhD Students</t>
+  </si>
+  <si>
+    <t>Yijun Chen</t>
+  </si>
+  <si>
+    <t>Qianqian Chen</t>
+  </si>
+  <si>
+    <t>Zihang Jia</t>
+  </si>
+  <si>
+    <t>Yuan Gao</t>
+  </si>
+  <si>
+    <t>Master Students</t>
+  </si>
+  <si>
+    <t>Xu Zou</t>
+  </si>
+  <si>
+    <t>Shufei Peng</t>
+  </si>
+  <si>
+    <t>Luanyu Kong</t>
+  </si>
+  <si>
+    <t>Shanshan Miao</t>
+  </si>
+  <si>
+    <t>Junting Guo</t>
+  </si>
+  <si>
+    <t>Xiaotong Wu</t>
+  </si>
+  <si>
+    <t>Xiaoqi Zhai</t>
+  </si>
+  <si>
+    <t>Zhihe Yu</t>
+  </si>
+  <si>
+    <t>Fu Xing</t>
+  </si>
+  <si>
+    <t>Ying Li</t>
+  </si>
+  <si>
+    <t>Zitong Li</t>
+  </si>
+  <si>
+    <t>Ziyu Xu</t>
+  </si>
+  <si>
+    <t>Yuan Jin</t>
+  </si>
+  <si>
+    <t>Jize Luo</t>
+  </si>
+  <si>
+    <t>Yimingxuan Zhou</t>
+  </si>
+  <si>
+    <t>Nan Yuan</t>
+  </si>
+  <si>
+    <t>Xiaoyun Zhang</t>
+  </si>
+  <si>
+    <t>Jinfang Gu</t>
+  </si>
+  <si>
+    <t>Shuyao Shen</t>
+  </si>
+  <si>
+    <t>Siyuan Ji</t>
+  </si>
+  <si>
+    <t>Nan Wang</t>
+  </si>
+  <si>
+    <t>Junliang Gao</t>
+  </si>
+  <si>
+    <t>Xinyue Kou</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Maintain changing website content in Excel, then convert to JSON for the homepage.</t>
+  </si>
+  <si>
+    <t>Do not maintain here</t>
+  </si>
+  <si>
+    <t>Profile, external links, and Scholar settings are stable and stored in index.html/site.config.js.</t>
+  </si>
+  <si>
+    <t>Publications</t>
+  </si>
+  <si>
+    <t>Use your existing publication Excel. The converter supports a separate --publications-xlsx input and outputs data/publications.json.</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>python scripts/convert_excel_to_json.py --excel homepage_content.xlsx --out data</t>
+  </si>
+  <si>
+    <t>Command with publications</t>
+  </si>
+  <si>
+    <t>python scripts/convert_excel_to_json.py --excel homepage_content.xlsx --publications-xlsx publications.xlsx --out data</t>
+  </si>
+  <si>
+    <t>Publication filters</t>
+  </si>
+  <si>
+    <t>The webpage automatically displays all records and supports filtering by year and type/category.</t>
+  </si>
+  <si>
+    <t>The International Conference of Granular-Ball Computing (ICGBC 2026)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>The 17th FLINS Conference &amp; the 21st ISKE Conference: Machine Learning and Knowledge Engineering for Decision Making (FLINS-ISKE 2026)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>The IEEE International Conference on Systems, Man, and Cybernetics (SMC, 2018, 2025)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>The 12th International FLINS Conference on Decision Making and Soft Computing (FLINS, 2014, 2016)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Joint 17th World Congress of International Fuzzy Systems Association and 9th International Conference on Soft Computing and Intelligent Systems (IFSA-SCIS 2017)</t>
-  </si>
-  <si>
-    <t>The 16th World Congress of the International Fuzzy Systems Association and the 9th Conference of the European Society for Fuzzy Logic and Technology (IFSA-EUSFLAT 2015)</t>
-  </si>
-  <si>
-    <t>The 15th IFSA World Congress and 32nd Annual Meeting of NAFIPS (IFSA-NAFIPS 2013)</t>
-  </si>
-  <si>
-    <t>Joint 10th International Conference on Soft Computing and Intelligent Systems and 19th International Symposium on Advanced Intelligent Systems in conjunction with Intelligent Systems Workshop 2018 (SCIS-ISIS2018)</t>
-  </si>
-  <si>
-    <t>The 1st International Alan Turing Conference on Decision Support and Recommender Systems (DSRS-Turing 2019)</t>
-  </si>
-  <si>
-    <t>The 2018 IEEE International Conference on Technology Management, Operations and Decisions (IEEE ICTMOD 2018)</t>
-  </si>
-  <si>
-    <t>The 37th North American Fuzzy Information Processing Society Annual Conference (NAFIPS 2018)</t>
-  </si>
-  <si>
-    <t>The 2013 International Conference on Knowledge Science, Engineering and Management (KSEM 2013)</t>
-  </si>
-  <si>
-    <t>The 12th International Workshop on Meta-synthesis &amp; Complex Systems (MCS 2012)</t>
-  </si>
-  <si>
-    <t>Special Session Organizers</t>
-  </si>
-  <si>
-    <t>"Artificial Intelligence for Optimization and Decision Making", in FLINS-ISKE 2026, co-organized by Zhen Zhang, Lijun Sun, Jiapeng Liu and Yucheng Dong.</t>
-  </si>
-  <si>
-    <t>"Intelligent Group Decision Making and Consensus Process", in GDN 2021, GDN 2022, GDN 2023, GDN 2025, GDN 2026, co-organized by Zhen Zhang, Yucheng Dong, Francisco Chiclana and Enrique Herrera-Viedma.</t>
-  </si>
-  <si>
-    <t>"Data and Network-Driven Decision Analysis", in Annual Conference on Data Science and Knowledge Systems Engineering, SESC, 2022, 2025, co-organized by Zhen Zhang, Jian Wu and Yucheng Dong.</t>
-  </si>
-  <si>
-    <t>"Data and Network-Driven Decision Analysis", in the 2021 Annual Conference on Data Science and Knowledge Systems Engineering, SESC, co-organized by Zhen Zhang and Yucheng Dong.</t>
-  </si>
-  <si>
-    <t>"Consensus for large-scale Group Decision Making", in ICSSE 2020, co-organized by Jian Wu, Yucheng Dong, Zaiwu Gong, Yejun Xu, and Zhen Zhang.</t>
-  </si>
-  <si>
-    <t>"Managing Uncertainty in Data-Driven Decision Making", in FLINS 2020, co-organized by Zhen Zhang, Yucheng Dong and Yejun Xu.</t>
-  </si>
-  <si>
-    <t>"Data-Driven Decision Making with Uncertainty", in ISKE 2019, co-organized by Luis Martínez, Yucheng Dong and Zhen Zhang.</t>
-  </si>
-  <si>
-    <t>"Group Decision Making in Social Networks", in CIE 49, co-organized by Jian Wu, Yucheng Dong, Zaiwu Gong, Yejun Xu and Zhen Zhang.</t>
-  </si>
-  <si>
-    <t>"Consensus Process Decision Making", in GDN 2018, co-organized by Yucheng Dong, Zaiwu Gong, Jian Wu, Zhen Zhang and Haiming Liang.</t>
-  </si>
-  <si>
-    <t>"Intelligent Decision Support Systems: Models, Methods and Applications", in ISKE 2017, co-organized by Zhen Zhang and Jialin Han.</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>Zhen Zhang</t>
-  </si>
-  <si>
-    <t>Professor, Institute of Systems Engineering, DUT</t>
-  </si>
-  <si>
-    <t>https://dm-dut.github.io/</t>
-  </si>
-  <si>
-    <t>Core Member</t>
-  </si>
-  <si>
-    <t>Wenyu Yu</t>
-  </si>
-  <si>
-    <t>Associate Professor, School of Data Science and Artificial Intelligence, DUFE</t>
-  </si>
-  <si>
-    <t>https://scholar.google.com/citations?user=O1SESW8AAAAJ</t>
-  </si>
-  <si>
-    <t>Zhuolin Li</t>
-  </si>
-  <si>
-    <t>Assitant Professor, School of Econimics and Management, SWJTU; Former PhD Student and Master Student</t>
-  </si>
-  <si>
-    <t>https://lzlloveys.github.io/</t>
-  </si>
-  <si>
-    <t>PhD Students</t>
-  </si>
-  <si>
-    <t>Yijun Chen</t>
-  </si>
-  <si>
-    <t>Qianqian Chen</t>
-  </si>
-  <si>
-    <t>Zihang Jia</t>
-  </si>
-  <si>
-    <t>Yuan Gao</t>
-  </si>
-  <si>
-    <t>Master Students</t>
-  </si>
-  <si>
-    <t>Xu Zou</t>
-  </si>
-  <si>
-    <t>Shufei Peng</t>
-  </si>
-  <si>
-    <t>Luanyu Kong</t>
-  </si>
-  <si>
-    <t>Shanshan Miao</t>
-  </si>
-  <si>
-    <t>Junting Guo</t>
-  </si>
-  <si>
-    <t>Xiaotong Wu</t>
-  </si>
-  <si>
-    <t>Xiaoqi Zhai</t>
-  </si>
-  <si>
-    <t>Zhihe Yu</t>
-  </si>
-  <si>
-    <t>Fu Xing</t>
-  </si>
-  <si>
-    <t>Ying Li</t>
-  </si>
-  <si>
-    <t>Zitong Li</t>
-  </si>
-  <si>
-    <t>Ziyu Xu</t>
-  </si>
-  <si>
-    <t>Yuan Jin</t>
-  </si>
-  <si>
-    <t>Jize Luo</t>
-  </si>
-  <si>
-    <t>Yimingxuan Zhou</t>
-  </si>
-  <si>
-    <t>Nan Yuan</t>
-  </si>
-  <si>
-    <t>Xiaoyun Zhang</t>
-  </si>
-  <si>
-    <t>Jinfang Gu</t>
-  </si>
-  <si>
-    <t>Shuyao Shen</t>
-  </si>
-  <si>
-    <t>Siyuan Ji</t>
-  </si>
-  <si>
-    <t>Nan Wang</t>
-  </si>
-  <si>
-    <t>Junliang Gao</t>
-  </si>
-  <si>
-    <t>Xinyue Kou</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Maintain changing website content in Excel, then convert to JSON for the homepage.</t>
-  </si>
-  <si>
-    <t>Do not maintain here</t>
-  </si>
-  <si>
-    <t>Profile, external links, and Scholar settings are stable and stored in index.html/site.config.js.</t>
-  </si>
-  <si>
-    <t>Publications</t>
-  </si>
-  <si>
-    <t>Use your existing publication Excel. The converter supports a separate --publications-xlsx input and outputs data/publications.json.</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>python scripts/convert_excel_to_json.py --excel homepage_content.xlsx --out data</t>
-  </si>
-  <si>
-    <t>Command with publications</t>
-  </si>
-  <si>
-    <t>python scripts/convert_excel_to_json.py --excel homepage_content.xlsx --publications-xlsx publications.xlsx --out data</t>
-  </si>
-  <si>
-    <t>Publication filters</t>
-  </si>
-  <si>
-    <t>The webpage automatically displays all records and supports filtering by year and type/category.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> IEEE International Conference on Technology Management, Operations and Decisions (IEEE ICTMOD, 2018, 2026)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1756,168 +1765,27 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1930,194 +1798,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2125,271 +1807,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2398,16 +1838,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2416,270 +1856,329 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="31">
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf/>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
+        <b/>
       </font>
-      <alignment horizontal="left" vertical="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
+        <b/>
+        <color theme="1"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2690,7 +2189,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2718,125 +2217,8 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -2851,34 +2233,37 @@
       <tableStyleElement type="firstColumnStripe" dxfId="24"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="40"/>
-      <tableStyleElement type="totalRow" dxfId="39"/>
-      <tableStyleElement type="firstRowStripe" dxfId="38"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="37"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="36"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="35"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="34"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="33"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="32"/>
-      <tableStyleElement type="pageFieldValues" dxfId="31"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="totalRow" dxfId="22"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="20"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="19"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="18"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="17"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="16"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="15"/>
+      <tableStyleElement type="pageFieldValues" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NewsTable" displayName="NewsTable" ref="A1:E78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E78">
   <tableColumns count="5">
-    <tableColumn id="1" name="date" dataDxfId="0"/>
-    <tableColumn id="2" name="category" dataDxfId="1"/>
-    <tableColumn id="3" name="content" dataDxfId="2"/>
-    <tableColumn id="4" name="link" dataDxfId="3"/>
-    <tableColumn id="5" name="show_on_home" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="9">
       <calculatedColumnFormula>IF(ROW()-1&lt;11,"yes","no")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2887,51 +2272,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AwardsTable" displayName="AwardsTable" ref="A1:C13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AwardsTable" displayName="AwardsTable" ref="A1:C13">
   <tableColumns count="3">
-    <tableColumn id="1" name="year" dataDxfId="5"/>
-    <tableColumn id="2" name="title" dataDxfId="6"/>
-    <tableColumn id="3" name="organization" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="year"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="title"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="organization"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="GrantsTable" displayName="GrantsTable" ref="A1:G23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="GrantsTable" displayName="GrantsTable" ref="A1:G23">
   <tableColumns count="7">
-    <tableColumn id="1" name="no" dataDxfId="8"/>
-    <tableColumn id="2" name="role" dataDxfId="9"/>
-    <tableColumn id="3" name="title" dataDxfId="10"/>
-    <tableColumn id="4" name="funder" dataDxfId="11"/>
-    <tableColumn id="5" name="grant_no" dataDxfId="12"/>
-    <tableColumn id="6" name="amount" dataDxfId="13"/>
-    <tableColumn id="7" name="period" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="no"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="role"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="title"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="funder"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="grant_no"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="amount"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="period"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ServicesTable" displayName="ServicesTable" ref="A1:E124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E125">
   <tableColumns count="5">
-    <tableColumn id="1" name="category" dataDxfId="15"/>
-    <tableColumn id="2" name="role" dataDxfId="16"/>
-    <tableColumn id="3" name="organization" dataDxfId="17"/>
-    <tableColumn id="4" name="item" dataDxfId="18"/>
-    <tableColumn id="5" name="period" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="GroupTable" displayName="GroupTable" ref="A1:D33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="GroupTable" displayName="GroupTable" ref="A1:D33">
   <tableColumns count="4">
-    <tableColumn id="1" name="category" dataDxfId="20"/>
-    <tableColumn id="2" name="name" dataDxfId="21"/>
-    <tableColumn id="3" name="note" dataDxfId="22"/>
-    <tableColumn id="4" name="link" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3080,23 +2465,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E78"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.5" customHeight="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.45" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="13" customWidth="1"/>
-    <col min="3" max="3" width="71.3666666666667" style="13" customWidth="1"/>
+    <col min="3" max="3" width="71.33203125" style="13" customWidth="1"/>
     <col min="4" max="4" width="18" style="13" customWidth="1"/>
     <col min="5" max="5" width="18" style="14" customWidth="1"/>
     <col min="6" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
+    <row r="1" spans="1:5" ht="54.45" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3113,7 +2498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="54.45" customHeight="1">
       <c r="A2" s="16">
         <v>46184</v>
       </c>
@@ -3131,7 +2516,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="54.45" customHeight="1">
       <c r="A3" s="16">
         <v>46177</v>
       </c>
@@ -3149,7 +2534,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="54.45" customHeight="1">
       <c r="A4" s="16">
         <v>46168</v>
       </c>
@@ -3165,7 +2550,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="54.45" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>12</v>
       </c>
@@ -3183,7 +2568,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="54.45" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
@@ -3201,7 +2586,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="54.45" customHeight="1">
       <c r="A7" s="17" t="s">
         <v>19</v>
       </c>
@@ -3219,7 +2604,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:5">
+    <row r="8" spans="1:5" ht="54.45" customHeight="1">
       <c r="A8" s="17" t="s">
         <v>23</v>
       </c>
@@ -3237,7 +2622,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="54.45" customHeight="1">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -3255,7 +2640,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="54.45" customHeight="1">
       <c r="A10" s="17" t="s">
         <v>30</v>
       </c>
@@ -3273,7 +2658,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:5">
+    <row r="11" spans="1:5" ht="54.45" customHeight="1">
       <c r="A11" s="17" t="s">
         <v>33</v>
       </c>
@@ -3291,7 +2676,7 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:5">
+    <row r="12" spans="1:5" ht="54.45" customHeight="1">
       <c r="A12" s="17" t="s">
         <v>33</v>
       </c>
@@ -3309,7 +2694,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:5">
+    <row r="13" spans="1:5" ht="54.45" customHeight="1">
       <c r="A13" s="17" t="s">
         <v>38</v>
       </c>
@@ -3327,7 +2712,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:5">
+    <row r="14" spans="1:5" ht="54.45" customHeight="1">
       <c r="A14" s="17" t="s">
         <v>41</v>
       </c>
@@ -3345,7 +2730,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:5">
+    <row r="15" spans="1:5" ht="54.45" customHeight="1">
       <c r="A15" s="17" t="s">
         <v>44</v>
       </c>
@@ -3363,7 +2748,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:5">
+    <row r="16" spans="1:5" ht="54.45" customHeight="1">
       <c r="A16" s="17" t="s">
         <v>47</v>
       </c>
@@ -3381,7 +2766,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:5">
+    <row r="17" spans="1:5" ht="54.45" customHeight="1">
       <c r="A17" s="17" t="s">
         <v>50</v>
       </c>
@@ -3399,7 +2784,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:5">
+    <row r="18" spans="1:5" ht="54.45" customHeight="1">
       <c r="A18" s="17" t="s">
         <v>53</v>
       </c>
@@ -3417,7 +2802,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:5">
+    <row r="19" spans="1:5" ht="54.45" customHeight="1">
       <c r="A19" s="17" t="s">
         <v>57</v>
       </c>
@@ -3435,7 +2820,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:5">
+    <row r="20" spans="1:5" ht="54.45" customHeight="1">
       <c r="A20" s="17" t="s">
         <v>57</v>
       </c>
@@ -3453,7 +2838,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:5">
+    <row r="21" spans="1:5" ht="54.45" customHeight="1">
       <c r="A21" s="17" t="s">
         <v>62</v>
       </c>
@@ -3471,7 +2856,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:5">
+    <row r="22" spans="1:5" ht="54.45" customHeight="1">
       <c r="A22" s="17" t="s">
         <v>65</v>
       </c>
@@ -3489,7 +2874,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:5">
+    <row r="23" spans="1:5" ht="54.45" customHeight="1">
       <c r="A23" s="17" t="s">
         <v>68</v>
       </c>
@@ -3507,7 +2892,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="54.45" customHeight="1">
       <c r="A24" s="17" t="s">
         <v>68</v>
       </c>
@@ -3525,7 +2910,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="54.45" customHeight="1">
       <c r="A25" s="17" t="s">
         <v>72</v>
       </c>
@@ -3543,7 +2928,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:5">
+    <row r="26" spans="1:5" ht="54.45" customHeight="1">
       <c r="A26" s="17" t="s">
         <v>75</v>
       </c>
@@ -3561,7 +2946,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:5">
+    <row r="27" spans="1:5" ht="54.45" customHeight="1">
       <c r="A27" s="17" t="s">
         <v>77</v>
       </c>
@@ -3579,7 +2964,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:5">
+    <row r="28" spans="1:5" ht="54.45" customHeight="1">
       <c r="A28" s="17" t="s">
         <v>80</v>
       </c>
@@ -3597,7 +2982,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:5">
+    <row r="29" spans="1:5" ht="54.45" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>83</v>
       </c>
@@ -3615,7 +3000,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:5">
+    <row r="30" spans="1:5" ht="54.45" customHeight="1">
       <c r="A30" s="17" t="s">
         <v>85</v>
       </c>
@@ -3633,7 +3018,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:5">
+    <row r="31" spans="1:5" ht="54.45" customHeight="1">
       <c r="A31" s="17" t="s">
         <v>88</v>
       </c>
@@ -3651,7 +3036,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:5">
+    <row r="32" spans="1:5" ht="54.45" customHeight="1">
       <c r="A32" s="17" t="s">
         <v>91</v>
       </c>
@@ -3669,7 +3054,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:5">
+    <row r="33" spans="1:5" ht="54.45" customHeight="1">
       <c r="A33" s="17" t="s">
         <v>93</v>
       </c>
@@ -3687,7 +3072,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:5">
+    <row r="34" spans="1:5" ht="54.45" customHeight="1">
       <c r="A34" s="17" t="s">
         <v>96</v>
       </c>
@@ -3705,7 +3090,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:5">
+    <row r="35" spans="1:5" ht="54.45" customHeight="1">
       <c r="A35" s="17" t="s">
         <v>99</v>
       </c>
@@ -3723,7 +3108,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:5">
+    <row r="36" spans="1:5" ht="54.45" customHeight="1">
       <c r="A36" s="17" t="s">
         <v>101</v>
       </c>
@@ -3741,7 +3126,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:5">
+    <row r="37" spans="1:5" ht="54.45" customHeight="1">
       <c r="A37" s="17" t="s">
         <v>104</v>
       </c>
@@ -3759,7 +3144,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:5">
+    <row r="38" spans="1:5" ht="54.45" customHeight="1">
       <c r="A38" s="17" t="s">
         <v>106</v>
       </c>
@@ -3777,7 +3162,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:5">
+    <row r="39" spans="1:5" ht="54.45" customHeight="1">
       <c r="A39" s="17" t="s">
         <v>109</v>
       </c>
@@ -3795,7 +3180,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:5">
+    <row r="40" spans="1:5" ht="54.45" customHeight="1">
       <c r="A40" s="20">
         <v>45597</v>
       </c>
@@ -3813,7 +3198,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:5">
+    <row r="41" spans="1:5" ht="54.45" customHeight="1">
       <c r="A41" s="20">
         <v>45593</v>
       </c>
@@ -3829,7 +3214,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:5">
+    <row r="42" spans="1:5" ht="54.45" customHeight="1">
       <c r="A42" s="20">
         <v>45585</v>
       </c>
@@ -3847,7 +3232,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:5">
+    <row r="43" spans="1:5" ht="54.45" customHeight="1">
       <c r="A43" s="20">
         <v>45584</v>
       </c>
@@ -3865,7 +3250,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:5">
+    <row r="44" spans="1:5" ht="54.45" customHeight="1">
       <c r="A44" s="20">
         <v>45583</v>
       </c>
@@ -3883,7 +3268,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:5">
+    <row r="45" spans="1:5" ht="54.45" customHeight="1">
       <c r="A45" s="17" t="s">
         <v>121</v>
       </c>
@@ -3901,7 +3286,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:5">
+    <row r="46" spans="1:5" ht="54.45" customHeight="1">
       <c r="A46" s="20">
         <v>45580</v>
       </c>
@@ -3917,7 +3302,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:5">
+    <row r="47" spans="1:5" ht="54.45" customHeight="1">
       <c r="A47" s="17" t="s">
         <v>124</v>
       </c>
@@ -3935,7 +3320,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:5">
+    <row r="48" spans="1:5" ht="54.45" customHeight="1">
       <c r="A48" s="17" t="s">
         <v>127</v>
       </c>
@@ -3953,7 +3338,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:5">
+    <row r="49" spans="1:5" ht="54.45" customHeight="1">
       <c r="A49" s="17" t="s">
         <v>130</v>
       </c>
@@ -3971,7 +3356,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:5">
+    <row r="50" spans="1:5" ht="54.45" customHeight="1">
       <c r="A50" s="20">
         <v>45514</v>
       </c>
@@ -3989,7 +3374,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:5">
+    <row r="51" spans="1:5" ht="54.45" customHeight="1">
       <c r="A51" s="17" t="s">
         <v>135</v>
       </c>
@@ -4007,7 +3392,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:5">
+    <row r="52" spans="1:5" ht="54.45" customHeight="1">
       <c r="A52" s="20">
         <v>45432</v>
       </c>
@@ -4025,7 +3410,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:5">
+    <row r="53" spans="1:5" ht="54.45" customHeight="1">
       <c r="A53" s="17" t="s">
         <v>140</v>
       </c>
@@ -4043,7 +3428,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:5">
+    <row r="54" spans="1:5" ht="54.45" customHeight="1">
       <c r="A54" s="17" t="s">
         <v>143</v>
       </c>
@@ -4061,7 +3446,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:5">
+    <row r="55" spans="1:5" ht="54.45" customHeight="1">
       <c r="A55" s="17" t="s">
         <v>146</v>
       </c>
@@ -4079,7 +3464,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:5">
+    <row r="56" spans="1:5" ht="54.45" customHeight="1">
       <c r="A56" s="17" t="s">
         <v>149</v>
       </c>
@@ -4097,7 +3482,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:5">
+    <row r="57" spans="1:5" ht="54.45" customHeight="1">
       <c r="A57" s="17" t="s">
         <v>152</v>
       </c>
@@ -4115,7 +3500,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:5">
+    <row r="58" spans="1:5" ht="54.45" customHeight="1">
       <c r="A58" s="20">
         <v>45264</v>
       </c>
@@ -4131,7 +3516,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:5">
+    <row r="59" spans="1:5" ht="54.45" customHeight="1">
       <c r="A59" s="17" t="s">
         <v>156</v>
       </c>
@@ -4149,7 +3534,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:5">
+    <row r="60" spans="1:5" ht="54.45" customHeight="1">
       <c r="A60" s="17" t="s">
         <v>159</v>
       </c>
@@ -4167,7 +3552,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:5">
+    <row r="61" spans="1:5" ht="54.45" customHeight="1">
       <c r="A61" s="17" t="s">
         <v>161</v>
       </c>
@@ -4185,7 +3570,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:5">
+    <row r="62" spans="1:5" ht="54.45" customHeight="1">
       <c r="A62" s="20">
         <v>45118</v>
       </c>
@@ -4203,7 +3588,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:5">
+    <row r="63" spans="1:5" ht="54.45" customHeight="1">
       <c r="A63" s="17" t="s">
         <v>165</v>
       </c>
@@ -4221,7 +3606,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:5">
+    <row r="64" spans="1:5" ht="54.45" customHeight="1">
       <c r="A64" s="17" t="s">
         <v>168</v>
       </c>
@@ -4239,7 +3624,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:5">
+    <row r="65" spans="1:5" ht="54.45" customHeight="1">
       <c r="A65" s="20">
         <v>45023</v>
       </c>
@@ -4255,7 +3640,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:5">
+    <row r="66" spans="1:5" ht="54.45" customHeight="1">
       <c r="A66" s="20">
         <v>45006</v>
       </c>
@@ -4271,7 +3656,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:5">
+    <row r="67" spans="1:5" ht="54.45" customHeight="1">
       <c r="A67" s="17" t="s">
         <v>173</v>
       </c>
@@ -4289,7 +3674,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:5">
+    <row r="68" spans="1:5" ht="54.45" customHeight="1">
       <c r="A68" s="17" t="s">
         <v>176</v>
       </c>
@@ -4307,7 +3692,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:5">
+    <row r="69" spans="1:5" ht="54.45" customHeight="1">
       <c r="A69" s="17" t="s">
         <v>179</v>
       </c>
@@ -4325,7 +3710,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:5">
+    <row r="70" spans="1:5" ht="54.45" customHeight="1">
       <c r="A70" s="17" t="s">
         <v>182</v>
       </c>
@@ -4343,7 +3728,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:5">
+    <row r="71" spans="1:5" ht="54.45" customHeight="1">
       <c r="A71" s="20">
         <v>44945</v>
       </c>
@@ -4361,7 +3746,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:5">
+    <row r="72" spans="1:5" ht="54.45" customHeight="1">
       <c r="A72" s="17" t="s">
         <v>187</v>
       </c>
@@ -4379,7 +3764,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:5">
+    <row r="73" spans="1:5" ht="54.45" customHeight="1">
       <c r="A73" s="17" t="s">
         <v>189</v>
       </c>
@@ -4397,7 +3782,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:5">
+    <row r="74" spans="1:5" ht="54.45" customHeight="1">
       <c r="A74" s="17" t="s">
         <v>192</v>
       </c>
@@ -4415,7 +3800,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:5">
+    <row r="75" spans="1:5" ht="54.45" customHeight="1">
       <c r="A75" s="17" t="s">
         <v>194</v>
       </c>
@@ -4433,7 +3818,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:5">
+    <row r="76" spans="1:5" ht="54.45" customHeight="1">
       <c r="A76" s="17" t="s">
         <v>196</v>
       </c>
@@ -4451,7 +3836,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:5">
+    <row r="77" spans="1:5" ht="54.45" customHeight="1">
       <c r="A77" s="17" t="s">
         <v>199</v>
       </c>
@@ -4469,7 +3854,7 @@
         <v>no</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:5">
+    <row r="78" spans="1:5" ht="54.45" customHeight="1">
       <c r="A78" s="17" t="s">
         <v>202</v>
       </c>
@@ -4488,8 +3873,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4497,10 +3882,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -4518,7 +3902,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" s="11" customFormat="1" ht="27.6" spans="1:3">
+    <row r="2" spans="1:3" s="11" customFormat="1" ht="28.8">
       <c r="A2" s="12">
         <v>2026</v>
       </c>
@@ -4540,7 +3924,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" ht="27.6" spans="1:3">
+    <row r="4" spans="1:3" ht="28.8">
       <c r="A4" s="2" t="s">
         <v>209</v>
       </c>
@@ -4551,7 +3935,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" ht="41.4" spans="1:3">
+    <row r="5" spans="1:3" ht="43.2">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -4562,7 +3946,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" ht="27.6" spans="1:3">
+    <row r="6" spans="1:3" ht="28.8">
       <c r="A6" s="2" t="s">
         <v>212</v>
       </c>
@@ -4584,7 +3968,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="8" ht="27.6" spans="1:3">
+    <row r="8" spans="1:3" ht="28.8">
       <c r="A8" s="2" t="s">
         <v>219</v>
       </c>
@@ -4606,7 +3990,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="10" ht="27.6" spans="1:3">
+    <row r="10" spans="1:3" ht="43.2">
       <c r="A10" s="2" t="s">
         <v>224</v>
       </c>
@@ -4628,7 +4012,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="12" ht="27.6" spans="1:3">
+    <row r="12" spans="1:3" ht="43.2">
       <c r="A12" s="2" t="s">
         <v>229</v>
       </c>
@@ -4639,7 +4023,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" ht="27.6" spans="1:3">
+    <row r="13" spans="1:3" ht="28.8">
       <c r="A13" s="2" t="s">
         <v>229</v>
       </c>
@@ -4651,8 +4035,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4660,10 +4044,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
@@ -4694,7 +4077,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="2" ht="41.4" spans="1:7">
+    <row r="2" spans="1:7" ht="57.6">
       <c r="A2" s="2" t="s">
         <v>239</v>
       </c>
@@ -4717,7 +4100,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="3" ht="41.4" spans="1:7">
+    <row r="3" spans="1:7" ht="57.6">
       <c r="A3" s="2" t="s">
         <v>246</v>
       </c>
@@ -4740,7 +4123,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" ht="27.6" spans="1:7">
+    <row r="4" spans="1:7" ht="43.2">
       <c r="A4" s="2" t="s">
         <v>251</v>
       </c>
@@ -4763,7 +4146,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" ht="27.6" spans="1:7">
+    <row r="5" spans="1:7" ht="43.2">
       <c r="A5" s="2" t="s">
         <v>256</v>
       </c>
@@ -4786,7 +4169,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" ht="27.6" spans="1:7">
+    <row r="6" spans="1:7" ht="43.2">
       <c r="A6" s="2" t="s">
         <v>262</v>
       </c>
@@ -4809,7 +4192,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="7" ht="41.4" spans="1:7">
+    <row r="7" spans="1:7" ht="43.2">
       <c r="A7" s="2" t="s">
         <v>267</v>
       </c>
@@ -4832,7 +4215,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8" ht="27.6" spans="1:7">
+    <row r="8" spans="1:7" ht="43.2">
       <c r="A8" s="2" t="s">
         <v>273</v>
       </c>
@@ -4855,7 +4238,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" ht="41.4" spans="1:7">
+    <row r="9" spans="1:7" ht="43.2">
       <c r="A9" s="2" t="s">
         <v>278</v>
       </c>
@@ -4878,7 +4261,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" ht="41.4" spans="1:7">
+    <row r="10" spans="1:7" ht="43.2">
       <c r="A10" s="2" t="s">
         <v>284</v>
       </c>
@@ -4901,7 +4284,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="11" ht="27.6" spans="1:7">
+    <row r="11" spans="1:7" ht="43.2">
       <c r="A11" s="2" t="s">
         <v>288</v>
       </c>
@@ -4924,7 +4307,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" ht="41.4" spans="1:7">
+    <row r="12" spans="1:7" ht="43.2">
       <c r="A12" s="2" t="s">
         <v>292</v>
       </c>
@@ -4947,7 +4330,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="13" ht="55.2" spans="1:7">
+    <row r="13" spans="1:7" ht="57.6">
       <c r="A13" s="2" t="s">
         <v>297</v>
       </c>
@@ -4970,7 +4353,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="14" ht="41.4" spans="1:7">
+    <row r="14" spans="1:7" ht="43.2">
       <c r="A14" s="2" t="s">
         <v>303</v>
       </c>
@@ -4993,7 +4376,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="15" ht="41.4" spans="1:7">
+    <row r="15" spans="1:7" ht="43.2">
       <c r="A15" s="2" t="s">
         <v>310</v>
       </c>
@@ -5016,7 +4399,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="16" ht="27.6" spans="1:7">
+    <row r="16" spans="1:7" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>315</v>
       </c>
@@ -5039,7 +4422,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="17" ht="27.6" spans="1:7">
+    <row r="17" spans="1:7" ht="28.8">
       <c r="A17" s="2" t="s">
         <v>320</v>
       </c>
@@ -5062,7 +4445,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="18" ht="41.4" spans="1:7">
+    <row r="18" spans="1:7" ht="57.6">
       <c r="A18" s="2" t="s">
         <v>325</v>
       </c>
@@ -5085,7 +4468,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="19" ht="27.6" spans="1:7">
+    <row r="19" spans="1:7" ht="28.8">
       <c r="A19" s="2" t="s">
         <v>330</v>
       </c>
@@ -5108,7 +4491,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" ht="27.6" spans="1:7">
+    <row r="20" spans="1:7" ht="28.8">
       <c r="A20" s="2" t="s">
         <v>335</v>
       </c>
@@ -5131,7 +4514,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="21" ht="27.6" spans="1:7">
+    <row r="21" spans="1:7" ht="43.2">
       <c r="A21" s="2" t="s">
         <v>341</v>
       </c>
@@ -5154,7 +4537,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="22" ht="27.6" spans="1:7">
+    <row r="22" spans="1:7" ht="43.2">
       <c r="A22" s="2" t="s">
         <v>345</v>
       </c>
@@ -5177,7 +4560,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="23" ht="27.6" spans="1:7">
+    <row r="23" spans="1:7" ht="43.2">
       <c r="A23" s="2" t="s">
         <v>351</v>
       </c>
@@ -5201,8 +4584,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5210,19 +4593,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E125"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="8" customWidth="1"/>
     <col min="3" max="3" width="32" style="8" customWidth="1"/>
     <col min="4" max="4" width="42" style="8" customWidth="1"/>
-    <col min="5" max="5" width="32.9083333333333" style="8" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" style="8" customWidth="1"/>
     <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
+    <row r="1" spans="1:5" ht="39" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
@@ -5239,7 +4621,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="39" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>358</v>
       </c>
@@ -5256,7 +4638,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="39" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>358</v>
       </c>
@@ -5273,7 +4655,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="39" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>358</v>
       </c>
@@ -5290,7 +4672,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="39" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>358</v>
       </c>
@@ -5307,7 +4689,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="39" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>358</v>
       </c>
@@ -5324,7 +4706,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="39" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>358</v>
       </c>
@@ -5341,7 +4723,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:5">
+    <row r="8" spans="1:5" ht="39" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>358</v>
       </c>
@@ -5358,7 +4740,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:5">
+    <row r="9" spans="1:5" ht="39" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>358</v>
       </c>
@@ -5375,7 +4757,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:5">
+    <row r="10" spans="1:5" ht="39" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
@@ -5392,7 +4774,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:5">
+    <row r="11" spans="1:5" ht="39" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>358</v>
       </c>
@@ -5409,7 +4791,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:5">
+    <row r="12" spans="1:5" ht="39" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>358</v>
       </c>
@@ -5426,7 +4808,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:5">
+    <row r="13" spans="1:5" ht="39" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>358</v>
       </c>
@@ -5443,7 +4825,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:5">
+    <row r="14" spans="1:5" ht="39" customHeight="1">
       <c r="A14" s="10" t="s">
         <v>358</v>
       </c>
@@ -5460,7 +4842,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:5">
+    <row r="15" spans="1:5" ht="39" customHeight="1">
       <c r="A15" s="10" t="s">
         <v>358</v>
       </c>
@@ -5477,7 +4859,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:5">
+    <row r="16" spans="1:5" ht="39" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>358</v>
       </c>
@@ -5494,7 +4876,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:5">
+    <row r="17" spans="1:5" ht="39" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>358</v>
       </c>
@@ -5511,7 +4893,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:5">
+    <row r="18" spans="1:5" ht="39" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>358</v>
       </c>
@@ -5528,7 +4910,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:5">
+    <row r="19" spans="1:5" ht="39" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>358</v>
       </c>
@@ -5545,7 +4927,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:5">
+    <row r="20" spans="1:5" ht="39" customHeight="1">
       <c r="A20" s="10" t="s">
         <v>358</v>
       </c>
@@ -5562,7 +4944,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:5">
+    <row r="21" spans="1:5" ht="39" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>358</v>
       </c>
@@ -5579,7 +4961,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:5">
+    <row r="22" spans="1:5" ht="39" customHeight="1">
       <c r="A22" s="10" t="s">
         <v>358</v>
       </c>
@@ -5596,7 +4978,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:5">
+    <row r="23" spans="1:5" ht="39" customHeight="1">
       <c r="A23" s="10" t="s">
         <v>407</v>
       </c>
@@ -5613,7 +4995,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:5">
+    <row r="24" spans="1:5" ht="39" customHeight="1">
       <c r="A24" s="10" t="s">
         <v>407</v>
       </c>
@@ -5630,7 +5012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:5">
+    <row r="25" spans="1:5" ht="39" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>407</v>
       </c>
@@ -5647,7 +5029,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:5">
+    <row r="26" spans="1:5" ht="39" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>407</v>
       </c>
@@ -5664,7 +5046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:5">
+    <row r="27" spans="1:5" ht="39" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>407</v>
       </c>
@@ -5681,7 +5063,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:5">
+    <row r="28" spans="1:5" ht="39" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>407</v>
       </c>
@@ -5698,7 +5080,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:5">
+    <row r="29" spans="1:5" ht="39" customHeight="1">
       <c r="A29" s="10" t="s">
         <v>407</v>
       </c>
@@ -5715,7 +5097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:5">
+    <row r="30" spans="1:5" ht="39" customHeight="1">
       <c r="A30" s="10" t="s">
         <v>407</v>
       </c>
@@ -5732,7 +5114,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:5">
+    <row r="31" spans="1:5" ht="39" customHeight="1">
       <c r="A31" s="10" t="s">
         <v>407</v>
       </c>
@@ -5749,7 +5131,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:5">
+    <row r="32" spans="1:5" ht="39" customHeight="1">
       <c r="A32" s="10" t="s">
         <v>407</v>
       </c>
@@ -5766,7 +5148,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:5">
+    <row r="33" spans="1:5" ht="39" customHeight="1">
       <c r="A33" s="10" t="s">
         <v>407</v>
       </c>
@@ -5783,7 +5165,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:5">
+    <row r="34" spans="1:5" ht="39" customHeight="1">
       <c r="A34" s="10" t="s">
         <v>407</v>
       </c>
@@ -5800,7 +5182,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:5">
+    <row r="35" spans="1:5" ht="39" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>407</v>
       </c>
@@ -5817,7 +5199,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:5">
+    <row r="36" spans="1:5" ht="39" customHeight="1">
       <c r="A36" s="10" t="s">
         <v>407</v>
       </c>
@@ -5834,7 +5216,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:5">
+    <row r="37" spans="1:5" ht="39" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>407</v>
       </c>
@@ -5851,7 +5233,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:5">
+    <row r="38" spans="1:5" ht="39" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>423</v>
       </c>
@@ -5868,7 +5250,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:5">
+    <row r="39" spans="1:5" ht="39" customHeight="1">
       <c r="A39" s="10" t="s">
         <v>423</v>
       </c>
@@ -5885,7 +5267,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:5">
+    <row r="40" spans="1:5" ht="39" customHeight="1">
       <c r="A40" s="10" t="s">
         <v>423</v>
       </c>
@@ -5902,7 +5284,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:5">
+    <row r="41" spans="1:5" ht="39" customHeight="1">
       <c r="A41" s="10" t="s">
         <v>423</v>
       </c>
@@ -5919,7 +5301,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:5">
+    <row r="42" spans="1:5" ht="39" customHeight="1">
       <c r="A42" s="10" t="s">
         <v>423</v>
       </c>
@@ -5936,7 +5318,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:5">
+    <row r="43" spans="1:5" ht="39" customHeight="1">
       <c r="A43" s="10" t="s">
         <v>423</v>
       </c>
@@ -5953,7 +5335,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:5">
+    <row r="44" spans="1:5" ht="39" customHeight="1">
       <c r="A44" s="10" t="s">
         <v>423</v>
       </c>
@@ -5970,7 +5352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:5">
+    <row r="45" spans="1:5" ht="39" customHeight="1">
       <c r="A45" s="10" t="s">
         <v>423</v>
       </c>
@@ -5987,7 +5369,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:5">
+    <row r="46" spans="1:5" ht="39" customHeight="1">
       <c r="A46" s="10" t="s">
         <v>423</v>
       </c>
@@ -6004,7 +5386,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:5">
+    <row r="47" spans="1:5" ht="39" customHeight="1">
       <c r="A47" s="10" t="s">
         <v>423</v>
       </c>
@@ -6021,7 +5403,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:5">
+    <row r="48" spans="1:5" ht="39" customHeight="1">
       <c r="A48" s="10" t="s">
         <v>423</v>
       </c>
@@ -6038,7 +5420,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:5">
+    <row r="49" spans="1:5" ht="39" customHeight="1">
       <c r="A49" s="10" t="s">
         <v>423</v>
       </c>
@@ -6055,7 +5437,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:5">
+    <row r="50" spans="1:5" ht="39" customHeight="1">
       <c r="A50" s="10" t="s">
         <v>423</v>
       </c>
@@ -6072,7 +5454,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:5">
+    <row r="51" spans="1:5" ht="39" customHeight="1">
       <c r="A51" s="10" t="s">
         <v>423</v>
       </c>
@@ -6089,7 +5471,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:5">
+    <row r="52" spans="1:5" ht="39" customHeight="1">
       <c r="A52" s="10" t="s">
         <v>423</v>
       </c>
@@ -6106,7 +5488,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:5">
+    <row r="53" spans="1:5" ht="39" customHeight="1">
       <c r="A53" s="10" t="s">
         <v>423</v>
       </c>
@@ -6123,7 +5505,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:5">
+    <row r="54" spans="1:5" ht="39" customHeight="1">
       <c r="A54" s="10" t="s">
         <v>423</v>
       </c>
@@ -6140,7 +5522,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:5">
+    <row r="55" spans="1:5" ht="39" customHeight="1">
       <c r="A55" s="10" t="s">
         <v>423</v>
       </c>
@@ -6157,7 +5539,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:5">
+    <row r="56" spans="1:5" ht="39" customHeight="1">
       <c r="A56" s="10" t="s">
         <v>423</v>
       </c>
@@ -6174,7 +5556,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:5">
+    <row r="57" spans="1:5" ht="39" customHeight="1">
       <c r="A57" s="10" t="s">
         <v>423</v>
       </c>
@@ -6191,7 +5573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:5">
+    <row r="58" spans="1:5" ht="39" customHeight="1">
       <c r="A58" s="10" t="s">
         <v>423</v>
       </c>
@@ -6208,7 +5590,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:5">
+    <row r="59" spans="1:5" ht="39" customHeight="1">
       <c r="A59" s="10" t="s">
         <v>423</v>
       </c>
@@ -6225,7 +5607,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:5">
+    <row r="60" spans="1:5" ht="39" customHeight="1">
       <c r="A60" s="10" t="s">
         <v>423</v>
       </c>
@@ -6242,7 +5624,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:5">
+    <row r="61" spans="1:5" ht="39" customHeight="1">
       <c r="A61" s="10" t="s">
         <v>423</v>
       </c>
@@ -6259,7 +5641,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:5">
+    <row r="62" spans="1:5" ht="39" customHeight="1">
       <c r="A62" s="10" t="s">
         <v>423</v>
       </c>
@@ -6276,7 +5658,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:5">
+    <row r="63" spans="1:5" ht="39" customHeight="1">
       <c r="A63" s="10" t="s">
         <v>423</v>
       </c>
@@ -6293,7 +5675,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:5">
+    <row r="64" spans="1:5" ht="39" customHeight="1">
       <c r="A64" s="10" t="s">
         <v>423</v>
       </c>
@@ -6310,7 +5692,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:5">
+    <row r="65" spans="1:5" ht="39" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>423</v>
       </c>
@@ -6327,7 +5709,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:5">
+    <row r="66" spans="1:5" ht="39" customHeight="1">
       <c r="A66" s="10" t="s">
         <v>423</v>
       </c>
@@ -6344,7 +5726,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:5">
+    <row r="67" spans="1:5" ht="39" customHeight="1">
       <c r="A67" s="10" t="s">
         <v>423</v>
       </c>
@@ -6361,7 +5743,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:5">
+    <row r="68" spans="1:5" ht="39" customHeight="1">
       <c r="A68" s="10" t="s">
         <v>423</v>
       </c>
@@ -6378,7 +5760,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:5">
+    <row r="69" spans="1:5" ht="39" customHeight="1">
       <c r="A69" s="10" t="s">
         <v>423</v>
       </c>
@@ -6395,7 +5777,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:5">
+    <row r="70" spans="1:5" ht="39" customHeight="1">
       <c r="A70" s="10" t="s">
         <v>423</v>
       </c>
@@ -6412,7 +5794,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:5">
+    <row r="71" spans="1:5" ht="39" customHeight="1">
       <c r="A71" s="10" t="s">
         <v>423</v>
       </c>
@@ -6429,7 +5811,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:5">
+    <row r="72" spans="1:5" ht="39" customHeight="1">
       <c r="A72" s="10" t="s">
         <v>423</v>
       </c>
@@ -6446,7 +5828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:5">
+    <row r="73" spans="1:5" ht="39" customHeight="1">
       <c r="A73" s="10" t="s">
         <v>423</v>
       </c>
@@ -6463,7 +5845,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:5">
+    <row r="74" spans="1:5" ht="39" customHeight="1">
       <c r="A74" s="10" t="s">
         <v>423</v>
       </c>
@@ -6480,7 +5862,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:5">
+    <row r="75" spans="1:5" ht="39" customHeight="1">
       <c r="A75" s="10" t="s">
         <v>423</v>
       </c>
@@ -6497,7 +5879,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:5">
+    <row r="76" spans="1:5" ht="39" customHeight="1">
       <c r="A76" s="10" t="s">
         <v>423</v>
       </c>
@@ -6514,7 +5896,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:5">
+    <row r="77" spans="1:5" ht="39" customHeight="1">
       <c r="A77" s="10" t="s">
         <v>423</v>
       </c>
@@ -6531,7 +5913,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:5">
+    <row r="78" spans="1:5" ht="39" customHeight="1">
       <c r="A78" s="10" t="s">
         <v>423</v>
       </c>
@@ -6548,7 +5930,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:5">
+    <row r="79" spans="1:5" ht="39" customHeight="1">
       <c r="A79" s="10" t="s">
         <v>423</v>
       </c>
@@ -6565,7 +5947,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:5">
+    <row r="80" spans="1:5" ht="39" customHeight="1">
       <c r="A80" s="10" t="s">
         <v>423</v>
       </c>
@@ -6582,7 +5964,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="1:5">
+    <row r="81" spans="1:5" ht="39" customHeight="1">
       <c r="A81" s="10" t="s">
         <v>423</v>
       </c>
@@ -6599,7 +5981,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="1:5">
+    <row r="82" spans="1:5" ht="39" customHeight="1">
       <c r="A82" s="10" t="s">
         <v>423</v>
       </c>
@@ -6616,7 +5998,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="1:5">
+    <row r="83" spans="1:5" ht="39" customHeight="1">
       <c r="A83" s="10" t="s">
         <v>423</v>
       </c>
@@ -6633,7 +6015,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:5">
+    <row r="84" spans="1:5" ht="39" customHeight="1">
       <c r="A84" s="10" t="s">
         <v>423</v>
       </c>
@@ -6650,7 +6032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="1:5">
+    <row r="85" spans="1:5" ht="39" customHeight="1">
       <c r="A85" s="10" t="s">
         <v>423</v>
       </c>
@@ -6667,7 +6049,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="1:5">
+    <row r="86" spans="1:5" ht="39" customHeight="1">
       <c r="A86" s="10" t="s">
         <v>423</v>
       </c>
@@ -6684,7 +6066,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="1:5">
+    <row r="87" spans="1:5" ht="39" customHeight="1">
       <c r="A87" s="10" t="s">
         <v>423</v>
       </c>
@@ -6701,7 +6083,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:5">
+    <row r="88" spans="1:5" ht="39" customHeight="1">
       <c r="A88" s="10" t="s">
         <v>423</v>
       </c>
@@ -6718,7 +6100,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:5">
+    <row r="89" spans="1:5" ht="39" customHeight="1">
       <c r="A89" s="10" t="s">
         <v>423</v>
       </c>
@@ -6735,7 +6117,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:5">
+    <row r="90" spans="1:5" ht="39" customHeight="1">
       <c r="A90" s="10" t="s">
         <v>423</v>
       </c>
@@ -6752,7 +6134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:5">
+    <row r="91" spans="1:5" ht="39" customHeight="1">
       <c r="A91" s="10" t="s">
         <v>423</v>
       </c>
@@ -6769,7 +6151,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:5">
+    <row r="92" spans="1:5" ht="39" customHeight="1">
       <c r="A92" s="10" t="s">
         <v>423</v>
       </c>
@@ -6786,41 +6168,29 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:5">
+    <row r="93" spans="1:5" ht="39" customHeight="1">
       <c r="A93" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B93" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
       <c r="D93" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="1:5">
+        <v>560</v>
+      </c>
+      <c r="E93" s="10"/>
+    </row>
+    <row r="94" spans="1:5" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B94" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
       <c r="D94" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="1:5">
+        <v>561</v>
+      </c>
+      <c r="E94" s="10"/>
+    </row>
+    <row r="95" spans="1:5" ht="39" customHeight="1">
       <c r="A95" s="10" t="s">
         <v>477</v>
       </c>
@@ -6831,13 +6201,13 @@
         <v>46</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:5">
+    <row r="96" spans="1:5" ht="39" customHeight="1">
       <c r="A96" s="10" t="s">
         <v>477</v>
       </c>
@@ -6848,13 +6218,13 @@
         <v>46</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:5">
+    <row r="97" spans="1:5" ht="39" customHeight="1">
       <c r="A97" s="10" t="s">
         <v>477</v>
       </c>
@@ -6865,13 +6235,13 @@
         <v>46</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="1:5">
+    <row r="98" spans="1:5" ht="39" customHeight="1">
       <c r="A98" s="10" t="s">
         <v>477</v>
       </c>
@@ -6882,13 +6252,13 @@
         <v>46</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="1:5">
+    <row r="99" spans="1:5" ht="39" customHeight="1">
       <c r="A99" s="10" t="s">
         <v>477</v>
       </c>
@@ -6899,13 +6269,13 @@
         <v>46</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:5">
+    <row r="100" spans="1:5" ht="39" customHeight="1">
       <c r="A100" s="10" t="s">
         <v>477</v>
       </c>
@@ -6916,13 +6286,13 @@
         <v>46</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:5">
+    <row r="101" spans="1:5" ht="39" customHeight="1">
       <c r="A101" s="10" t="s">
         <v>477</v>
       </c>
@@ -6933,13 +6303,13 @@
         <v>46</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:5">
+    <row r="102" spans="1:5" ht="39" customHeight="1">
       <c r="A102" s="10" t="s">
         <v>477</v>
       </c>
@@ -6950,13 +6320,13 @@
         <v>46</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>487</v>
+        <v>562</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:5">
+    <row r="103" spans="1:5" ht="39" customHeight="1">
       <c r="A103" s="10" t="s">
         <v>477</v>
       </c>
@@ -6967,13 +6337,13 @@
         <v>46</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:5">
+    <row r="104" spans="1:5" ht="39" customHeight="1">
       <c r="A104" s="10" t="s">
         <v>477</v>
       </c>
@@ -6984,13 +6354,13 @@
         <v>46</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:5">
+    <row r="105" spans="1:5" ht="39" customHeight="1">
       <c r="A105" s="10" t="s">
         <v>477</v>
       </c>
@@ -7001,13 +6371,13 @@
         <v>46</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="1:5">
+    <row r="106" spans="1:5" ht="39" customHeight="1">
       <c r="A106" s="10" t="s">
         <v>477</v>
       </c>
@@ -7018,13 +6388,13 @@
         <v>46</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>491</v>
+        <v>563</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:5">
+    <row r="107" spans="1:5" ht="39" customHeight="1">
       <c r="A107" s="10" t="s">
         <v>477</v>
       </c>
@@ -7035,13 +6405,13 @@
         <v>46</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>492</v>
+        <v>564</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:5">
+    <row r="108" spans="1:5" ht="39" customHeight="1">
       <c r="A108" s="10" t="s">
         <v>477</v>
       </c>
@@ -7052,13 +6422,13 @@
         <v>46</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:5">
+    <row r="109" spans="1:5" ht="39" customHeight="1">
       <c r="A109" s="10" t="s">
         <v>477</v>
       </c>
@@ -7069,13 +6439,13 @@
         <v>46</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:5">
+    <row r="110" spans="1:5" ht="39" customHeight="1">
       <c r="A110" s="10" t="s">
         <v>477</v>
       </c>
@@ -7086,13 +6456,13 @@
         <v>46</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:5">
+    <row r="111" spans="1:5" ht="39" customHeight="1">
       <c r="A111" s="10" t="s">
         <v>477</v>
       </c>
@@ -7103,13 +6473,13 @@
         <v>46</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:5">
+    <row r="112" spans="1:5" ht="39" customHeight="1">
       <c r="A112" s="10" t="s">
         <v>477</v>
       </c>
@@ -7120,13 +6490,13 @@
         <v>46</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="1:5">
+    <row r="113" spans="1:5" ht="39" customHeight="1">
       <c r="A113" s="10" t="s">
         <v>477</v>
       </c>
@@ -7137,13 +6507,13 @@
         <v>46</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="1:5">
+    <row r="114" spans="1:5" ht="39" customHeight="1">
       <c r="A114" s="10" t="s">
         <v>477</v>
       </c>
@@ -7154,185 +6524,202 @@
         <v>46</v>
       </c>
       <c r="D114" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="39" customHeight="1">
+      <c r="A115" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="39" customHeight="1">
+      <c r="A116" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D116" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="39" customHeight="1">
+      <c r="A117" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="39" customHeight="1">
+      <c r="A118" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="39" customHeight="1">
+      <c r="A119" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D119" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="E114" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="1:5">
-      <c r="A115" s="10" t="s">
+      <c r="E119" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="39" customHeight="1">
+      <c r="A120" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D120" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="B115" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D115" s="10" t="s">
+      <c r="E120" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="39" customHeight="1">
+      <c r="A121" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D121" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="E115" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="1:5">
-      <c r="A116" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D116" s="10" t="s">
+      <c r="E121" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="39" customHeight="1">
+      <c r="A122" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D122" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="E116" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="1:5">
-      <c r="A117" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D117" s="10" t="s">
+      <c r="E122" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="39" customHeight="1">
+      <c r="A123" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D123" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="E117" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="1:5">
-      <c r="A118" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D118" s="10" t="s">
+      <c r="E123" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="39" customHeight="1">
+      <c r="A124" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D124" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="E118" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="1:5">
-      <c r="A119" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D119" s="10" t="s">
+      <c r="E124" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="39" customHeight="1">
+      <c r="A125" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="E119" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="1:5">
-      <c r="A120" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="1:5">
-      <c r="A121" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" spans="1:5">
-      <c r="A122" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" spans="1:5">
-      <c r="A123" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="1:5">
-      <c r="A124" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="E124" s="10" t="s">
+      <c r="E125" s="10" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -7340,10 +6727,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="18" style="4" customWidth="1"/>
     <col min="3" max="3" width="42" style="4" customWidth="1"/>
@@ -7356,73 +6742,73 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="27.6">
       <c r="A2" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.6">
+      <c r="A3" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="D2" s="6" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="41.4">
+      <c r="A4" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="3" ht="27.6" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="4" ht="41.4" spans="1:4">
-      <c r="A4" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
@@ -7431,10 +6817,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -7443,10 +6829,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
@@ -7455,40 +6841,40 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6" t="s">
@@ -7497,10 +6883,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>529</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>534</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6" t="s">
@@ -7509,10 +6895,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6" t="s">
@@ -7521,40 +6907,40 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
@@ -7563,10 +6949,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6" t="s">
@@ -7575,10 +6961,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
@@ -7587,10 +6973,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
@@ -7599,10 +6985,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
@@ -7611,10 +6997,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
@@ -7623,10 +7009,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
@@ -7635,10 +7021,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6" t="s">
@@ -7647,10 +7033,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
@@ -7659,10 +7045,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
@@ -7671,10 +7057,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
@@ -7683,10 +7069,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6" t="s">
@@ -7695,10 +7081,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6" t="s">
@@ -7707,10 +7093,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6" t="s">
@@ -7719,10 +7105,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
@@ -7731,10 +7117,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6" t="s">
@@ -7742,8 +7128,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -7751,10 +7137,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -7787,20 +7172,19 @@
         <v>238</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
@@ -7808,54 +7192,54 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8">
+      <c r="A2" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8">
+      <c r="A3" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="3" ht="27.6" spans="1:2">
-      <c r="A3" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8">
+      <c r="A5" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8">
+      <c r="A6" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" ht="27.6" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>564</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D86604-9819-4064-8841-92024B21B4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB02F6F9-B150-4A5D-A44D-68EC24FA8801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="567">
   <si>
     <t>date</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at Hebei University (HBU).</t>
-  </si>
-  <si>
-    <t>http://dm-dut.github.io/images/hbu.jpg</t>
   </si>
   <si>
     <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at Nanjing University of Information Science and Technology (NUIST).</t>
@@ -1742,6 +1739,14 @@
   </si>
   <si>
     <t xml:space="preserve"> IEEE International Conference on Technology Management, Operations and Decisions (IEEE ICTMOD, 2018, 2026)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dm-dut.github.io/images/HBU260611.jpg</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dm-dut.github.io/images/XIDIAN251031.jpg</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1749,6 +1754,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -1859,19 +1867,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1880,6 +1888,67 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="31">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1974,62 +2043,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <fill>
@@ -2259,11 +2272,11 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E78">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="1">
       <calculatedColumnFormula>IF(ROW()-1&lt;11,"yes","no")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2300,11 +2313,11 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E125">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2313,10 +2326,10 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="GroupTable" displayName="GroupTable" ref="A1:D33">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2499,1375 +2512,1375 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>46184</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="18" t="str">
+      <c r="D2" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="E2" s="17" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A3" s="16">
+      <c r="A3" s="18">
         <v>46177</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="18" t="str">
+      <c r="E3" s="17" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A4" s="16">
+      <c r="A4" s="18">
         <v>46168</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18" t="str">
+      <c r="D4" s="16"/>
+      <c r="E4" s="17" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="18" t="str">
+      <c r="E5" s="17" t="str">
         <f t="shared" ref="E5:E14" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="18" t="str">
+      <c r="E6" s="17" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="18" t="str">
+      <c r="E7" s="17" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="18" t="str">
+      <c r="E8" s="17" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="18" t="str">
+      <c r="E9" s="17" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="18" t="str">
+      <c r="E10" s="17" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="18" t="str">
+      <c r="E11" s="17" t="str">
         <f t="shared" si="0"/>
         <v>yes</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="18" t="str">
+      <c r="E12" s="17" t="str">
         <f t="shared" si="0"/>
         <v>no</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="18" t="str">
+      <c r="E13" s="17" t="str">
         <f t="shared" si="0"/>
         <v>no</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="18" t="str">
+      <c r="E14" s="17" t="str">
         <f t="shared" si="0"/>
         <v>no</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="18" t="str">
+      <c r="D15" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="17" t="str">
         <f t="shared" ref="E15:E24" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="18" t="str">
+      <c r="E16" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="18" t="str">
+      <c r="E17" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="18" t="str">
+      <c r="E18" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="D19" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="18" t="str">
+      <c r="E19" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A20" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="18" t="str">
+      <c r="E20" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="18" t="str">
+      <c r="E21" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="18" t="str">
+      <c r="E22" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="18" t="str">
+      <c r="D23" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="E23" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A24" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="18" t="str">
+      <c r="E24" s="17" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="17" t="s">
+      <c r="D25" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="18" t="str">
+      <c r="E25" s="17" t="str">
         <f t="shared" ref="E25:E34" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="18" t="str">
+      <c r="D26" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="17" t="s">
+      <c r="D27" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="18" t="str">
+      <c r="E27" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="17" t="s">
+      <c r="D28" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="18" t="str">
+      <c r="E28" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" s="18" t="str">
+      <c r="D29" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="17" t="s">
+      <c r="D30" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="18" t="str">
+      <c r="E30" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="17" t="s">
+      <c r="D31" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="18" t="str">
+      <c r="E31" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="18" t="str">
+      <c r="D32" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="18" t="str">
+      <c r="E33" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="17" t="s">
+      <c r="D34" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="18" t="str">
+      <c r="E34" s="17" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" s="18" t="str">
+      <c r="E35" s="17" t="str">
         <f t="shared" ref="E35:E52" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="17" t="s">
+      <c r="D36" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="18" t="str">
+      <c r="E36" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" s="18" t="str">
+      <c r="E37" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="17" t="s">
+      <c r="D38" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" s="18" t="str">
+      <c r="E38" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="18" t="str">
+      <c r="E39" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A40" s="20">
+      <c r="A40" s="18">
         <v>45597</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E40" s="18" t="str">
+      <c r="E40" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A41" s="20">
+      <c r="A41" s="18">
         <v>45593</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="18" t="str">
+      <c r="C41" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A42" s="20">
+      <c r="A42" s="18">
         <v>45585</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D42" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" s="18" t="str">
+      <c r="E42" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A43" s="20">
+      <c r="A43" s="18">
         <v>45584</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="18" t="str">
+      <c r="E43" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A44" s="20">
+      <c r="A44" s="18">
         <v>45583</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D44" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="18" t="str">
+      <c r="E44" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E45" s="18" t="str">
+      <c r="D45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A46" s="20">
+      <c r="A46" s="18">
         <v>45580</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="18" t="str">
+      <c r="C46" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="16"/>
+      <c r="E46" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B47" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="17" t="s">
+      <c r="D47" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" s="18" t="str">
+      <c r="E47" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="17" t="s">
+      <c r="D48" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="18" t="str">
+      <c r="E48" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="C49" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E49" s="18" t="str">
+      <c r="D49" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A50" s="20">
+      <c r="A50" s="18">
         <v>45514</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D50" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="18" t="str">
+      <c r="E50" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B51" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="17" t="s">
+      <c r="D51" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="18" t="str">
+      <c r="E51" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A52" s="20">
+      <c r="A52" s="18">
         <v>45432</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" s="18" t="str">
+      <c r="E52" s="17" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B53" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="17" t="s">
+      <c r="D53" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" s="18" t="str">
+      <c r="E53" s="17" t="str">
         <f t="shared" ref="E53:E66" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="17" t="s">
+      <c r="D54" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" s="18" t="str">
+      <c r="E54" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="B55" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="17" t="s">
+      <c r="D55" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D55" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55" s="18" t="str">
+      <c r="E55" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="17" t="s">
+      <c r="D56" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D56" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E56" s="18" t="str">
+      <c r="E56" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B57" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="17" t="s">
+      <c r="D57" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D57" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" s="18" t="str">
+      <c r="E57" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A58" s="20">
+      <c r="A58" s="18">
         <v>45264</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D58" s="17"/>
-      <c r="E58" s="18" t="str">
+      <c r="C58" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D58" s="16"/>
+      <c r="E58" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="17" t="s">
+      <c r="D59" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="D59" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E59" s="18" t="str">
+      <c r="E59" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="B60" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" s="18" t="str">
+      <c r="D60" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="D61" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E61" s="18" t="str">
+      <c r="D61" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A62" s="20">
+      <c r="A62" s="18">
         <v>45118</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D62" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="D62" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E62" s="18" t="str">
+      <c r="E62" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B63" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="17" t="s">
+      <c r="D63" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="D63" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" s="18" t="str">
+      <c r="E63" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B64" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="17" t="s">
+      <c r="D64" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="E64" s="18" t="str">
+      <c r="E64" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A65" s="20">
+      <c r="A65" s="18">
         <v>45023</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C65" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D65" s="17"/>
-      <c r="E65" s="18" t="str">
+      <c r="C65" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D65" s="16"/>
+      <c r="E65" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A66" s="20">
+      <c r="A66" s="18">
         <v>45006</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D66" s="17"/>
-      <c r="E66" s="18" t="str">
+      <c r="C66" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D66" s="16"/>
+      <c r="E66" s="17" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B67" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="17" t="s">
+      <c r="D67" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D67" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="E67" s="18" t="str">
+      <c r="E67" s="17" t="str">
         <f t="shared" ref="E67:E78" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B68" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="17" t="s">
+      <c r="D68" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="E68" s="18" t="str">
+      <c r="E68" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B69" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="17" t="s">
+      <c r="D69" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D69" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="E69" s="18" t="str">
+      <c r="E69" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B70" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="17" t="s">
+      <c r="D70" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D70" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="E70" s="18" t="str">
+      <c r="E70" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A71" s="20">
+      <c r="A71" s="18">
         <v>44945</v>
       </c>
-      <c r="B71" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="17" t="s">
+      <c r="B71" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D71" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D71" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="E71" s="18" t="str">
+      <c r="E71" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B72" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="D72" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E72" s="18" t="str">
+      <c r="D72" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="17" t="s">
+      <c r="D73" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D73" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="E73" s="18" t="str">
+      <c r="E73" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B74" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E74" s="18" t="str">
+      <c r="D74" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E75" s="18" t="str">
+      <c r="D75" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B76" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="17" t="s">
+      <c r="D76" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="D76" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="E76" s="18" t="str">
+      <c r="E76" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="B77" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="17" t="s">
+      <c r="D77" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D77" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="E77" s="18" t="str">
+      <c r="E77" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B78" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="D78" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E78" s="18" t="str">
+      <c r="D78" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" s="17" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
@@ -3893,13 +3906,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="11" customFormat="1" ht="28.8">
@@ -3907,131 +3920,131 @@
         <v>2026</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.2">
       <c r="A5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8">
       <c r="A8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="43.2">
       <c r="A10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.2">
       <c r="A12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="28.8">
       <c r="A13" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -4056,531 +4069,531 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="57.6">
       <c r="A2" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="57.6">
       <c r="A3" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2">
       <c r="A4" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2">
       <c r="A5" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2">
       <c r="A6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
       <c r="A7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2">
       <c r="A8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2">
       <c r="A9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2">
       <c r="A10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.2">
       <c r="A11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2">
       <c r="A12" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="57.6">
       <c r="A13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.2">
       <c r="A14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="43.2">
       <c r="A15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8">
       <c r="A16" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8">
       <c r="A17" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="57.6">
       <c r="A18" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8">
       <c r="A19" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8">
       <c r="A20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.2">
       <c r="A21" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="43.2">
       <c r="A22" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="43.2">
       <c r="A23" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4609,2112 +4622,2112 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="39" customHeight="1">
       <c r="A2" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>360</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="39" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="39" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>365</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="39" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>368</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="39" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="39" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>372</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>374</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="39" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>376</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="39" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>379</v>
-      </c>
       <c r="D10" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="39" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>381</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="39" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>384</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="39" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>387</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="39" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>390</v>
-      </c>
       <c r="D14" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="39" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="39" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="39" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>394</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="39" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="D18" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="39" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>399</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="39" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C20" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>401</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1">
       <c r="A21" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>359</v>
-      </c>
       <c r="C21" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="39" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>406</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" customHeight="1">
       <c r="A23" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>408</v>
-      </c>
       <c r="E23" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="39" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="39" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="39" customHeight="1">
       <c r="A26" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="39" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="39" customHeight="1">
       <c r="A28" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="39" customHeight="1">
       <c r="A29" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="39" customHeight="1">
       <c r="A30" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="39" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="39" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="39" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="39" customHeight="1">
       <c r="A34" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="39" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="39" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="39" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="39" customHeight="1">
       <c r="A38" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>424</v>
-      </c>
       <c r="E38" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="39" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="39" customHeight="1">
       <c r="A40" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="39" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="39" customHeight="1">
       <c r="A42" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="39" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="39" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="39" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="39" customHeight="1">
       <c r="A46" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="39" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="39" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="39" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="39" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="39" customHeight="1">
       <c r="A51" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="39" customHeight="1">
       <c r="A52" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="39" customHeight="1">
       <c r="A53" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="39" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="39" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="39" customHeight="1">
       <c r="A56" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="39" customHeight="1">
       <c r="A57" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="39" customHeight="1">
       <c r="A58" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="39" customHeight="1">
       <c r="A59" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="39" customHeight="1">
       <c r="A60" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="39" customHeight="1">
       <c r="A61" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="39" customHeight="1">
       <c r="A62" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="39" customHeight="1">
       <c r="A63" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="39" customHeight="1">
       <c r="A64" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="39" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="39" customHeight="1">
       <c r="A66" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="39" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="39" customHeight="1">
       <c r="A68" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="39" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="39" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="39" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="39" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="39" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="39" customHeight="1">
       <c r="A74" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="39" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="39" customHeight="1">
       <c r="A76" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="39" customHeight="1">
       <c r="A77" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="39" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="39" customHeight="1">
       <c r="A79" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1">
       <c r="A80" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="39" customHeight="1">
       <c r="A81" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="39" customHeight="1">
       <c r="A82" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="39" customHeight="1">
       <c r="A83" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="39" customHeight="1">
       <c r="A84" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="39" customHeight="1">
       <c r="A85" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="39" customHeight="1">
       <c r="A86" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="39" customHeight="1">
       <c r="A87" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="39" customHeight="1">
       <c r="A88" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="39" customHeight="1">
       <c r="A89" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="39" customHeight="1">
       <c r="A90" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="39" customHeight="1">
       <c r="A91" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="39" customHeight="1">
       <c r="A92" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="39" customHeight="1">
       <c r="A93" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E93" s="10"/>
     </row>
     <row r="94" spans="1:5" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E94" s="10"/>
     </row>
     <row r="95" spans="1:5" ht="39" customHeight="1">
       <c r="A95" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D95" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>478</v>
-      </c>
       <c r="E95" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="39" customHeight="1">
       <c r="A96" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="39" customHeight="1">
       <c r="A97" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="39" customHeight="1">
       <c r="A98" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="39" customHeight="1">
       <c r="A99" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="39" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="39" customHeight="1">
       <c r="A101" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="39" customHeight="1">
       <c r="A102" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="39" customHeight="1">
       <c r="A103" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="39" customHeight="1">
       <c r="A104" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="39" customHeight="1">
       <c r="A105" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="39" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="39" customHeight="1">
       <c r="A107" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="39" customHeight="1">
       <c r="A108" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="39" customHeight="1">
       <c r="A109" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="39" customHeight="1">
       <c r="A110" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="39" customHeight="1">
       <c r="A111" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="39" customHeight="1">
       <c r="A112" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="39" customHeight="1">
       <c r="A113" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="39" customHeight="1">
       <c r="A114" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="39" customHeight="1">
       <c r="A115" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="39" customHeight="1">
       <c r="A116" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D116" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="B116" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D116" s="10" t="s">
-        <v>496</v>
-      </c>
       <c r="E116" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="39" customHeight="1">
       <c r="A117" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="39" customHeight="1">
       <c r="A118" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="39" customHeight="1">
       <c r="A119" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="39" customHeight="1">
       <c r="A120" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="39" customHeight="1">
       <c r="A121" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="39" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="39" customHeight="1">
       <c r="A123" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="39" customHeight="1">
       <c r="A124" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="39" customHeight="1">
       <c r="A125" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -6742,10 +6755,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
@@ -6753,378 +6766,378 @@
     </row>
     <row r="2" spans="1:4" ht="27.6">
       <c r="A2" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.6">
       <c r="A3" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>514</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="41.4">
       <c r="A4" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>517</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>519</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>520</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>525</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -7154,25 +7167,25 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="E1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -7192,50 +7205,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8">
       <c r="A2" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.8">
       <c r="A3" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28.8">
       <c r="A5" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8">
       <c r="A6" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB02F6F9-B150-4A5D-A44D-68EC24FA8801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D999F0-9297-4441-9AF9-50BEBA667D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="569">
   <si>
     <t>date</t>
   </si>
@@ -1748,6 +1748,13 @@
   <si>
     <t>http://dm-dut.github.io/images/XIDIAN251031.jpg</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was invited to join in the editorial board of Decision Making and Analysis as an editorial board member.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ojs.luminescience.cn/DMA/about/editorialTeam</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1762,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1873,7 +1880,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1888,67 +1895,6 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="31">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2043,6 +1989,67 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2270,13 +2277,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E79">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="content" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="link" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="show_on_home" dataDxfId="9">
       <calculatedColumnFormula>IF(ROW()-1&lt;11,"yes","no")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2313,11 +2320,11 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E125">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="organization" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="period" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2326,10 +2333,10 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="GroupTable" displayName="GroupTable" ref="A1:D33">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="category" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="name" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="note" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="link" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2484,7 +2491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.45" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="13" customWidth="1"/>
@@ -2513,34 +2520,34 @@
     </row>
     <row r="2" spans="1:5" ht="54.45" customHeight="1">
       <c r="A2" s="18">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>6</v>
+        <v>567</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E2" s="17" t="str">
-        <f>IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" ref="E2" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54.45" customHeight="1">
       <c r="A3" s="18">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>565</v>
       </c>
       <c r="E3" s="17" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2549,143 +2556,143 @@
     </row>
     <row r="4" spans="1:5" ht="54.45" customHeight="1">
       <c r="A4" s="18">
-        <v>46168</v>
+        <v>46177</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="16"/>
+        <v>7</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="17" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>11</v>
+      <c r="A5" s="18">
+        <v>46168</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>14</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D5" s="16"/>
       <c r="E5" s="17" t="str">
-        <f t="shared" ref="E5:E14" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.45" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="E6" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E6:E15" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.45" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.45" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>21</v>
       </c>
       <c r="E8" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.45" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="E9" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.45" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="E10" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="54.45" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E11" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
@@ -2697,139 +2704,139 @@
         <v>5</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="54.45" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54.45" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E14" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="54.45" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E15" s="17" t="str">
-        <f t="shared" ref="E15:E24" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="54.45" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E16" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E16:E25" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54.45" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E17" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.45" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E18" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54.45" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E19" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
@@ -2841,67 +2848,67 @@
         <v>5</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="54.45" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E21" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54.45" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E22" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="54.45" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>566</v>
+        <v>65</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="E23" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
@@ -2913,975 +2920,993 @@
         <v>5</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>566</v>
       </c>
       <c r="E24" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="54.45" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E25" s="17" t="str">
-        <f t="shared" ref="E25:E34" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="54.45" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E26" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E26:E35" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54.45" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E27" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54.45" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E28" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54.45" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="E29" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="54.45" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E30" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="54.45" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E31" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="54.45" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E32" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="54.45" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E33" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="54.45" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E34" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="54.45" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E35" s="17" t="str">
-        <f t="shared" ref="E35:E52" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="54.45" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E36" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E36:E53" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="54.45" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E37" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="54.45" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E38" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="54.45" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A40" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D40" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A40" s="18">
-        <v>45597</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>112</v>
-      </c>
       <c r="E40" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="54.45" customHeight="1">
       <c r="A41" s="18">
-        <v>45593</v>
+        <v>45597</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="16"/>
+        <v>111</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>112</v>
+      </c>
       <c r="E41" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="54.45" customHeight="1">
       <c r="A42" s="18">
-        <v>45585</v>
+        <v>45593</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>115</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D42" s="16"/>
       <c r="E42" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="54.45" customHeight="1">
       <c r="A43" s="18">
-        <v>45584</v>
+        <v>45585</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E43" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="54.45" customHeight="1">
       <c r="A44" s="18">
-        <v>45583</v>
+        <v>45584</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E44" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A45" s="18">
+        <v>45583</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="17" t="str">
-        <f t="shared" si="3"/>
+      <c r="E45" s="17" t="str">
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A45" s="18" t="s">
+    <row r="46" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A46" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B46" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C46" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D46" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="17" t="str">
-        <f t="shared" si="3"/>
+      <c r="E46" s="17" t="str">
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A46" s="18">
+    <row r="47" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A47" s="18">
         <v>45580</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B47" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A47" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>125</v>
-      </c>
+      <c r="D47" s="16"/>
       <c r="E47" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="54.45" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E48" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="54.45" customHeight="1">
       <c r="A49" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A50" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B50" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C50" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="17" t="str">
-        <f t="shared" si="3"/>
+      <c r="D50" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="17" t="str">
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A50" s="18">
+    <row r="51" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A51" s="18">
         <v>45514</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B51" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C51" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D51" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E50" s="17" t="str">
-        <f t="shared" si="3"/>
+      <c r="E51" s="17" t="str">
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A51" s="18" t="s">
+    <row r="52" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A52" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B52" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="E51" s="17" t="str">
-        <f t="shared" si="3"/>
+      <c r="E52" s="17" t="str">
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A52" s="18">
+    <row r="53" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A53" s="18">
         <v>45432</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B53" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="D53" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="E52" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A53" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>141</v>
-      </c>
       <c r="E53" s="17" t="str">
-        <f t="shared" ref="E53:E66" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="54.45" customHeight="1">
       <c r="A54" s="18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E54" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E54:E67" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="54.45" customHeight="1">
       <c r="A55" s="18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E55" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54.45" customHeight="1">
       <c r="A56" s="18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E56" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="54.45" customHeight="1">
       <c r="A57" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A58" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B58" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C58" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D58" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E57" s="17" t="str">
-        <f t="shared" si="4"/>
+      <c r="E58" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A58" s="18">
+    <row r="59" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A59" s="18">
         <v>45264</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B59" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A59" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>157</v>
-      </c>
+      <c r="D59" s="16"/>
       <c r="E59" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="54.45" customHeight="1">
       <c r="A60" s="18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="E60" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="54.45" customHeight="1">
       <c r="A61" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A62" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B62" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C62" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="17" t="str">
-        <f t="shared" si="4"/>
+      <c r="D62" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="17" t="str">
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A62" s="18">
+    <row r="63" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A63" s="18">
         <v>45118</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B63" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C63" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D63" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E62" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A63" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>166</v>
-      </c>
       <c r="E63" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="54.45" customHeight="1">
       <c r="A64" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E64" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A65" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B65" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C65" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D65" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E64" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A65" s="18">
-        <v>45023</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D65" s="16"/>
       <c r="E65" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="54.45" customHeight="1">
       <c r="A66" s="18">
-        <v>45006</v>
+        <v>45023</v>
       </c>
       <c r="B66" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A67" s="18" t="s">
-        <v>172</v>
+      <c r="A67" s="18">
+        <v>45006</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>174</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="D67" s="16"/>
       <c r="E67" s="17" t="str">
-        <f t="shared" ref="E67:E78" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="54.45" customHeight="1">
       <c r="A68" s="18" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B68" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E68" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E68:E79" si="6">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="54.45" customHeight="1">
       <c r="A69" s="18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B69" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E69" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="54.45" customHeight="1">
       <c r="A70" s="18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E70" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A71" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="D71" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E70" s="17" t="str">
-        <f t="shared" si="5"/>
+      <c r="E71" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A71" s="18">
+    <row r="72" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A72" s="18">
         <v>44945</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="E71" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>no</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A72" s="18" t="s">
-        <v>186</v>
       </c>
       <c r="B72" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="E72" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="54.45" customHeight="1">
       <c r="A73" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="E73" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="54.45" customHeight="1">
       <c r="A74" s="18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B74" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="E74" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="54.45" customHeight="1">
       <c r="A75" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D75" s="16" t="s">
         <v>45</v>
       </c>
       <c r="E75" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="54.45" customHeight="1">
       <c r="A76" s="18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="E76" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="54.45" customHeight="1">
       <c r="A77" s="18" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B77" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E77" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="54.45" customHeight="1">
       <c r="A78" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E78" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A79" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B79" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C79" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="D78" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E78" s="17" t="str">
-        <f t="shared" si="5"/>
+      <c r="D79" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D999F0-9297-4441-9AF9-50BEBA667D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF716207-4EE3-4222-A417-CE10435ABB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="570">
   <si>
     <t>date</t>
   </si>
@@ -1755,6 +1755,10 @@
   </si>
   <si>
     <t>https://ojs.luminescience.cn/DMA/about/editorialTeam</t>
+  </si>
+  <si>
+    <t>Decision Making and Analysis</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2318,7 +2322,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E126">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="7"/>
@@ -4632,7 +4636,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="8" customWidth="1"/>
@@ -4973,30 +4977,28 @@
         <v>379</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>400</v>
+        <v>569</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>401</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>357</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="39" customHeight="1">
@@ -5004,30 +5006,30 @@
         <v>357</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>45</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>406</v>
+        <v>357</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>45</v>
+        <v>404</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>45</v>
+        <v>405</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>45</v>
@@ -5044,7 +5046,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>45</v>
@@ -5061,7 +5063,7 @@
         <v>45</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>45</v>
@@ -5078,7 +5080,7 @@
         <v>45</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>45</v>
@@ -5095,7 +5097,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>45</v>
@@ -5112,7 +5114,7 @@
         <v>45</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>45</v>
@@ -5129,7 +5131,7 @@
         <v>45</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>45</v>
@@ -5146,7 +5148,7 @@
         <v>45</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>45</v>
@@ -5163,7 +5165,7 @@
         <v>45</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>45</v>
@@ -5180,7 +5182,7 @@
         <v>45</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>45</v>
@@ -5197,7 +5199,7 @@
         <v>45</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>45</v>
@@ -5214,7 +5216,7 @@
         <v>45</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>45</v>
@@ -5231,7 +5233,7 @@
         <v>45</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>45</v>
@@ -5248,7 +5250,7 @@
         <v>45</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>45</v>
@@ -5265,7 +5267,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>45</v>
@@ -5273,7 +5275,7 @@
     </row>
     <row r="38" spans="1:5" ht="39" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>45</v>
@@ -5282,7 +5284,7 @@
         <v>45</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>45</v>
@@ -5299,7 +5301,7 @@
         <v>45</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>45</v>
@@ -5316,7 +5318,7 @@
         <v>45</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>45</v>
@@ -5333,7 +5335,7 @@
         <v>45</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>45</v>
@@ -5350,7 +5352,7 @@
         <v>45</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>426</v>
+        <v>389</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>45</v>
@@ -5367,7 +5369,7 @@
         <v>45</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>45</v>
@@ -5384,7 +5386,7 @@
         <v>45</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>45</v>
@@ -5401,7 +5403,7 @@
         <v>45</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>45</v>
@@ -5418,7 +5420,7 @@
         <v>45</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>45</v>
@@ -5435,7 +5437,7 @@
         <v>45</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>45</v>
@@ -5452,7 +5454,7 @@
         <v>45</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>45</v>
@@ -5469,7 +5471,7 @@
         <v>45</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>45</v>
@@ -5486,7 +5488,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>45</v>
@@ -5503,7 +5505,7 @@
         <v>45</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>45</v>
@@ -5520,7 +5522,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>45</v>
@@ -5537,7 +5539,7 @@
         <v>45</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>45</v>
@@ -5554,7 +5556,7 @@
         <v>45</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>45</v>
@@ -5571,7 +5573,7 @@
         <v>45</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>45</v>
@@ -5588,7 +5590,7 @@
         <v>45</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>45</v>
@@ -5605,7 +5607,7 @@
         <v>45</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>45</v>
@@ -5622,7 +5624,7 @@
         <v>45</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>45</v>
@@ -5639,7 +5641,7 @@
         <v>45</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>45</v>
@@ -5656,7 +5658,7 @@
         <v>45</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>45</v>
@@ -5673,7 +5675,7 @@
         <v>45</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>45</v>
@@ -5690,7 +5692,7 @@
         <v>45</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>45</v>
@@ -5707,7 +5709,7 @@
         <v>45</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>45</v>
@@ -5724,7 +5726,7 @@
         <v>45</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>45</v>
@@ -5741,7 +5743,7 @@
         <v>45</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>45</v>
@@ -5758,7 +5760,7 @@
         <v>45</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>45</v>
@@ -5775,7 +5777,7 @@
         <v>45</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>45</v>
@@ -5792,7 +5794,7 @@
         <v>45</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>45</v>
@@ -5809,7 +5811,7 @@
         <v>45</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>362</v>
+        <v>452</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>45</v>
@@ -5826,7 +5828,7 @@
         <v>45</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>453</v>
+        <v>362</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>45</v>
@@ -5843,7 +5845,7 @@
         <v>45</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>45</v>
@@ -5860,7 +5862,7 @@
         <v>45</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>45</v>
@@ -5877,7 +5879,7 @@
         <v>45</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>45</v>
@@ -5894,7 +5896,7 @@
         <v>45</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>45</v>
@@ -5911,7 +5913,7 @@
         <v>45</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>45</v>
@@ -5928,7 +5930,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>45</v>
@@ -5945,7 +5947,7 @@
         <v>45</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>45</v>
@@ -5962,7 +5964,7 @@
         <v>45</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>45</v>
@@ -5979,7 +5981,7 @@
         <v>45</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>45</v>
@@ -5996,7 +5998,7 @@
         <v>45</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>45</v>
@@ -6013,7 +6015,7 @@
         <v>45</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>45</v>
@@ -6030,7 +6032,7 @@
         <v>45</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>45</v>
@@ -6047,7 +6049,7 @@
         <v>45</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>45</v>
@@ -6064,7 +6066,7 @@
         <v>45</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>45</v>
@@ -6081,7 +6083,7 @@
         <v>45</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>45</v>
@@ -6098,7 +6100,7 @@
         <v>45</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>45</v>
@@ -6115,7 +6117,7 @@
         <v>45</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>45</v>
@@ -6132,7 +6134,7 @@
         <v>45</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>45</v>
@@ -6149,7 +6151,7 @@
         <v>45</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>45</v>
@@ -6166,7 +6168,7 @@
         <v>45</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>45</v>
@@ -6183,7 +6185,7 @@
         <v>45</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>45</v>
@@ -6200,7 +6202,7 @@
         <v>45</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>45</v>
@@ -6208,14 +6210,20 @@
     </row>
     <row r="93" spans="1:5" ht="39" customHeight="1">
       <c r="A93" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
+        <v>422</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D93" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="E93" s="10"/>
+        <v>475</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="94" spans="1:5" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
@@ -6224,7 +6232,7 @@
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E94" s="10"/>
     </row>
@@ -6232,18 +6240,12 @@
       <c r="A95" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>45</v>
-      </c>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
       <c r="D95" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>45</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="E95" s="10"/>
     </row>
     <row r="96" spans="1:5" ht="39" customHeight="1">
       <c r="A96" s="10" t="s">
@@ -6256,7 +6258,7 @@
         <v>45</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>45</v>
@@ -6273,7 +6275,7 @@
         <v>45</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>45</v>
@@ -6290,7 +6292,7 @@
         <v>45</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>45</v>
@@ -6307,7 +6309,7 @@
         <v>45</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>45</v>
@@ -6324,7 +6326,7 @@
         <v>45</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>45</v>
@@ -6341,7 +6343,7 @@
         <v>45</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>45</v>
@@ -6358,7 +6360,7 @@
         <v>45</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>561</v>
+        <v>483</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>45</v>
@@ -6375,7 +6377,7 @@
         <v>45</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>484</v>
+        <v>561</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>45</v>
@@ -6392,7 +6394,7 @@
         <v>45</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>45</v>
@@ -6409,7 +6411,7 @@
         <v>45</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>45</v>
@@ -6426,7 +6428,7 @@
         <v>45</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>562</v>
+        <v>486</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>45</v>
@@ -6443,7 +6445,7 @@
         <v>45</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>45</v>
@@ -6460,7 +6462,7 @@
         <v>45</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>487</v>
+        <v>563</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>45</v>
@@ -6477,7 +6479,7 @@
         <v>45</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>45</v>
@@ -6494,7 +6496,7 @@
         <v>45</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>45</v>
@@ -6511,7 +6513,7 @@
         <v>45</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>45</v>
@@ -6528,7 +6530,7 @@
         <v>45</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>564</v>
+        <v>490</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>45</v>
@@ -6545,7 +6547,7 @@
         <v>45</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>491</v>
+        <v>564</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>45</v>
@@ -6562,7 +6564,7 @@
         <v>45</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>45</v>
@@ -6579,7 +6581,7 @@
         <v>45</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>45</v>
@@ -6587,7 +6589,7 @@
     </row>
     <row r="116" spans="1:5" ht="39" customHeight="1">
       <c r="A116" s="10" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>45</v>
@@ -6596,7 +6598,7 @@
         <v>45</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>45</v>
@@ -6613,7 +6615,7 @@
         <v>45</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>45</v>
@@ -6630,7 +6632,7 @@
         <v>45</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>45</v>
@@ -6647,7 +6649,7 @@
         <v>45</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>45</v>
@@ -6664,7 +6666,7 @@
         <v>45</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>45</v>
@@ -6681,7 +6683,7 @@
         <v>45</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>45</v>
@@ -6698,7 +6700,7 @@
         <v>45</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>45</v>
@@ -6715,7 +6717,7 @@
         <v>45</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>45</v>
@@ -6732,7 +6734,7 @@
         <v>45</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>45</v>
@@ -6749,9 +6751,26 @@
         <v>45</v>
       </c>
       <c r="D125" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="39" customHeight="1">
+      <c r="A126" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E126" s="10" t="s">
         <v>45</v>
       </c>
     </row>

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF716207-4EE3-4222-A417-CE10435ABB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F530DC93-2D97-4338-84B1-FCAFDD8A6ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="571">
   <si>
     <t>date</t>
   </si>
@@ -1232,9 +1232,6 @@
     <t>Mathematics (SCI)</t>
   </si>
   <si>
-    <t>since June 2022</t>
-  </si>
-  <si>
     <t>Information (ESCI)</t>
   </si>
   <si>
@@ -1248,9 +1245,6 @@
   </si>
   <si>
     <t>ICSES Transactions on Neural and Fuzzy Computing</t>
-  </si>
-  <si>
-    <t>since April 2019</t>
   </si>
   <si>
     <t>Secretary</t>
@@ -1758,6 +1752,18 @@
   </si>
   <si>
     <t>Decision Making and Analysis</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>since Jun. 2026</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>since Apr. 2019</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>since Jun. 2022</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2530,10 +2536,10 @@
         <v>19</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E2" s="17" t="str">
         <f t="shared" ref="E2" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2551,7 +2557,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E3" s="17" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2927,7 +2933,7 @@
         <v>68</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E24" s="17" t="str">
         <f t="shared" si="2"/>
@@ -4949,7 +4955,7 @@
         <v>396</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>397</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="39" customHeight="1">
@@ -4960,13 +4966,13 @@
         <v>395</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>398</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="39" customHeight="1">
@@ -4977,12 +4983,14 @@
         <v>379</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="E20" s="10"/>
+        <v>567</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1">
       <c r="A21" s="10" t="s">
@@ -4992,13 +5000,13 @@
         <v>379</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>400</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="39" customHeight="1">
@@ -5009,13 +5017,13 @@
         <v>358</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>403</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" customHeight="1">
@@ -5023,13 +5031,13 @@
         <v>357</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>45</v>
@@ -5037,7 +5045,7 @@
     </row>
     <row r="24" spans="1:5" ht="39" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>45</v>
@@ -5046,7 +5054,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>45</v>
@@ -5054,16 +5062,16 @@
     </row>
     <row r="25" spans="1:5" ht="39" customHeight="1">
       <c r="A25" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>406</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>408</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>45</v>
@@ -5071,7 +5079,7 @@
     </row>
     <row r="26" spans="1:5" ht="39" customHeight="1">
       <c r="A26" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>45</v>
@@ -5080,7 +5088,7 @@
         <v>45</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>45</v>
@@ -5088,7 +5096,7 @@
     </row>
     <row r="27" spans="1:5" ht="39" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>45</v>
@@ -5097,7 +5105,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>45</v>
@@ -5105,7 +5113,7 @@
     </row>
     <row r="28" spans="1:5" ht="39" customHeight="1">
       <c r="A28" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>45</v>
@@ -5114,7 +5122,7 @@
         <v>45</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>45</v>
@@ -5122,7 +5130,7 @@
     </row>
     <row r="29" spans="1:5" ht="39" customHeight="1">
       <c r="A29" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>45</v>
@@ -5131,7 +5139,7 @@
         <v>45</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>45</v>
@@ -5139,7 +5147,7 @@
     </row>
     <row r="30" spans="1:5" ht="39" customHeight="1">
       <c r="A30" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>45</v>
@@ -5148,7 +5156,7 @@
         <v>45</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>45</v>
@@ -5156,7 +5164,7 @@
     </row>
     <row r="31" spans="1:5" ht="39" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>45</v>
@@ -5165,7 +5173,7 @@
         <v>45</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>45</v>
@@ -5173,7 +5181,7 @@
     </row>
     <row r="32" spans="1:5" ht="39" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>45</v>
@@ -5182,7 +5190,7 @@
         <v>45</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>45</v>
@@ -5190,7 +5198,7 @@
     </row>
     <row r="33" spans="1:5" ht="39" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>45</v>
@@ -5199,7 +5207,7 @@
         <v>45</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>45</v>
@@ -5207,7 +5215,7 @@
     </row>
     <row r="34" spans="1:5" ht="39" customHeight="1">
       <c r="A34" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>45</v>
@@ -5216,7 +5224,7 @@
         <v>45</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>45</v>
@@ -5224,7 +5232,7 @@
     </row>
     <row r="35" spans="1:5" ht="39" customHeight="1">
       <c r="A35" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>45</v>
@@ -5233,7 +5241,7 @@
         <v>45</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>45</v>
@@ -5241,7 +5249,7 @@
     </row>
     <row r="36" spans="1:5" ht="39" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>45</v>
@@ -5250,7 +5258,7 @@
         <v>45</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>45</v>
@@ -5258,7 +5266,7 @@
     </row>
     <row r="37" spans="1:5" ht="39" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>45</v>
@@ -5267,7 +5275,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>45</v>
@@ -5275,7 +5283,7 @@
     </row>
     <row r="38" spans="1:5" ht="39" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>45</v>
@@ -5284,7 +5292,7 @@
         <v>45</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>45</v>
@@ -5292,7 +5300,7 @@
     </row>
     <row r="39" spans="1:5" ht="39" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>45</v>
@@ -5301,7 +5309,7 @@
         <v>45</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>45</v>
@@ -5309,16 +5317,16 @@
     </row>
     <row r="40" spans="1:5" ht="39" customHeight="1">
       <c r="A40" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>422</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>424</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>45</v>
@@ -5326,7 +5334,7 @@
     </row>
     <row r="41" spans="1:5" ht="39" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>45</v>
@@ -5335,7 +5343,7 @@
         <v>45</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>45</v>
@@ -5343,7 +5351,7 @@
     </row>
     <row r="42" spans="1:5" ht="39" customHeight="1">
       <c r="A42" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>45</v>
@@ -5360,7 +5368,7 @@
     </row>
     <row r="43" spans="1:5" ht="39" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>45</v>
@@ -5369,7 +5377,7 @@
         <v>45</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>45</v>
@@ -5377,7 +5385,7 @@
     </row>
     <row r="44" spans="1:5" ht="39" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>45</v>
@@ -5386,7 +5394,7 @@
         <v>45</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>45</v>
@@ -5394,7 +5402,7 @@
     </row>
     <row r="45" spans="1:5" ht="39" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>45</v>
@@ -5403,7 +5411,7 @@
         <v>45</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>45</v>
@@ -5411,7 +5419,7 @@
     </row>
     <row r="46" spans="1:5" ht="39" customHeight="1">
       <c r="A46" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>45</v>
@@ -5420,7 +5428,7 @@
         <v>45</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>45</v>
@@ -5428,7 +5436,7 @@
     </row>
     <row r="47" spans="1:5" ht="39" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>45</v>
@@ -5437,7 +5445,7 @@
         <v>45</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>45</v>
@@ -5445,7 +5453,7 @@
     </row>
     <row r="48" spans="1:5" ht="39" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>45</v>
@@ -5454,7 +5462,7 @@
         <v>45</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>45</v>
@@ -5462,7 +5470,7 @@
     </row>
     <row r="49" spans="1:5" ht="39" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>45</v>
@@ -5471,7 +5479,7 @@
         <v>45</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>45</v>
@@ -5479,7 +5487,7 @@
     </row>
     <row r="50" spans="1:5" ht="39" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>45</v>
@@ -5488,7 +5496,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>45</v>
@@ -5496,7 +5504,7 @@
     </row>
     <row r="51" spans="1:5" ht="39" customHeight="1">
       <c r="A51" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>45</v>
@@ -5505,7 +5513,7 @@
         <v>45</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>45</v>
@@ -5513,7 +5521,7 @@
     </row>
     <row r="52" spans="1:5" ht="39" customHeight="1">
       <c r="A52" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>45</v>
@@ -5522,7 +5530,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>45</v>
@@ -5530,7 +5538,7 @@
     </row>
     <row r="53" spans="1:5" ht="39" customHeight="1">
       <c r="A53" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>45</v>
@@ -5539,7 +5547,7 @@
         <v>45</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>45</v>
@@ -5547,7 +5555,7 @@
     </row>
     <row r="54" spans="1:5" ht="39" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>45</v>
@@ -5556,7 +5564,7 @@
         <v>45</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>45</v>
@@ -5564,7 +5572,7 @@
     </row>
     <row r="55" spans="1:5" ht="39" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>45</v>
@@ -5573,7 +5581,7 @@
         <v>45</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>45</v>
@@ -5581,7 +5589,7 @@
     </row>
     <row r="56" spans="1:5" ht="39" customHeight="1">
       <c r="A56" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>45</v>
@@ -5590,7 +5598,7 @@
         <v>45</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>45</v>
@@ -5598,7 +5606,7 @@
     </row>
     <row r="57" spans="1:5" ht="39" customHeight="1">
       <c r="A57" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>45</v>
@@ -5607,7 +5615,7 @@
         <v>45</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>45</v>
@@ -5615,7 +5623,7 @@
     </row>
     <row r="58" spans="1:5" ht="39" customHeight="1">
       <c r="A58" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>45</v>
@@ -5624,7 +5632,7 @@
         <v>45</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>45</v>
@@ -5632,7 +5640,7 @@
     </row>
     <row r="59" spans="1:5" ht="39" customHeight="1">
       <c r="A59" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>45</v>
@@ -5641,7 +5649,7 @@
         <v>45</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>45</v>
@@ -5649,7 +5657,7 @@
     </row>
     <row r="60" spans="1:5" ht="39" customHeight="1">
       <c r="A60" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>45</v>
@@ -5658,7 +5666,7 @@
         <v>45</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>45</v>
@@ -5666,7 +5674,7 @@
     </row>
     <row r="61" spans="1:5" ht="39" customHeight="1">
       <c r="A61" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>45</v>
@@ -5675,7 +5683,7 @@
         <v>45</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>45</v>
@@ -5683,7 +5691,7 @@
     </row>
     <row r="62" spans="1:5" ht="39" customHeight="1">
       <c r="A62" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>45</v>
@@ -5692,7 +5700,7 @@
         <v>45</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>45</v>
@@ -5700,7 +5708,7 @@
     </row>
     <row r="63" spans="1:5" ht="39" customHeight="1">
       <c r="A63" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>45</v>
@@ -5709,7 +5717,7 @@
         <v>45</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>45</v>
@@ -5717,7 +5725,7 @@
     </row>
     <row r="64" spans="1:5" ht="39" customHeight="1">
       <c r="A64" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>45</v>
@@ -5726,7 +5734,7 @@
         <v>45</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>45</v>
@@ -5734,7 +5742,7 @@
     </row>
     <row r="65" spans="1:5" ht="39" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>45</v>
@@ -5743,7 +5751,7 @@
         <v>45</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>45</v>
@@ -5751,7 +5759,7 @@
     </row>
     <row r="66" spans="1:5" ht="39" customHeight="1">
       <c r="A66" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>45</v>
@@ -5760,7 +5768,7 @@
         <v>45</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>45</v>
@@ -5768,7 +5776,7 @@
     </row>
     <row r="67" spans="1:5" ht="39" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>45</v>
@@ -5777,7 +5785,7 @@
         <v>45</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>45</v>
@@ -5785,7 +5793,7 @@
     </row>
     <row r="68" spans="1:5" ht="39" customHeight="1">
       <c r="A68" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>45</v>
@@ -5794,7 +5802,7 @@
         <v>45</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>45</v>
@@ -5802,7 +5810,7 @@
     </row>
     <row r="69" spans="1:5" ht="39" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>45</v>
@@ -5811,7 +5819,7 @@
         <v>45</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>45</v>
@@ -5819,7 +5827,7 @@
     </row>
     <row r="70" spans="1:5" ht="39" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>45</v>
@@ -5836,7 +5844,7 @@
     </row>
     <row r="71" spans="1:5" ht="39" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>45</v>
@@ -5845,7 +5853,7 @@
         <v>45</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>45</v>
@@ -5853,7 +5861,7 @@
     </row>
     <row r="72" spans="1:5" ht="39" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>45</v>
@@ -5862,7 +5870,7 @@
         <v>45</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>45</v>
@@ -5870,7 +5878,7 @@
     </row>
     <row r="73" spans="1:5" ht="39" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>45</v>
@@ -5879,7 +5887,7 @@
         <v>45</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>45</v>
@@ -5887,7 +5895,7 @@
     </row>
     <row r="74" spans="1:5" ht="39" customHeight="1">
       <c r="A74" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>45</v>
@@ -5896,7 +5904,7 @@
         <v>45</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>45</v>
@@ -5904,7 +5912,7 @@
     </row>
     <row r="75" spans="1:5" ht="39" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>45</v>
@@ -5913,7 +5921,7 @@
         <v>45</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>45</v>
@@ -5921,7 +5929,7 @@
     </row>
     <row r="76" spans="1:5" ht="39" customHeight="1">
       <c r="A76" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>45</v>
@@ -5930,7 +5938,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>45</v>
@@ -5938,7 +5946,7 @@
     </row>
     <row r="77" spans="1:5" ht="39" customHeight="1">
       <c r="A77" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>45</v>
@@ -5947,7 +5955,7 @@
         <v>45</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>45</v>
@@ -5955,7 +5963,7 @@
     </row>
     <row r="78" spans="1:5" ht="39" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>45</v>
@@ -5964,7 +5972,7 @@
         <v>45</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>45</v>
@@ -5972,7 +5980,7 @@
     </row>
     <row r="79" spans="1:5" ht="39" customHeight="1">
       <c r="A79" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>45</v>
@@ -5981,7 +5989,7 @@
         <v>45</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>45</v>
@@ -5989,7 +5997,7 @@
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1">
       <c r="A80" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>45</v>
@@ -5998,7 +6006,7 @@
         <v>45</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>45</v>
@@ -6006,7 +6014,7 @@
     </row>
     <row r="81" spans="1:5" ht="39" customHeight="1">
       <c r="A81" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>45</v>
@@ -6015,7 +6023,7 @@
         <v>45</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>45</v>
@@ -6023,7 +6031,7 @@
     </row>
     <row r="82" spans="1:5" ht="39" customHeight="1">
       <c r="A82" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>45</v>
@@ -6032,7 +6040,7 @@
         <v>45</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>45</v>
@@ -6040,7 +6048,7 @@
     </row>
     <row r="83" spans="1:5" ht="39" customHeight="1">
       <c r="A83" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>45</v>
@@ -6049,7 +6057,7 @@
         <v>45</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>45</v>
@@ -6057,7 +6065,7 @@
     </row>
     <row r="84" spans="1:5" ht="39" customHeight="1">
       <c r="A84" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>45</v>
@@ -6066,7 +6074,7 @@
         <v>45</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>45</v>
@@ -6074,7 +6082,7 @@
     </row>
     <row r="85" spans="1:5" ht="39" customHeight="1">
       <c r="A85" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>45</v>
@@ -6083,7 +6091,7 @@
         <v>45</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>45</v>
@@ -6091,7 +6099,7 @@
     </row>
     <row r="86" spans="1:5" ht="39" customHeight="1">
       <c r="A86" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>45</v>
@@ -6100,7 +6108,7 @@
         <v>45</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>45</v>
@@ -6108,7 +6116,7 @@
     </row>
     <row r="87" spans="1:5" ht="39" customHeight="1">
       <c r="A87" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>45</v>
@@ -6117,7 +6125,7 @@
         <v>45</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>45</v>
@@ -6125,7 +6133,7 @@
     </row>
     <row r="88" spans="1:5" ht="39" customHeight="1">
       <c r="A88" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>45</v>
@@ -6134,7 +6142,7 @@
         <v>45</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>45</v>
@@ -6142,7 +6150,7 @@
     </row>
     <row r="89" spans="1:5" ht="39" customHeight="1">
       <c r="A89" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>45</v>
@@ -6151,7 +6159,7 @@
         <v>45</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>45</v>
@@ -6159,7 +6167,7 @@
     </row>
     <row r="90" spans="1:5" ht="39" customHeight="1">
       <c r="A90" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>45</v>
@@ -6168,7 +6176,7 @@
         <v>45</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>45</v>
@@ -6176,7 +6184,7 @@
     </row>
     <row r="91" spans="1:5" ht="39" customHeight="1">
       <c r="A91" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>45</v>
@@ -6185,7 +6193,7 @@
         <v>45</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>45</v>
@@ -6193,7 +6201,7 @@
     </row>
     <row r="92" spans="1:5" ht="39" customHeight="1">
       <c r="A92" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>45</v>
@@ -6202,7 +6210,7 @@
         <v>45</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>45</v>
@@ -6210,7 +6218,7 @@
     </row>
     <row r="93" spans="1:5" ht="39" customHeight="1">
       <c r="A93" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>45</v>
@@ -6219,7 +6227,7 @@
         <v>45</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>45</v>
@@ -6227,29 +6235,29 @@
     </row>
     <row r="94" spans="1:5" ht="39" customHeight="1">
       <c r="A94" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E94" s="10"/>
     </row>
     <row r="95" spans="1:5" ht="39" customHeight="1">
       <c r="A95" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E95" s="10"/>
     </row>
     <row r="96" spans="1:5" ht="39" customHeight="1">
       <c r="A96" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>45</v>
@@ -6258,7 +6266,7 @@
         <v>45</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>45</v>
@@ -6266,16 +6274,16 @@
     </row>
     <row r="97" spans="1:5" ht="39" customHeight="1">
       <c r="A97" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>476</v>
-      </c>
-      <c r="B97" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>478</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>45</v>
@@ -6283,7 +6291,7 @@
     </row>
     <row r="98" spans="1:5" ht="39" customHeight="1">
       <c r="A98" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>45</v>
@@ -6292,7 +6300,7 @@
         <v>45</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>45</v>
@@ -6300,7 +6308,7 @@
     </row>
     <row r="99" spans="1:5" ht="39" customHeight="1">
       <c r="A99" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>45</v>
@@ -6309,7 +6317,7 @@
         <v>45</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>45</v>
@@ -6317,7 +6325,7 @@
     </row>
     <row r="100" spans="1:5" ht="39" customHeight="1">
       <c r="A100" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>45</v>
@@ -6326,7 +6334,7 @@
         <v>45</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>45</v>
@@ -6334,7 +6342,7 @@
     </row>
     <row r="101" spans="1:5" ht="39" customHeight="1">
       <c r="A101" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>45</v>
@@ -6343,7 +6351,7 @@
         <v>45</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>45</v>
@@ -6351,7 +6359,7 @@
     </row>
     <row r="102" spans="1:5" ht="39" customHeight="1">
       <c r="A102" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>45</v>
@@ -6360,7 +6368,7 @@
         <v>45</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>45</v>
@@ -6368,7 +6376,7 @@
     </row>
     <row r="103" spans="1:5" ht="39" customHeight="1">
       <c r="A103" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>45</v>
@@ -6377,7 +6385,7 @@
         <v>45</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>45</v>
@@ -6385,7 +6393,7 @@
     </row>
     <row r="104" spans="1:5" ht="39" customHeight="1">
       <c r="A104" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>45</v>
@@ -6394,7 +6402,7 @@
         <v>45</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>45</v>
@@ -6402,7 +6410,7 @@
     </row>
     <row r="105" spans="1:5" ht="39" customHeight="1">
       <c r="A105" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>45</v>
@@ -6411,7 +6419,7 @@
         <v>45</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>45</v>
@@ -6419,7 +6427,7 @@
     </row>
     <row r="106" spans="1:5" ht="39" customHeight="1">
       <c r="A106" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>45</v>
@@ -6428,7 +6436,7 @@
         <v>45</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>45</v>
@@ -6436,7 +6444,7 @@
     </row>
     <row r="107" spans="1:5" ht="39" customHeight="1">
       <c r="A107" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>45</v>
@@ -6445,7 +6453,7 @@
         <v>45</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>45</v>
@@ -6453,7 +6461,7 @@
     </row>
     <row r="108" spans="1:5" ht="39" customHeight="1">
       <c r="A108" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>45</v>
@@ -6462,7 +6470,7 @@
         <v>45</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>45</v>
@@ -6470,7 +6478,7 @@
     </row>
     <row r="109" spans="1:5" ht="39" customHeight="1">
       <c r="A109" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>45</v>
@@ -6479,7 +6487,7 @@
         <v>45</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>45</v>
@@ -6487,7 +6495,7 @@
     </row>
     <row r="110" spans="1:5" ht="39" customHeight="1">
       <c r="A110" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>45</v>
@@ -6496,7 +6504,7 @@
         <v>45</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>45</v>
@@ -6504,7 +6512,7 @@
     </row>
     <row r="111" spans="1:5" ht="39" customHeight="1">
       <c r="A111" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>45</v>
@@ -6513,7 +6521,7 @@
         <v>45</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>45</v>
@@ -6521,7 +6529,7 @@
     </row>
     <row r="112" spans="1:5" ht="39" customHeight="1">
       <c r="A112" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>45</v>
@@ -6530,7 +6538,7 @@
         <v>45</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>45</v>
@@ -6538,7 +6546,7 @@
     </row>
     <row r="113" spans="1:5" ht="39" customHeight="1">
       <c r="A113" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>45</v>
@@ -6547,7 +6555,7 @@
         <v>45</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>45</v>
@@ -6555,7 +6563,7 @@
     </row>
     <row r="114" spans="1:5" ht="39" customHeight="1">
       <c r="A114" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>45</v>
@@ -6564,7 +6572,7 @@
         <v>45</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>45</v>
@@ -6572,7 +6580,7 @@
     </row>
     <row r="115" spans="1:5" ht="39" customHeight="1">
       <c r="A115" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>45</v>
@@ -6581,7 +6589,7 @@
         <v>45</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>45</v>
@@ -6589,7 +6597,7 @@
     </row>
     <row r="116" spans="1:5" ht="39" customHeight="1">
       <c r="A116" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>45</v>
@@ -6598,7 +6606,7 @@
         <v>45</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>45</v>
@@ -6606,7 +6614,7 @@
     </row>
     <row r="117" spans="1:5" ht="39" customHeight="1">
       <c r="A117" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>45</v>
@@ -6615,7 +6623,7 @@
         <v>45</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>45</v>
@@ -6623,16 +6631,16 @@
     </row>
     <row r="118" spans="1:5" ht="39" customHeight="1">
       <c r="A118" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D118" s="10" t="s">
         <v>494</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>496</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>45</v>
@@ -6640,7 +6648,7 @@
     </row>
     <row r="119" spans="1:5" ht="39" customHeight="1">
       <c r="A119" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>45</v>
@@ -6649,7 +6657,7 @@
         <v>45</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>45</v>
@@ -6657,7 +6665,7 @@
     </row>
     <row r="120" spans="1:5" ht="39" customHeight="1">
       <c r="A120" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>45</v>
@@ -6666,7 +6674,7 @@
         <v>45</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>45</v>
@@ -6674,7 +6682,7 @@
     </row>
     <row r="121" spans="1:5" ht="39" customHeight="1">
       <c r="A121" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>45</v>
@@ -6683,7 +6691,7 @@
         <v>45</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>45</v>
@@ -6691,7 +6699,7 @@
     </row>
     <row r="122" spans="1:5" ht="39" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>45</v>
@@ -6700,7 +6708,7 @@
         <v>45</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>45</v>
@@ -6708,7 +6716,7 @@
     </row>
     <row r="123" spans="1:5" ht="39" customHeight="1">
       <c r="A123" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>45</v>
@@ -6717,7 +6725,7 @@
         <v>45</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>45</v>
@@ -6725,7 +6733,7 @@
     </row>
     <row r="124" spans="1:5" ht="39" customHeight="1">
       <c r="A124" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>45</v>
@@ -6734,7 +6742,7 @@
         <v>45</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>45</v>
@@ -6742,7 +6750,7 @@
     </row>
     <row r="125" spans="1:5" ht="39" customHeight="1">
       <c r="A125" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>45</v>
@@ -6751,7 +6759,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>45</v>
@@ -6759,7 +6767,7 @@
     </row>
     <row r="126" spans="1:5" ht="39" customHeight="1">
       <c r="A126" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>45</v>
@@ -6768,7 +6776,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>45</v>
@@ -6799,10 +6807,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
@@ -6810,62 +6818,62 @@
     </row>
     <row r="2" spans="1:4" ht="27.6">
       <c r="A2" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.6">
       <c r="A3" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="41.4">
       <c r="A4" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>515</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>520</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
@@ -6874,10 +6882,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
@@ -6886,10 +6894,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
@@ -6898,40 +6906,40 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>523</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>525</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6" t="s">
@@ -6940,10 +6948,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6" t="s">
@@ -6952,10 +6960,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6" t="s">
@@ -6964,40 +6972,40 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
@@ -7006,10 +7014,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6" t="s">
@@ -7018,10 +7026,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
@@ -7030,10 +7038,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
@@ -7042,10 +7050,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
@@ -7054,10 +7062,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
@@ -7066,10 +7074,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
@@ -7078,10 +7086,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6" t="s">
@@ -7090,10 +7098,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
@@ -7102,10 +7110,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
@@ -7114,10 +7122,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
@@ -7126,10 +7134,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6" t="s">
@@ -7138,10 +7146,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6" t="s">
@@ -7150,10 +7158,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6" t="s">
@@ -7162,10 +7170,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
@@ -7174,10 +7182,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6" t="s">
@@ -7229,7 +7237,7 @@
         <v>237</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -7249,50 +7257,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8">
       <c r="A2" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.8">
       <c r="A3" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28.8">
       <c r="A5" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F530DC93-2D97-4338-84B1-FCAFDD8A6ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E452D8F0-FE81-404E-AC8A-D24BCB4D7170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="23040" windowHeight="12204" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,6 @@
     <sheet name="Grants" sheetId="3" r:id="rId3"/>
     <sheet name="Services" sheetId="4" r:id="rId4"/>
     <sheet name="Group" sheetId="5" r:id="rId5"/>
-    <sheet name="Projects" sheetId="6" r:id="rId6"/>
-    <sheet name="README" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="559">
   <si>
     <t>date</t>
   </si>
@@ -1674,42 +1672,6 @@
   </si>
   <si>
     <t>Xinyue Kou</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Maintain changing website content in Excel, then convert to JSON for the homepage.</t>
-  </si>
-  <si>
-    <t>Do not maintain here</t>
-  </si>
-  <si>
-    <t>Profile, external links, and Scholar settings are stable and stored in index.html/site.config.js.</t>
-  </si>
-  <si>
-    <t>Publications</t>
-  </si>
-  <si>
-    <t>Use your existing publication Excel. The converter supports a separate --publications-xlsx input and outputs data/publications.json.</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>python scripts/convert_excel_to_json.py --excel homepage_content.xlsx --out data</t>
-  </si>
-  <si>
-    <t>Command with publications</t>
-  </si>
-  <si>
-    <t>python scripts/convert_excel_to_json.py --excel homepage_content.xlsx --publications-xlsx publications.xlsx --out data</t>
-  </si>
-  <si>
-    <t>Publication filters</t>
-  </si>
-  <si>
-    <t>The webpage automatically displays all records and supports filtering by year and type/category.</t>
   </si>
   <si>
     <t>The International Conference of Granular-Ball Computing (ICGBC 2026)</t>
@@ -1839,11 +1801,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2504,1418 +2463,1418 @@
   <dimension ref="A1:E79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.45" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="18" style="13" customWidth="1"/>
-    <col min="3" max="3" width="71.33203125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="18" style="13" customWidth="1"/>
-    <col min="5" max="5" width="18" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="13"/>
+    <col min="1" max="2" width="18" style="12" customWidth="1"/>
+    <col min="3" max="3" width="71.33203125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18" style="12" customWidth="1"/>
+    <col min="5" max="5" width="18" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A2" s="18">
+      <c r="A2" s="17">
         <v>46189</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>565</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>566</v>
-      </c>
-      <c r="E2" s="17" t="str">
+      <c r="C2" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="E2" s="16" t="str">
         <f t="shared" ref="E2" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A3" s="18">
+      <c r="A3" s="17">
         <v>46184</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>563</v>
-      </c>
-      <c r="E3" s="17" t="str">
+      <c r="D3" s="18" t="s">
+        <v>551</v>
+      </c>
+      <c r="E3" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A4" s="18">
+      <c r="A4" s="17">
         <v>46177</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="17" t="str">
+      <c r="E4" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <v>46168</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17" t="str">
+      <c r="D5" s="15"/>
+      <c r="E5" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="16" t="str">
         <f t="shared" ref="E6:E15" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="16" t="str">
         <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="16" t="str">
         <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="16" t="str">
         <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="17" t="str">
+      <c r="E10" s="16" t="str">
         <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="17" t="str">
+      <c r="E11" s="16" t="str">
         <f t="shared" si="1"/>
         <v>yes</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="17" t="str">
+      <c r="E12" s="16" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="17" t="str">
+      <c r="E13" s="16" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="17" t="str">
+      <c r="E14" s="16" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="17" t="str">
+      <c r="E15" s="16" t="str">
         <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="17" t="str">
+      <c r="D16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="16" t="str">
         <f t="shared" ref="E16:E25" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="17" t="str">
+      <c r="E17" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="17" t="str">
+      <c r="E18" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="17" t="str">
+      <c r="E19" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="17" t="str">
+      <c r="E20" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="17" t="str">
+      <c r="E21" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="17" t="str">
+      <c r="E22" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="17" t="str">
+      <c r="E23" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="E24" s="17" t="str">
+      <c r="D24" s="18" t="s">
+        <v>552</v>
+      </c>
+      <c r="E24" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="17" t="str">
+      <c r="E25" s="16" t="str">
         <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="17" t="str">
+      <c r="E26" s="16" t="str">
         <f t="shared" ref="E26:E35" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="17" t="str">
+      <c r="D27" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="17" t="str">
+      <c r="E28" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="17" t="str">
+      <c r="E29" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="17" t="str">
+      <c r="D30" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="17" t="str">
+      <c r="E31" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="17" t="str">
+      <c r="E32" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="17" t="str">
+      <c r="D33" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="17" t="str">
+      <c r="E34" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="17" t="str">
+      <c r="E35" s="16" t="str">
         <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E36" s="17" t="str">
+      <c r="E36" s="16" t="str">
         <f t="shared" ref="E36:E53" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="17" t="str">
+      <c r="E37" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="17" t="str">
+      <c r="E38" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="17" t="str">
+      <c r="E39" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E40" s="17" t="str">
+      <c r="E40" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A41" s="18">
+      <c r="A41" s="17">
         <v>45597</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E41" s="17" t="str">
+      <c r="E41" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A42" s="18">
+      <c r="A42" s="17">
         <v>45593</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="17" t="str">
+      <c r="D42" s="15"/>
+      <c r="E42" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A43" s="18">
+      <c r="A43" s="17">
         <v>45585</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A44" s="18">
+      <c r="A44" s="17">
         <v>45584</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E44" s="17" t="str">
+      <c r="E44" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A45" s="18">
+      <c r="A45" s="17">
         <v>45583</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="17" t="str">
+      <c r="E45" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="17" t="str">
+      <c r="E46" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A47" s="18">
+      <c r="A47" s="17">
         <v>45580</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="17" t="str">
+      <c r="D47" s="15"/>
+      <c r="E47" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="17" t="str">
+      <c r="E48" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="17" t="str">
+      <c r="E49" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D50" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E50" s="17" t="str">
+      <c r="D50" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A51" s="18">
+      <c r="A51" s="17">
         <v>45514</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E51" s="17" t="str">
+      <c r="E51" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="17" t="str">
+      <c r="E52" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A53" s="18">
+      <c r="A53" s="17">
         <v>45432</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D53" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="E53" s="17" t="str">
+      <c r="E53" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D54" s="16" t="s">
+      <c r="D54" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E54" s="17" t="str">
+      <c r="E54" s="16" t="str">
         <f t="shared" ref="E54:E67" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E55" s="17" t="str">
+      <c r="E55" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E56" s="17" t="str">
+      <c r="E56" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="E57" s="17" t="str">
+      <c r="E57" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D58" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E58" s="17" t="str">
+      <c r="E58" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A59" s="18">
+      <c r="A59" s="17">
         <v>45264</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="D59" s="16"/>
-      <c r="E59" s="17" t="str">
+      <c r="D59" s="15"/>
+      <c r="E59" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E60" s="17" t="str">
+      <c r="E60" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="17" t="str">
+      <c r="D61" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D62" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E62" s="17" t="str">
+      <c r="D62" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A63" s="18">
+      <c r="A63" s="17">
         <v>45118</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D63" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E63" s="17" t="str">
+      <c r="E63" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="E64" s="17" t="str">
+      <c r="E64" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A65" s="18" t="s">
+      <c r="A65" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E65" s="17" t="str">
+      <c r="E65" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A66" s="18">
+      <c r="A66" s="17">
         <v>45023</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D66" s="16"/>
-      <c r="E66" s="17" t="str">
+      <c r="D66" s="15"/>
+      <c r="E66" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A67" s="18">
+      <c r="A67" s="17">
         <v>45006</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D67" s="16"/>
-      <c r="E67" s="17" t="str">
+      <c r="D67" s="15"/>
+      <c r="E67" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="16" t="s">
+      <c r="D68" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E68" s="17" t="str">
+      <c r="E68" s="16" t="str">
         <f t="shared" ref="E68:E79" si="6">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="E69" s="17" t="str">
+      <c r="E69" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A70" s="18" t="s">
+      <c r="A70" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C70" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="D70" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E70" s="17" t="str">
+      <c r="E70" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="E71" s="17" t="str">
+      <c r="E71" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A72" s="18">
+      <c r="A72" s="17">
         <v>44945</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="D72" s="16" t="s">
+      <c r="D72" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E72" s="17" t="str">
+      <c r="E72" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E73" s="17" t="str">
+      <c r="E73" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A74" s="18" t="s">
+      <c r="A74" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="D74" s="16" t="s">
+      <c r="D74" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="E74" s="17" t="str">
+      <c r="E74" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A75" s="18" t="s">
+      <c r="A75" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B75" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D75" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E75" s="17" t="str">
+      <c r="D75" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A76" s="18" t="s">
+      <c r="A76" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D76" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E76" s="17" t="str">
+      <c r="D76" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A77" s="18" t="s">
+      <c r="A77" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="D77" s="16" t="s">
+      <c r="D77" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E77" s="17" t="str">
+      <c r="E77" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A78" s="18" t="s">
+      <c r="A78" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="D78" s="16" t="s">
+      <c r="D78" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E78" s="17" t="str">
+      <c r="E78" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A79" s="18" t="s">
+      <c r="A79" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="D79" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" s="17" t="str">
+      <c r="D79" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
@@ -3940,145 +3899,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="11" customFormat="1" ht="28.8">
-      <c r="A2" s="12">
+    <row r="2" spans="1:3" s="10" customFormat="1" ht="28.8">
+      <c r="A2" s="11">
         <v>2026</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="43.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="28.8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4103,531 +4062,531 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="57.6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="57.6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="57.6">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="43.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="57.6">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="43.2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="43.2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>355</v>
       </c>
     </row>
@@ -4645,2140 +4604,2140 @@
   <dimension ref="A1:E126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="18" style="8" customWidth="1"/>
-    <col min="3" max="3" width="32" style="8" customWidth="1"/>
-    <col min="4" max="4" width="42" style="8" customWidth="1"/>
-    <col min="5" max="5" width="32.88671875" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="8"/>
+    <col min="1" max="2" width="18" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32" style="7" customWidth="1"/>
+    <col min="4" max="4" width="42" style="7" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="39" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="39" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="39" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="39" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="39" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="39" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="39" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="39" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="39" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="39" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="39" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="39" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="39" customHeight="1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="39" customHeight="1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="39" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="39" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>570</v>
+      <c r="E18" s="9" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="39" customHeight="1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="39" customHeight="1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>568</v>
+      <c r="C20" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="39" customHeight="1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>569</v>
+      <c r="E22" s="9" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" customHeight="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="39" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="B24" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="39" customHeight="1">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="B25" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="39" customHeight="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="39" customHeight="1">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="B27" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="39" customHeight="1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="B28" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="39" customHeight="1">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="B29" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="39" customHeight="1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="39" customHeight="1">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="B31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="39" customHeight="1">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="B32" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="39" customHeight="1">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="B33" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="39" customHeight="1">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="B34" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="39" customHeight="1">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="B35" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="39" customHeight="1">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="B36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="39" customHeight="1">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="B37" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="39" customHeight="1">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="B38" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="39" customHeight="1">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="B39" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="39" customHeight="1">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="B40" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="39" customHeight="1">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="B41" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="39" customHeight="1">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="10" t="s">
+      <c r="B42" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="39" customHeight="1">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="B43" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="39" customHeight="1">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="10" t="s">
+      <c r="B44" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="39" customHeight="1">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="10" t="s">
+      <c r="B45" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="39" customHeight="1">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="10" t="s">
+      <c r="B46" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="39" customHeight="1">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="B47" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="39" customHeight="1">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="B48" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="39" customHeight="1">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="B49" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="39" customHeight="1">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="B50" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="39" customHeight="1">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="10" t="s">
+      <c r="B51" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="39" customHeight="1">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="B52" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="39" customHeight="1">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="10" t="s">
+      <c r="B53" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="39" customHeight="1">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="B54" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="39" customHeight="1">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="10" t="s">
+      <c r="B55" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="39" customHeight="1">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="B56" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="39" customHeight="1">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" s="10" t="s">
+      <c r="B57" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="39" customHeight="1">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D58" s="10" t="s">
+      <c r="B58" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="39" customHeight="1">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D59" s="10" t="s">
+      <c r="B59" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="39" customHeight="1">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="10" t="s">
+      <c r="B60" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="39" customHeight="1">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D61" s="10" t="s">
+      <c r="B61" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="39" customHeight="1">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D62" s="10" t="s">
+      <c r="B62" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="39" customHeight="1">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D63" s="10" t="s">
+      <c r="B63" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="39" customHeight="1">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D64" s="10" t="s">
+      <c r="B64" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="39" customHeight="1">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D65" s="10" t="s">
+      <c r="B65" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="39" customHeight="1">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D66" s="10" t="s">
+      <c r="B66" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="39" customHeight="1">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="10" t="s">
+      <c r="B67" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="39" customHeight="1">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D68" s="10" t="s">
+      <c r="B68" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="39" customHeight="1">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" s="10" t="s">
+      <c r="B69" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="39" customHeight="1">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D70" s="10" t="s">
+      <c r="B70" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="39" customHeight="1">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D71" s="10" t="s">
+      <c r="B71" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="39" customHeight="1">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D72" s="10" t="s">
+      <c r="B72" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="39" customHeight="1">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73" s="10" t="s">
+      <c r="B73" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="39" customHeight="1">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="B74" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D74" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E74" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="39" customHeight="1">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D75" s="10" t="s">
+      <c r="B75" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D75" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="39" customHeight="1">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D76" s="10" t="s">
+      <c r="B76" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="39" customHeight="1">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D77" s="10" t="s">
+      <c r="B77" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="39" customHeight="1">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D78" s="10" t="s">
+      <c r="B78" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="39" customHeight="1">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B79" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="10" t="s">
+      <c r="B79" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B80" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D80" s="10" t="s">
+      <c r="B80" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="39" customHeight="1">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D81" s="10" t="s">
+      <c r="B81" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="39" customHeight="1">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B82" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D82" s="10" t="s">
+      <c r="B82" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="39" customHeight="1">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B83" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D83" s="10" t="s">
+      <c r="B83" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D83" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="39" customHeight="1">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B84" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D84" s="10" t="s">
+      <c r="B84" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="39" customHeight="1">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B85" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D85" s="10" t="s">
+      <c r="B85" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D85" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="39" customHeight="1">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B86" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D86" s="10" t="s">
+      <c r="B86" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="39" customHeight="1">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D87" s="10" t="s">
+      <c r="B87" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="39" customHeight="1">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B88" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D88" s="10" t="s">
+      <c r="B88" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="39" customHeight="1">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B89" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D89" s="10" t="s">
+      <c r="B89" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="39" customHeight="1">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B90" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D90" s="10" t="s">
+      <c r="B90" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D90" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="39" customHeight="1">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B91" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D91" s="10" t="s">
+      <c r="B91" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="39" customHeight="1">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B92" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D92" s="10" t="s">
+      <c r="B92" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="39" customHeight="1">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B93" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D93" s="10" t="s">
+      <c r="B93" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="39" customHeight="1">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="E94" s="10"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E94" s="9"/>
     </row>
     <row r="95" spans="1:5" ht="39" customHeight="1">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="E95" s="10"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E95" s="9"/>
     </row>
     <row r="96" spans="1:5" ht="39" customHeight="1">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D96" s="10" t="s">
+      <c r="B96" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D96" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E96" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="39" customHeight="1">
-      <c r="A97" s="10" t="s">
+      <c r="A97" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B97" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D97" s="10" t="s">
+      <c r="B97" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="39" customHeight="1">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B98" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D98" s="10" t="s">
+      <c r="B98" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E98" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="39" customHeight="1">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B99" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D99" s="10" t="s">
+      <c r="B99" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D99" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="39" customHeight="1">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B100" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D100" s="10" t="s">
+      <c r="B100" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E100" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="39" customHeight="1">
-      <c r="A101" s="10" t="s">
+      <c r="A101" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C101" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D101" s="10" t="s">
+      <c r="B101" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="39" customHeight="1">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B102" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D102" s="10" t="s">
+      <c r="B102" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="E102" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="39" customHeight="1">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B103" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="E103" s="10" t="s">
+      <c r="B103" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="E103" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="39" customHeight="1">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D104" s="10" t="s">
+      <c r="B104" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="E104" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="39" customHeight="1">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B105" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D105" s="10" t="s">
+      <c r="B105" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D105" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="39" customHeight="1">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B106" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D106" s="10" t="s">
+      <c r="B106" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D106" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="E106" s="10" t="s">
+      <c r="E106" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="39" customHeight="1">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B107" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="E107" s="10" t="s">
+      <c r="B107" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E107" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="39" customHeight="1">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B108" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="E108" s="10" t="s">
+      <c r="B108" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="E108" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="39" customHeight="1">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B109" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D109" s="10" t="s">
+      <c r="B109" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D109" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E109" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="39" customHeight="1">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B110" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D110" s="10" t="s">
+      <c r="B110" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D110" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="E110" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="39" customHeight="1">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B111" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D111" s="10" t="s">
+      <c r="B111" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D111" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="39" customHeight="1">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B112" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D112" s="10" t="s">
+      <c r="B112" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D112" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="E112" s="10" t="s">
+      <c r="E112" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="39" customHeight="1">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B113" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="E113" s="10" t="s">
+      <c r="B113" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="E113" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="39" customHeight="1">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D114" s="10" t="s">
+      <c r="B114" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D114" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E114" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="39" customHeight="1">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B115" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D115" s="10" t="s">
+      <c r="B115" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D115" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="E115" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="39" customHeight="1">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B116" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D116" s="10" t="s">
+      <c r="B116" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D116" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="E116" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="39" customHeight="1">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B117" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D117" s="10" t="s">
+      <c r="B117" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D117" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E117" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="39" customHeight="1">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B118" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D118" s="10" t="s">
+      <c r="B118" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D118" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="E118" s="10" t="s">
+      <c r="E118" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="39" customHeight="1">
-      <c r="A119" s="10" t="s">
+      <c r="A119" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B119" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D119" s="10" t="s">
+      <c r="B119" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D119" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="E119" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="39" customHeight="1">
-      <c r="A120" s="10" t="s">
+      <c r="A120" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B120" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D120" s="10" t="s">
+      <c r="B120" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D120" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E120" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="39" customHeight="1">
-      <c r="A121" s="10" t="s">
+      <c r="A121" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B121" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D121" s="10" t="s">
+      <c r="B121" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D121" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E121" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="39" customHeight="1">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B122" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D122" s="10" t="s">
+      <c r="B122" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="E122" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="39" customHeight="1">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D123" s="10" t="s">
+      <c r="B123" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D123" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="E123" s="10" t="s">
+      <c r="E123" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="39" customHeight="1">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B124" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D124" s="10" t="s">
+      <c r="B124" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D124" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="E124" s="10" t="s">
+      <c r="E124" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="39" customHeight="1">
-      <c r="A125" s="10" t="s">
+      <c r="A125" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B125" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D125" s="10" t="s">
+      <c r="B125" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D125" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E125" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="39" customHeight="1">
-      <c r="A126" s="10" t="s">
+      <c r="A126" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B126" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D126" s="10" t="s">
+      <c r="B126" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="E126" s="10" t="s">
+      <c r="E126" s="9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6796,399 +6755,399 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="18" style="4" customWidth="1"/>
-    <col min="3" max="3" width="42" style="4" customWidth="1"/>
-    <col min="4" max="4" width="18" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="4"/>
+    <col min="1" max="2" width="18" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27.6">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.6">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="41.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6" t="s">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6" t="s">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6" t="s">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7199,112 +7158,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>504</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="28.8">
-      <c r="A2" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.8">
-      <c r="A3" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8">
-      <c r="A5" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8">
-      <c r="A6" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E452D8F0-FE81-404E-AC8A-D24BCB4D7170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E882B29-8D8F-4340-93BD-992847BE78CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="23040" windowHeight="12204" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="561">
   <si>
     <t>date</t>
   </si>
@@ -1710,9 +1710,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://ojs.luminescience.cn/DMA/about/editorialTeam</t>
-  </si>
-  <si>
     <t>Decision Making and Analysis</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1726,6 +1723,18 @@
   </si>
   <si>
     <t>since Jun. 2022</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was invited to deliver a talk entitled "An Optimization-Driven Framework for Persuader Selection in Social Networks with Opinion Evolution" at the 8th Chinese Conference on Systems of Systems Engineering, Urumqi.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ojs.luminescience.cn/DMA/about/editorialTeam</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/GGR3Hbh0oWMYfosSp5cnUw</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1801,7 +1810,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1857,6 +1866,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2246,7 +2258,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E80">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="12"/>
@@ -2460,7 +2472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.45" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="12" customWidth="1"/>
@@ -2489,52 +2501,52 @@
     </row>
     <row r="2" spans="1:5" ht="54.45" customHeight="1">
       <c r="A2" s="17">
-        <v>46189</v>
+        <v>46242</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>554</v>
+        <v>558</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>560</v>
       </c>
       <c r="E2" s="16" t="str">
-        <f t="shared" ref="E2" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54.45" customHeight="1">
       <c r="A3" s="17">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>551</v>
+        <v>553</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>559</v>
       </c>
       <c r="E3" s="16" t="str">
-        <f>IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" ref="E3" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.45" customHeight="1">
       <c r="A4" s="17">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>551</v>
       </c>
       <c r="E4" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2543,68 +2555,68 @@
     </row>
     <row r="5" spans="1:5" ht="54.45" customHeight="1">
       <c r="A5" s="17">
-        <v>46168</v>
+        <v>46177</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="15"/>
+        <v>7</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>11</v>
+      <c r="A6" s="17">
+        <v>46168</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>14</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D6" s="15"/>
       <c r="E6" s="16" t="str">
-        <f t="shared" ref="E6:E15" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.45" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="E7" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E7:E16" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.45" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2613,16 +2625,16 @@
     </row>
     <row r="9" spans="1:5" ht="54.45" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="E9" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2631,16 +2643,16 @@
     </row>
     <row r="10" spans="1:5" ht="54.45" customHeight="1">
       <c r="A10" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="E10" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2649,16 +2661,16 @@
     </row>
     <row r="11" spans="1:5" ht="54.45" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="E11" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2667,16 +2679,16 @@
     </row>
     <row r="12" spans="1:5" ht="54.45" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2691,10 +2703,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2703,16 +2715,16 @@
     </row>
     <row r="14" spans="1:5" ht="54.45" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2721,16 +2733,16 @@
     </row>
     <row r="15" spans="1:5" ht="54.45" customHeight="1">
       <c r="A15" s="17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E15" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2739,52 +2751,52 @@
     </row>
     <row r="16" spans="1:5" ht="54.45" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E16" s="16" t="str">
-        <f t="shared" ref="E16:E25" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54.45" customHeight="1">
       <c r="A17" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E17" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E17:E26" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.45" customHeight="1">
       <c r="A18" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E18" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2793,16 +2805,16 @@
     </row>
     <row r="19" spans="1:5" ht="54.45" customHeight="1">
       <c r="A19" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E19" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2811,16 +2823,16 @@
     </row>
     <row r="20" spans="1:5" ht="54.45" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E20" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2835,10 +2847,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2847,16 +2859,16 @@
     </row>
     <row r="22" spans="1:5" ht="54.45" customHeight="1">
       <c r="A22" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E22" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2865,16 +2877,16 @@
     </row>
     <row r="23" spans="1:5" ht="54.45" customHeight="1">
       <c r="A23" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E23" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2883,16 +2895,16 @@
     </row>
     <row r="24" spans="1:5" ht="54.45" customHeight="1">
       <c r="A24" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>552</v>
+        <v>65</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="E24" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2907,10 +2919,10 @@
         <v>5</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>552</v>
       </c>
       <c r="E25" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2919,52 +2931,52 @@
     </row>
     <row r="26" spans="1:5" ht="54.45" customHeight="1">
       <c r="A26" s="17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E26" s="16" t="str">
-        <f t="shared" ref="E26:E35" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54.45" customHeight="1">
       <c r="A27" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E27" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E27:E36" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54.45" customHeight="1">
       <c r="A28" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E28" s="16" t="str">
         <f t="shared" si="3"/>
@@ -2973,16 +2985,16 @@
     </row>
     <row r="29" spans="1:5" ht="54.45" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E29" s="16" t="str">
         <f t="shared" si="3"/>
@@ -2991,16 +3003,16 @@
     </row>
     <row r="30" spans="1:5" ht="54.45" customHeight="1">
       <c r="A30" s="17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="E30" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3009,16 +3021,16 @@
     </row>
     <row r="31" spans="1:5" ht="54.45" customHeight="1">
       <c r="A31" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E31" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3027,16 +3039,16 @@
     </row>
     <row r="32" spans="1:5" ht="54.45" customHeight="1">
       <c r="A32" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E32" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3045,16 +3057,16 @@
     </row>
     <row r="33" spans="1:5" ht="54.45" customHeight="1">
       <c r="A33" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E33" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3063,16 +3075,16 @@
     </row>
     <row r="34" spans="1:5" ht="54.45" customHeight="1">
       <c r="A34" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E34" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3081,16 +3093,16 @@
     </row>
     <row r="35" spans="1:5" ht="54.45" customHeight="1">
       <c r="A35" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E35" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3099,52 +3111,52 @@
     </row>
     <row r="36" spans="1:5" ht="54.45" customHeight="1">
       <c r="A36" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E36" s="16" t="str">
-        <f t="shared" ref="E36:E53" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="54.45" customHeight="1">
       <c r="A37" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E37" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E37:E54" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="54.45" customHeight="1">
       <c r="A38" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E38" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3153,16 +3165,16 @@
     </row>
     <row r="39" spans="1:5" ht="54.45" customHeight="1">
       <c r="A39" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E39" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3171,16 +3183,16 @@
     </row>
     <row r="40" spans="1:5" ht="54.45" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E40" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3188,17 +3200,17 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A41" s="17">
-        <v>45597</v>
+      <c r="A41" s="17" t="s">
+        <v>108</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E41" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3207,15 +3219,17 @@
     </row>
     <row r="42" spans="1:5" ht="54.45" customHeight="1">
       <c r="A42" s="17">
-        <v>45593</v>
+        <v>45597</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42" s="15"/>
+        <v>111</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="E42" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3223,17 +3237,15 @@
     </row>
     <row r="43" spans="1:5" ht="54.45" customHeight="1">
       <c r="A43" s="17">
-        <v>45585</v>
+        <v>45593</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>115</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D43" s="15"/>
       <c r="E43" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3241,16 +3253,16 @@
     </row>
     <row r="44" spans="1:5" ht="54.45" customHeight="1">
       <c r="A44" s="17">
-        <v>45584</v>
+        <v>45585</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E44" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3259,16 +3271,16 @@
     </row>
     <row r="45" spans="1:5" ht="54.45" customHeight="1">
       <c r="A45" s="17">
-        <v>45583</v>
+        <v>45584</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E45" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3276,17 +3288,17 @@
       </c>
     </row>
     <row r="46" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A46" s="17" t="s">
-        <v>120</v>
+      <c r="A46" s="17">
+        <v>45583</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="E46" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3294,34 +3306,34 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A47" s="17">
-        <v>45580</v>
+      <c r="A47" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D47" s="15"/>
+        <v>121</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="E47" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A48" s="17" t="s">
-        <v>123</v>
+      <c r="A48" s="17">
+        <v>45580</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>125</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D48" s="15"/>
       <c r="E48" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3329,16 +3341,16 @@
     </row>
     <row r="49" spans="1:5" ht="54.45" customHeight="1">
       <c r="A49" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E49" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3347,16 +3359,16 @@
     </row>
     <row r="50" spans="1:5" ht="54.45" customHeight="1">
       <c r="A50" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="E50" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3364,17 +3376,17 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A51" s="17">
-        <v>45514</v>
+      <c r="A51" s="17" t="s">
+        <v>129</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="E51" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3382,17 +3394,17 @@
       </c>
     </row>
     <row r="52" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A52" s="17" t="s">
-        <v>134</v>
+      <c r="A52" s="17">
+        <v>45514</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E52" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3400,17 +3412,17 @@
       </c>
     </row>
     <row r="53" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A53" s="17">
-        <v>45432</v>
+      <c r="A53" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>136</v>
       </c>
       <c r="E53" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3418,53 +3430,53 @@
       </c>
     </row>
     <row r="54" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A54" s="17" t="s">
-        <v>139</v>
+      <c r="A54" s="17">
+        <v>45432</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>138</v>
       </c>
       <c r="E54" s="16" t="str">
-        <f t="shared" ref="E54:E67" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="54.45" customHeight="1">
       <c r="A55" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B55" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E55" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E55:E68" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54.45" customHeight="1">
       <c r="A56" s="17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E56" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3473,16 +3485,16 @@
     </row>
     <row r="57" spans="1:5" ht="54.45" customHeight="1">
       <c r="A57" s="17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E57" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3491,16 +3503,16 @@
     </row>
     <row r="58" spans="1:5" ht="54.45" customHeight="1">
       <c r="A58" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E58" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3508,34 +3520,34 @@
       </c>
     </row>
     <row r="59" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A59" s="17">
-        <v>45264</v>
+      <c r="A59" s="17" t="s">
+        <v>151</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D59" s="15"/>
+        <v>152</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>153</v>
+      </c>
       <c r="E59" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A60" s="17" t="s">
-        <v>155</v>
+      <c r="A60" s="17">
+        <v>45264</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>157</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D60" s="15"/>
       <c r="E60" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
@@ -3543,16 +3555,16 @@
     </row>
     <row r="61" spans="1:5" ht="54.45" customHeight="1">
       <c r="A61" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="E61" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3561,13 +3573,13 @@
     </row>
     <row r="62" spans="1:5" ht="54.45" customHeight="1">
       <c r="A62" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>45</v>
@@ -3578,17 +3590,17 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A63" s="17">
-        <v>45118</v>
+      <c r="A63" s="17" t="s">
+        <v>160</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="E63" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3596,17 +3608,17 @@
       </c>
     </row>
     <row r="64" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A64" s="17" t="s">
-        <v>164</v>
+      <c r="A64" s="17">
+        <v>45118</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E64" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3615,16 +3627,16 @@
     </row>
     <row r="65" spans="1:5" ht="54.45" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E65" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3632,16 +3644,18 @@
       </c>
     </row>
     <row r="66" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A66" s="17">
-        <v>45023</v>
+      <c r="A66" s="17" t="s">
+        <v>167</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D66" s="15"/>
+        <v>168</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>169</v>
+      </c>
       <c r="E66" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
@@ -3649,13 +3663,13 @@
     </row>
     <row r="67" spans="1:5" ht="54.45" customHeight="1">
       <c r="A67" s="17">
-        <v>45006</v>
+        <v>45023</v>
       </c>
       <c r="B67" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D67" s="15"/>
       <c r="E67" s="16" t="str">
@@ -3664,53 +3678,51 @@
       </c>
     </row>
     <row r="68" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A68" s="17" t="s">
-        <v>172</v>
+      <c r="A68" s="17">
+        <v>45006</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>174</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="D68" s="15"/>
       <c r="E68" s="16" t="str">
-        <f t="shared" ref="E68:E79" si="6">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="54.45" customHeight="1">
       <c r="A69" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B69" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E69" s="16" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E69:E80" si="6">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="54.45" customHeight="1">
       <c r="A70" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B70" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E70" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3719,16 +3731,16 @@
     </row>
     <row r="71" spans="1:5" ht="54.45" customHeight="1">
       <c r="A71" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B71" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E71" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3736,17 +3748,17 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A72" s="17">
-        <v>44945</v>
+      <c r="A72" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E72" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3754,17 +3766,17 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A73" s="17" t="s">
-        <v>186</v>
+      <c r="A73" s="17">
+        <v>44945</v>
       </c>
       <c r="B73" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="E73" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3773,16 +3785,16 @@
     </row>
     <row r="74" spans="1:5" ht="54.45" customHeight="1">
       <c r="A74" s="17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="E74" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3791,16 +3803,16 @@
     </row>
     <row r="75" spans="1:5" ht="54.45" customHeight="1">
       <c r="A75" s="17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="E75" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3809,13 +3821,13 @@
     </row>
     <row r="76" spans="1:5" ht="54.45" customHeight="1">
       <c r="A76" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>45</v>
@@ -3827,16 +3839,16 @@
     </row>
     <row r="77" spans="1:5" ht="54.45" customHeight="1">
       <c r="A77" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="E77" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3845,16 +3857,16 @@
     </row>
     <row r="78" spans="1:5" ht="54.45" customHeight="1">
       <c r="A78" s="17" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B78" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E78" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3863,18 +3875,36 @@
     </row>
     <row r="79" spans="1:5" ht="54.45" customHeight="1">
       <c r="A79" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E79" s="16" t="str">
+        <f t="shared" si="6"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A80" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B80" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C80" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="D79" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" s="16" t="str">
+      <c r="D80" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
@@ -4914,7 +4944,7 @@
         <v>396</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="39" customHeight="1">
@@ -4942,13 +4972,13 @@
         <v>379</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>555</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1">
@@ -4982,7 +5012,7 @@
         <v>401</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" customHeight="1">

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E882B29-8D8F-4340-93BD-992847BE78CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768CAE57-234B-4FE0-9BE5-E0F7CD68802C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="565">
   <si>
     <t>date</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>Group</t>
-  </si>
-  <si>
-    <t>Congratulations to Zhuolin Li on successfully completing her Ph.D. thesis defense.</t>
   </si>
   <si>
     <t>https://mp.weixin.qq.com/s/GyFnl6HYnp43uVc8vZzroA</t>
@@ -1735,6 +1732,26 @@
   </si>
   <si>
     <t>https://mp.weixin.qq.com/s/GGR3Hbh0oWMYfosSp5cnUw</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Patterns (SCI)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A paper titled "A unified framework for clustering-oriented granular-ball quality assessment based on fuzzy information granules" was accepted by the 2026 International Conference of Granular-Ball Computing (ICGBC 2026).</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>206-08-25</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Congratulations to Zhuolin Li on successfully completing her Ph.D. thesis defense.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A new research project was granted by the National Natural Science Foundation of China (NSFC). Congratulations to Zhuolin Li.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2258,7 +2275,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NewsTable" displayName="NewsTable" ref="A1:E82">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category" dataDxfId="12"/>
@@ -2299,7 +2316,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ServicesTable" displayName="ServicesTable" ref="A1:E127">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="category" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="role" dataDxfId="7"/>
@@ -2472,7 +2489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.45" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="12" customWidth="1"/>
@@ -2500,17 +2517,14 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A2" s="17">
-        <v>46242</v>
+      <c r="A2" s="12" t="s">
+        <v>562</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>558</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E2" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2519,34 +2533,32 @@
     </row>
     <row r="3" spans="1:5" ht="54.45" customHeight="1">
       <c r="A3" s="17">
-        <v>46189</v>
+        <v>46253</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>559</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="D3" s="18"/>
       <c r="E3" s="16" t="str">
-        <f t="shared" ref="E3" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.45" customHeight="1">
       <c r="A4" s="17">
-        <v>46184</v>
+        <v>46242</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>551</v>
+        <v>557</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>559</v>
       </c>
       <c r="E4" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2555,104 +2567,104 @@
     </row>
     <row r="5" spans="1:5" ht="54.45" customHeight="1">
       <c r="A5" s="17">
-        <v>46177</v>
+        <v>46189</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>8</v>
+        <v>552</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>558</v>
       </c>
       <c r="E5" s="16" t="str">
-        <f>IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" ref="E5" si="0">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.45" customHeight="1">
       <c r="A6" s="17">
-        <v>46168</v>
+        <v>46184</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15"/>
+        <v>6</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>550</v>
+      </c>
       <c r="E6" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>11</v>
+      <c r="A7" s="17">
+        <v>46177</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="E7" s="16" t="str">
-        <f t="shared" ref="E7:E16" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A8" s="17" t="s">
-        <v>15</v>
+      <c r="A8" s="17">
+        <v>46168</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D8" s="15"/>
       <c r="E8" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.45" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="E9" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E9:E18" si="1">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>yes</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.45" customHeight="1">
       <c r="A10" s="17" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="E10" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2661,16 +2673,16 @@
     </row>
     <row r="11" spans="1:5" ht="54.45" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E11" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2679,16 +2691,16 @@
     </row>
     <row r="12" spans="1:5" ht="54.45" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E12" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2697,16 +2709,16 @@
     </row>
     <row r="13" spans="1:5" ht="54.45" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>34</v>
+        <v>27</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="E13" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2715,16 +2727,16 @@
     </row>
     <row r="14" spans="1:5" ht="54.45" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E14" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2733,16 +2745,16 @@
     </row>
     <row r="15" spans="1:5" ht="54.45" customHeight="1">
       <c r="A15" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E15" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2751,16 +2763,16 @@
     </row>
     <row r="16" spans="1:5" ht="54.45" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2769,70 +2781,70 @@
     </row>
     <row r="17" spans="1:5" ht="54.45" customHeight="1">
       <c r="A17" s="17" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E17" s="16" t="str">
-        <f t="shared" ref="E17:E26" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.45" customHeight="1">
       <c r="A18" s="17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E18" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>no</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54.45" customHeight="1">
       <c r="A19" s="17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E19" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E19:E28" si="2">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54.45" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E20" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2841,16 +2853,16 @@
     </row>
     <row r="21" spans="1:5" ht="54.45" customHeight="1">
       <c r="A21" s="17" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E21" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2859,16 +2871,16 @@
     </row>
     <row r="22" spans="1:5" ht="54.45" customHeight="1">
       <c r="A22" s="17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>59</v>
+        <v>563</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E22" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2877,16 +2889,16 @@
     </row>
     <row r="23" spans="1:5" ht="54.45" customHeight="1">
       <c r="A23" s="17" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E23" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2895,16 +2907,16 @@
     </row>
     <row r="24" spans="1:5" ht="54.45" customHeight="1">
       <c r="A24" s="17" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E24" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2913,16 +2925,16 @@
     </row>
     <row r="25" spans="1:5" ht="54.45" customHeight="1">
       <c r="A25" s="17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>552</v>
+        <v>61</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="E25" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2931,16 +2943,16 @@
     </row>
     <row r="26" spans="1:5" ht="54.45" customHeight="1">
       <c r="A26" s="17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E26" s="16" t="str">
         <f t="shared" si="2"/>
@@ -2949,70 +2961,70 @@
     </row>
     <row r="27" spans="1:5" ht="54.45" customHeight="1">
       <c r="A27" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>551</v>
       </c>
       <c r="E27" s="16" t="str">
-        <f t="shared" ref="E27:E36" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54.45" customHeight="1">
       <c r="A28" s="17" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E28" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>no</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54.45" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E29" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E29:E38" si="3">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="54.45" customHeight="1">
       <c r="A30" s="17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="E30" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3021,16 +3033,16 @@
     </row>
     <row r="31" spans="1:5" ht="54.45" customHeight="1">
       <c r="A31" s="17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E31" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3039,16 +3051,16 @@
     </row>
     <row r="32" spans="1:5" ht="54.45" customHeight="1">
       <c r="A32" s="17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E32" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3057,16 +3069,16 @@
     </row>
     <row r="33" spans="1:5" ht="54.45" customHeight="1">
       <c r="A33" s="17" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="E33" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3075,16 +3087,16 @@
     </row>
     <row r="34" spans="1:5" ht="54.45" customHeight="1">
       <c r="A34" s="17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="E34" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3093,16 +3105,16 @@
     </row>
     <row r="35" spans="1:5" ht="54.45" customHeight="1">
       <c r="A35" s="17" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E35" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3111,16 +3123,16 @@
     </row>
     <row r="36" spans="1:5" ht="54.45" customHeight="1">
       <c r="A36" s="17" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E36" s="16" t="str">
         <f t="shared" si="3"/>
@@ -3129,70 +3141,70 @@
     </row>
     <row r="37" spans="1:5" ht="54.45" customHeight="1">
       <c r="A37" s="17" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E37" s="16" t="str">
-        <f t="shared" ref="E37:E54" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="54.45" customHeight="1">
       <c r="A38" s="17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E38" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>no</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="54.45" customHeight="1">
       <c r="A39" s="17" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E39" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E39:E56" si="4">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="54.45" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E40" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3201,16 +3213,16 @@
     </row>
     <row r="41" spans="1:5" ht="54.45" customHeight="1">
       <c r="A41" s="17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E41" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3218,17 +3230,17 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A42" s="17">
-        <v>45597</v>
+      <c r="A42" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E42" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3236,16 +3248,18 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A43" s="17">
-        <v>45593</v>
+      <c r="A43" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" s="15"/>
+        <v>108</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>109</v>
+      </c>
       <c r="E43" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3253,16 +3267,16 @@
     </row>
     <row r="44" spans="1:5" ht="54.45" customHeight="1">
       <c r="A44" s="17">
-        <v>45585</v>
+        <v>45597</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E44" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3271,17 +3285,15 @@
     </row>
     <row r="45" spans="1:5" ht="54.45" customHeight="1">
       <c r="A45" s="17">
-        <v>45584</v>
+        <v>45593</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>117</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D45" s="15"/>
       <c r="E45" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3289,16 +3301,16 @@
     </row>
     <row r="46" spans="1:5" ht="54.45" customHeight="1">
       <c r="A46" s="17">
-        <v>45583</v>
+        <v>45585</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E46" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3306,17 +3318,17 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A47" s="17" t="s">
-        <v>120</v>
+      <c r="A47" s="17">
+        <v>45584</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="E47" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3325,15 +3337,17 @@
     </row>
     <row r="48" spans="1:5" ht="54.45" customHeight="1">
       <c r="A48" s="17">
-        <v>45580</v>
+        <v>45583</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="15"/>
+        <v>117</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="E48" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3341,16 +3355,16 @@
     </row>
     <row r="49" spans="1:5" ht="54.45" customHeight="1">
       <c r="A49" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="E49" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3358,18 +3372,16 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A50" s="17" t="s">
-        <v>126</v>
+      <c r="A50" s="17">
+        <v>45580</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>128</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D50" s="15"/>
       <c r="E50" s="16" t="str">
         <f t="shared" si="4"/>
         <v>no</v>
@@ -3377,16 +3389,16 @@
     </row>
     <row r="51" spans="1:5" ht="54.45" customHeight="1">
       <c r="A51" s="17" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="E51" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3394,17 +3406,17 @@
       </c>
     </row>
     <row r="52" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A52" s="17">
-        <v>45514</v>
+      <c r="A52" s="17" t="s">
+        <v>125</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E52" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3413,16 +3425,16 @@
     </row>
     <row r="53" spans="1:5" ht="54.45" customHeight="1">
       <c r="A53" s="17" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="E53" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3431,16 +3443,16 @@
     </row>
     <row r="54" spans="1:5" ht="54.45" customHeight="1">
       <c r="A54" s="17">
-        <v>45432</v>
+        <v>45514</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>138</v>
+        <v>131</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="E54" s="16" t="str">
         <f t="shared" si="4"/>
@@ -3449,70 +3461,70 @@
     </row>
     <row r="55" spans="1:5" ht="54.45" customHeight="1">
       <c r="A55" s="17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E55" s="16" t="str">
-        <f t="shared" ref="E55:E68" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A56" s="17" t="s">
-        <v>142</v>
+      <c r="A56" s="17">
+        <v>45432</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>144</v>
+        <v>136</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>137</v>
       </c>
       <c r="E56" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>no</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="54.45" customHeight="1">
       <c r="A57" s="17" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B57" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E57" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E57:E70" si="5">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="54.45" customHeight="1">
       <c r="A58" s="17" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E58" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3521,16 +3533,16 @@
     </row>
     <row r="59" spans="1:5" ht="54.45" customHeight="1">
       <c r="A59" s="17" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E59" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3538,16 +3550,18 @@
       </c>
     </row>
     <row r="60" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A60" s="17">
-        <v>45264</v>
+      <c r="A60" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" s="15"/>
+        <v>148</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>149</v>
+      </c>
       <c r="E60" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
@@ -3555,16 +3569,16 @@
     </row>
     <row r="61" spans="1:5" ht="54.45" customHeight="1">
       <c r="A61" s="17" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E61" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3572,18 +3586,16 @@
       </c>
     </row>
     <row r="62" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A62" s="17" t="s">
-        <v>158</v>
+      <c r="A62" s="17">
+        <v>45264</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>45</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="D62" s="15"/>
       <c r="E62" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
@@ -3591,16 +3603,16 @@
     </row>
     <row r="63" spans="1:5" ht="54.45" customHeight="1">
       <c r="A63" s="17" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="E63" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3608,17 +3620,17 @@
       </c>
     </row>
     <row r="64" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A64" s="17">
-        <v>45118</v>
+      <c r="A64" s="17" t="s">
+        <v>157</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="E64" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3627,16 +3639,16 @@
     </row>
     <row r="65" spans="1:5" ht="54.45" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="E65" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3644,17 +3656,17 @@
       </c>
     </row>
     <row r="66" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A66" s="17" t="s">
-        <v>167</v>
+      <c r="A66" s="17">
+        <v>45118</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E66" s="16" t="str">
         <f t="shared" si="5"/>
@@ -3662,103 +3674,103 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A67" s="17">
-        <v>45023</v>
+      <c r="A67" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D67" s="15"/>
+        <v>164</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>165</v>
+      </c>
       <c r="E67" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A68" s="17">
-        <v>45006</v>
+      <c r="A68" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D68" s="15"/>
+        <v>167</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>168</v>
+      </c>
       <c r="E68" s="16" t="str">
         <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A69" s="17" t="s">
-        <v>172</v>
+      <c r="A69" s="17">
+        <v>45023</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>174</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="D69" s="15"/>
       <c r="E69" s="16" t="str">
-        <f t="shared" ref="E69:E80" si="6">IF(ROW()-1&lt;11,"yes","no")</f>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A70" s="17" t="s">
-        <v>175</v>
+      <c r="A70" s="17">
+        <v>45006</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>177</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D70" s="15"/>
       <c r="E70" s="16" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>no</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="54.45" customHeight="1">
       <c r="A71" s="17" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B71" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E71" s="16" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E71:E82" si="6">IF(ROW()-1&lt;11,"yes","no")</f>
         <v>no</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="54.45" customHeight="1">
       <c r="A72" s="17" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E72" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3766,17 +3778,17 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A73" s="17">
-        <v>44945</v>
+      <c r="A73" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E73" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3785,16 +3797,16 @@
     </row>
     <row r="74" spans="1:5" ht="54.45" customHeight="1">
       <c r="A74" s="17" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="E74" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3802,17 +3814,17 @@
       </c>
     </row>
     <row r="75" spans="1:5" ht="54.45" customHeight="1">
-      <c r="A75" s="17" t="s">
-        <v>188</v>
+      <c r="A75" s="17">
+        <v>44945</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E75" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3821,16 +3833,16 @@
     </row>
     <row r="76" spans="1:5" ht="54.45" customHeight="1">
       <c r="A76" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E76" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3839,16 +3851,16 @@
     </row>
     <row r="77" spans="1:5" ht="54.45" customHeight="1">
       <c r="A77" s="17" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="E77" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3857,16 +3869,16 @@
     </row>
     <row r="78" spans="1:5" ht="54.45" customHeight="1">
       <c r="A78" s="17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="E78" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3875,16 +3887,16 @@
     </row>
     <row r="79" spans="1:5" ht="54.45" customHeight="1">
       <c r="A79" s="17" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="E79" s="16" t="str">
         <f t="shared" si="6"/>
@@ -3893,18 +3905,54 @@
     </row>
     <row r="80" spans="1:5" ht="54.45" customHeight="1">
       <c r="A80" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E80" s="16" t="str">
+        <f t="shared" si="6"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A81" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E81" s="16" t="str">
+        <f t="shared" si="6"/>
+        <v>no</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="54.45" customHeight="1">
+      <c r="A82" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E80" s="16" t="str">
+      <c r="D82" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E82" s="16" t="str">
         <f t="shared" si="6"/>
         <v>no</v>
       </c>
@@ -3930,13 +3978,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="10" customFormat="1" ht="28.8">
@@ -3944,40 +3992,40 @@
         <v>2026</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8">
       <c r="A4" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.2">
       <c r="A5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>45</v>
@@ -3985,90 +4033,90 @@
     </row>
     <row r="6" spans="1:3" ht="28.8">
       <c r="A6" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8">
       <c r="A8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="43.2">
       <c r="A10" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.2">
       <c r="A12" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="28.8">
       <c r="A13" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -4093,531 +4141,531 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="57.6">
       <c r="A2" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="57.6">
       <c r="A3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2">
       <c r="A4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2">
       <c r="A5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2">
       <c r="A6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
       <c r="A7" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2">
       <c r="A8" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2">
       <c r="A9" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2">
       <c r="A10" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43.2">
       <c r="A11" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2">
       <c r="A12" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="57.6">
       <c r="A13" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.2">
       <c r="A14" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="43.2">
       <c r="A15" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8">
       <c r="A16" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8">
       <c r="A17" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="57.6">
       <c r="A18" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8">
       <c r="A19" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8">
       <c r="A20" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.2">
       <c r="A21" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="43.2">
       <c r="A22" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="43.2">
       <c r="A23" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4631,7 +4679,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" style="7" customWidth="1"/>
@@ -4646,387 +4694,387 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="39" customHeight="1">
       <c r="A2" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>359</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="39" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="39" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="39" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>367</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="39" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>369</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="39" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>373</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="39" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>375</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="39" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>378</v>
-      </c>
       <c r="D10" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="39" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>380</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="39" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>383</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="39" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>386</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="39" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>389</v>
-      </c>
       <c r="D14" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="39" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>390</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="39" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="39" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="39" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>396</v>
-      </c>
       <c r="D18" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="39" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="39" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>554</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>399</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="39" customHeight="1">
       <c r="A22" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>358</v>
-      </c>
       <c r="C22" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="39" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>403</v>
-      </c>
       <c r="D23" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>45</v>
@@ -5034,16 +5082,16 @@
     </row>
     <row r="24" spans="1:5" ht="39" customHeight="1">
       <c r="A24" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>404</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>405</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>45</v>
@@ -5051,7 +5099,7 @@
     </row>
     <row r="25" spans="1:5" ht="39" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>45</v>
@@ -5060,7 +5108,7 @@
         <v>45</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>45</v>
@@ -5068,7 +5116,7 @@
     </row>
     <row r="26" spans="1:5" ht="39" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>45</v>
@@ -5077,7 +5125,7 @@
         <v>45</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>45</v>
@@ -5085,7 +5133,7 @@
     </row>
     <row r="27" spans="1:5" ht="39" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>45</v>
@@ -5094,7 +5142,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>45</v>
@@ -5102,7 +5150,7 @@
     </row>
     <row r="28" spans="1:5" ht="39" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>45</v>
@@ -5111,7 +5159,7 @@
         <v>45</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>45</v>
@@ -5119,7 +5167,7 @@
     </row>
     <row r="29" spans="1:5" ht="39" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>45</v>
@@ -5128,7 +5176,7 @@
         <v>45</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>45</v>
@@ -5136,7 +5184,7 @@
     </row>
     <row r="30" spans="1:5" ht="39" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>45</v>
@@ -5145,7 +5193,7 @@
         <v>45</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>45</v>
@@ -5153,7 +5201,7 @@
     </row>
     <row r="31" spans="1:5" ht="39" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>45</v>
@@ -5162,7 +5210,7 @@
         <v>45</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>45</v>
@@ -5170,7 +5218,7 @@
     </row>
     <row r="32" spans="1:5" ht="39" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>45</v>
@@ -5179,7 +5227,7 @@
         <v>45</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>45</v>
@@ -5187,7 +5235,7 @@
     </row>
     <row r="33" spans="1:5" ht="39" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>45</v>
@@ -5196,7 +5244,7 @@
         <v>45</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>45</v>
@@ -5204,7 +5252,7 @@
     </row>
     <row r="34" spans="1:5" ht="39" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>45</v>
@@ -5213,7 +5261,7 @@
         <v>45</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>45</v>
@@ -5221,7 +5269,7 @@
     </row>
     <row r="35" spans="1:5" ht="39" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>45</v>
@@ -5230,7 +5278,7 @@
         <v>45</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>45</v>
@@ -5238,7 +5286,7 @@
     </row>
     <row r="36" spans="1:5" ht="39" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>45</v>
@@ -5247,7 +5295,7 @@
         <v>45</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>45</v>
@@ -5255,7 +5303,7 @@
     </row>
     <row r="37" spans="1:5" ht="39" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>45</v>
@@ -5264,7 +5312,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>45</v>
@@ -5272,7 +5320,7 @@
     </row>
     <row r="38" spans="1:5" ht="39" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>45</v>
@@ -5281,7 +5329,7 @@
         <v>45</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>45</v>
@@ -5289,16 +5337,16 @@
     </row>
     <row r="39" spans="1:5" ht="39" customHeight="1">
       <c r="A39" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>420</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>421</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>45</v>
@@ -5306,7 +5354,7 @@
     </row>
     <row r="40" spans="1:5" ht="39" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>45</v>
@@ -5315,7 +5363,7 @@
         <v>45</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>45</v>
@@ -5323,7 +5371,7 @@
     </row>
     <row r="41" spans="1:5" ht="39" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>45</v>
@@ -5332,7 +5380,7 @@
         <v>45</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>45</v>
@@ -5340,7 +5388,7 @@
     </row>
     <row r="42" spans="1:5" ht="39" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>45</v>
@@ -5349,7 +5397,7 @@
         <v>45</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>45</v>
@@ -5357,7 +5405,7 @@
     </row>
     <row r="43" spans="1:5" ht="39" customHeight="1">
       <c r="A43" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>45</v>
@@ -5366,7 +5414,7 @@
         <v>45</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>45</v>
@@ -5374,7 +5422,7 @@
     </row>
     <row r="44" spans="1:5" ht="39" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>45</v>
@@ -5383,7 +5431,7 @@
         <v>45</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>45</v>
@@ -5391,7 +5439,7 @@
     </row>
     <row r="45" spans="1:5" ht="39" customHeight="1">
       <c r="A45" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>45</v>
@@ -5400,7 +5448,7 @@
         <v>45</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>45</v>
@@ -5408,7 +5456,7 @@
     </row>
     <row r="46" spans="1:5" ht="39" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>45</v>
@@ -5417,7 +5465,7 @@
         <v>45</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>45</v>
@@ -5425,7 +5473,7 @@
     </row>
     <row r="47" spans="1:5" ht="39" customHeight="1">
       <c r="A47" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>45</v>
@@ -5434,7 +5482,7 @@
         <v>45</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>45</v>
@@ -5442,7 +5490,7 @@
     </row>
     <row r="48" spans="1:5" ht="39" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>45</v>
@@ -5451,7 +5499,7 @@
         <v>45</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>45</v>
@@ -5459,7 +5507,7 @@
     </row>
     <row r="49" spans="1:5" ht="39" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>45</v>
@@ -5468,7 +5516,7 @@
         <v>45</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>45</v>
@@ -5476,7 +5524,7 @@
     </row>
     <row r="50" spans="1:5" ht="39" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>45</v>
@@ -5485,7 +5533,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>45</v>
@@ -5493,7 +5541,7 @@
     </row>
     <row r="51" spans="1:5" ht="39" customHeight="1">
       <c r="A51" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>45</v>
@@ -5502,7 +5550,7 @@
         <v>45</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>45</v>
@@ -5510,7 +5558,7 @@
     </row>
     <row r="52" spans="1:5" ht="39" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>45</v>
@@ -5519,7 +5567,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>45</v>
@@ -5527,7 +5575,7 @@
     </row>
     <row r="53" spans="1:5" ht="39" customHeight="1">
       <c r="A53" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>45</v>
@@ -5536,7 +5584,7 @@
         <v>45</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>45</v>
@@ -5544,7 +5592,7 @@
     </row>
     <row r="54" spans="1:5" ht="39" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>45</v>
@@ -5553,7 +5601,7 @@
         <v>45</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>45</v>
@@ -5561,7 +5609,7 @@
     </row>
     <row r="55" spans="1:5" ht="39" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>45</v>
@@ -5570,7 +5618,7 @@
         <v>45</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>45</v>
@@ -5578,7 +5626,7 @@
     </row>
     <row r="56" spans="1:5" ht="39" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>45</v>
@@ -5587,7 +5635,7 @@
         <v>45</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>45</v>
@@ -5595,7 +5643,7 @@
     </row>
     <row r="57" spans="1:5" ht="39" customHeight="1">
       <c r="A57" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>45</v>
@@ -5604,7 +5652,7 @@
         <v>45</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>45</v>
@@ -5612,7 +5660,7 @@
     </row>
     <row r="58" spans="1:5" ht="39" customHeight="1">
       <c r="A58" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>45</v>
@@ -5621,7 +5669,7 @@
         <v>45</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>45</v>
@@ -5629,7 +5677,7 @@
     </row>
     <row r="59" spans="1:5" ht="39" customHeight="1">
       <c r="A59" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>45</v>
@@ -5638,7 +5686,7 @@
         <v>45</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>45</v>
@@ -5646,7 +5694,7 @@
     </row>
     <row r="60" spans="1:5" ht="39" customHeight="1">
       <c r="A60" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>45</v>
@@ -5655,7 +5703,7 @@
         <v>45</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>45</v>
@@ -5663,7 +5711,7 @@
     </row>
     <row r="61" spans="1:5" ht="39" customHeight="1">
       <c r="A61" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>45</v>
@@ -5672,7 +5720,7 @@
         <v>45</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>45</v>
@@ -5680,7 +5728,7 @@
     </row>
     <row r="62" spans="1:5" ht="39" customHeight="1">
       <c r="A62" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>45</v>
@@ -5689,7 +5737,7 @@
         <v>45</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>45</v>
@@ -5697,7 +5745,7 @@
     </row>
     <row r="63" spans="1:5" ht="39" customHeight="1">
       <c r="A63" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>45</v>
@@ -5706,7 +5754,7 @@
         <v>45</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>45</v>
@@ -5714,7 +5762,7 @@
     </row>
     <row r="64" spans="1:5" ht="39" customHeight="1">
       <c r="A64" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>45</v>
@@ -5723,7 +5771,7 @@
         <v>45</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>45</v>
@@ -5731,7 +5779,7 @@
     </row>
     <row r="65" spans="1:5" ht="39" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>45</v>
@@ -5740,7 +5788,7 @@
         <v>45</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>45</v>
@@ -5748,7 +5796,7 @@
     </row>
     <row r="66" spans="1:5" ht="39" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>45</v>
@@ -5757,7 +5805,7 @@
         <v>45</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>45</v>
@@ -5765,7 +5813,7 @@
     </row>
     <row r="67" spans="1:5" ht="39" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>45</v>
@@ -5774,7 +5822,7 @@
         <v>45</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>45</v>
@@ -5782,7 +5830,7 @@
     </row>
     <row r="68" spans="1:5" ht="39" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>45</v>
@@ -5791,7 +5839,7 @@
         <v>45</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>45</v>
@@ -5799,7 +5847,7 @@
     </row>
     <row r="69" spans="1:5" ht="39" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>45</v>
@@ -5808,7 +5856,7 @@
         <v>45</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>45</v>
@@ -5816,7 +5864,7 @@
     </row>
     <row r="70" spans="1:5" ht="39" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>45</v>
@@ -5825,7 +5873,7 @@
         <v>45</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>45</v>
@@ -5833,7 +5881,7 @@
     </row>
     <row r="71" spans="1:5" ht="39" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>45</v>
@@ -5842,7 +5890,7 @@
         <v>45</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>45</v>
@@ -5850,7 +5898,7 @@
     </row>
     <row r="72" spans="1:5" ht="39" customHeight="1">
       <c r="A72" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>45</v>
@@ -5859,7 +5907,7 @@
         <v>45</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>45</v>
@@ -5867,7 +5915,7 @@
     </row>
     <row r="73" spans="1:5" ht="39" customHeight="1">
       <c r="A73" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>45</v>
@@ -5876,7 +5924,7 @@
         <v>45</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>45</v>
@@ -5884,7 +5932,7 @@
     </row>
     <row r="74" spans="1:5" ht="39" customHeight="1">
       <c r="A74" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>45</v>
@@ -5893,7 +5941,7 @@
         <v>45</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>45</v>
@@ -5901,7 +5949,7 @@
     </row>
     <row r="75" spans="1:5" ht="39" customHeight="1">
       <c r="A75" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>45</v>
@@ -5910,7 +5958,7 @@
         <v>45</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>45</v>
@@ -5918,7 +5966,7 @@
     </row>
     <row r="76" spans="1:5" ht="39" customHeight="1">
       <c r="A76" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>45</v>
@@ -5927,7 +5975,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>45</v>
@@ -5935,7 +5983,7 @@
     </row>
     <row r="77" spans="1:5" ht="39" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>45</v>
@@ -5944,7 +5992,7 @@
         <v>45</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>45</v>
@@ -5952,7 +6000,7 @@
     </row>
     <row r="78" spans="1:5" ht="39" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>45</v>
@@ -5961,7 +6009,7 @@
         <v>45</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>45</v>
@@ -5969,7 +6017,7 @@
     </row>
     <row r="79" spans="1:5" ht="39" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>45</v>
@@ -5978,7 +6026,7 @@
         <v>45</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>45</v>
@@ -5986,7 +6034,7 @@
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>45</v>
@@ -5995,7 +6043,7 @@
         <v>45</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>45</v>
@@ -6003,7 +6051,7 @@
     </row>
     <row r="81" spans="1:5" ht="39" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>45</v>
@@ -6012,7 +6060,7 @@
         <v>45</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>45</v>
@@ -6020,7 +6068,7 @@
     </row>
     <row r="82" spans="1:5" ht="39" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>45</v>
@@ -6029,7 +6077,7 @@
         <v>45</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>45</v>
@@ -6037,7 +6085,7 @@
     </row>
     <row r="83" spans="1:5" ht="39" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>45</v>
@@ -6046,7 +6094,7 @@
         <v>45</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>45</v>
@@ -6054,24 +6102,18 @@
     </row>
     <row r="84" spans="1:5" ht="39" customHeight="1">
       <c r="A84" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>45</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
       <c r="D84" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>45</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="E84" s="9"/>
     </row>
     <row r="85" spans="1:5" ht="39" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>45</v>
@@ -6080,7 +6122,7 @@
         <v>45</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>45</v>
@@ -6088,7 +6130,7 @@
     </row>
     <row r="86" spans="1:5" ht="39" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>45</v>
@@ -6097,7 +6139,7 @@
         <v>45</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>45</v>
@@ -6105,7 +6147,7 @@
     </row>
     <row r="87" spans="1:5" ht="39" customHeight="1">
       <c r="A87" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>45</v>
@@ -6114,7 +6156,7 @@
         <v>45</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>45</v>
@@ -6122,7 +6164,7 @@
     </row>
     <row r="88" spans="1:5" ht="39" customHeight="1">
       <c r="A88" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>45</v>
@@ -6131,7 +6173,7 @@
         <v>45</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>45</v>
@@ -6139,7 +6181,7 @@
     </row>
     <row r="89" spans="1:5" ht="39" customHeight="1">
       <c r="A89" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>45</v>
@@ -6148,7 +6190,7 @@
         <v>45</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>45</v>
@@ -6156,7 +6198,7 @@
     </row>
     <row r="90" spans="1:5" ht="39" customHeight="1">
       <c r="A90" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>45</v>
@@ -6165,7 +6207,7 @@
         <v>45</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>45</v>
@@ -6173,7 +6215,7 @@
     </row>
     <row r="91" spans="1:5" ht="39" customHeight="1">
       <c r="A91" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>45</v>
@@ -6182,7 +6224,7 @@
         <v>45</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>45</v>
@@ -6190,7 +6232,7 @@
     </row>
     <row r="92" spans="1:5" ht="39" customHeight="1">
       <c r="A92" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>45</v>
@@ -6199,7 +6241,7 @@
         <v>45</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>45</v>
@@ -6207,7 +6249,7 @@
     </row>
     <row r="93" spans="1:5" ht="39" customHeight="1">
       <c r="A93" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>45</v>
@@ -6216,7 +6258,7 @@
         <v>45</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>45</v>
@@ -6224,55 +6266,55 @@
     </row>
     <row r="94" spans="1:5" ht="39" customHeight="1">
       <c r="A94" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
+        <v>419</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="D94" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="E94" s="9"/>
+        <v>472</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="95" spans="1:5" ht="39" customHeight="1">
       <c r="A95" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="9" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E95" s="9"/>
     </row>
     <row r="96" spans="1:5" ht="39" customHeight="1">
       <c r="A96" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>45</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
       <c r="D96" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>45</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="E96" s="9"/>
     </row>
     <row r="97" spans="1:5" ht="39" customHeight="1">
       <c r="A97" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>476</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>45</v>
@@ -6280,7 +6322,7 @@
     </row>
     <row r="98" spans="1:5" ht="39" customHeight="1">
       <c r="A98" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>45</v>
@@ -6289,7 +6331,7 @@
         <v>45</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>45</v>
@@ -6297,7 +6339,7 @@
     </row>
     <row r="99" spans="1:5" ht="39" customHeight="1">
       <c r="A99" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>45</v>
@@ -6306,7 +6348,7 @@
         <v>45</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>45</v>
@@ -6314,7 +6356,7 @@
     </row>
     <row r="100" spans="1:5" ht="39" customHeight="1">
       <c r="A100" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>45</v>
@@ -6323,7 +6365,7 @@
         <v>45</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>45</v>
@@ -6331,7 +6373,7 @@
     </row>
     <row r="101" spans="1:5" ht="39" customHeight="1">
       <c r="A101" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>45</v>
@@ -6340,7 +6382,7 @@
         <v>45</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>45</v>
@@ -6348,7 +6390,7 @@
     </row>
     <row r="102" spans="1:5" ht="39" customHeight="1">
       <c r="A102" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>45</v>
@@ -6357,7 +6399,7 @@
         <v>45</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>45</v>
@@ -6365,7 +6407,7 @@
     </row>
     <row r="103" spans="1:5" ht="39" customHeight="1">
       <c r="A103" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>45</v>
@@ -6374,7 +6416,7 @@
         <v>45</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>547</v>
+        <v>480</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>45</v>
@@ -6382,7 +6424,7 @@
     </row>
     <row r="104" spans="1:5" ht="39" customHeight="1">
       <c r="A104" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>45</v>
@@ -6391,7 +6433,7 @@
         <v>45</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>482</v>
+        <v>546</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>45</v>
@@ -6399,7 +6441,7 @@
     </row>
     <row r="105" spans="1:5" ht="39" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>45</v>
@@ -6408,7 +6450,7 @@
         <v>45</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>45</v>
@@ -6416,7 +6458,7 @@
     </row>
     <row r="106" spans="1:5" ht="39" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>45</v>
@@ -6425,7 +6467,7 @@
         <v>45</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>45</v>
@@ -6433,7 +6475,7 @@
     </row>
     <row r="107" spans="1:5" ht="39" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>45</v>
@@ -6442,7 +6484,7 @@
         <v>45</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>548</v>
+        <v>483</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>45</v>
@@ -6450,7 +6492,7 @@
     </row>
     <row r="108" spans="1:5" ht="39" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>45</v>
@@ -6459,7 +6501,7 @@
         <v>45</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>45</v>
@@ -6467,7 +6509,7 @@
     </row>
     <row r="109" spans="1:5" ht="39" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>45</v>
@@ -6476,7 +6518,7 @@
         <v>45</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>485</v>
+        <v>548</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>45</v>
@@ -6484,7 +6526,7 @@
     </row>
     <row r="110" spans="1:5" ht="39" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>45</v>
@@ -6493,7 +6535,7 @@
         <v>45</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>45</v>
@@ -6501,7 +6543,7 @@
     </row>
     <row r="111" spans="1:5" ht="39" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>45</v>
@@ -6510,7 +6552,7 @@
         <v>45</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>45</v>
@@ -6518,7 +6560,7 @@
     </row>
     <row r="112" spans="1:5" ht="39" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>45</v>
@@ -6527,7 +6569,7 @@
         <v>45</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>45</v>
@@ -6535,7 +6577,7 @@
     </row>
     <row r="113" spans="1:5" ht="39" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>45</v>
@@ -6544,7 +6586,7 @@
         <v>45</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>550</v>
+        <v>487</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>45</v>
@@ -6552,7 +6594,7 @@
     </row>
     <row r="114" spans="1:5" ht="39" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>45</v>
@@ -6561,7 +6603,7 @@
         <v>45</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>489</v>
+        <v>549</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>45</v>
@@ -6569,7 +6611,7 @@
     </row>
     <row r="115" spans="1:5" ht="39" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>45</v>
@@ -6578,7 +6620,7 @@
         <v>45</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>45</v>
@@ -6586,7 +6628,7 @@
     </row>
     <row r="116" spans="1:5" ht="39" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>45</v>
@@ -6595,7 +6637,7 @@
         <v>45</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>45</v>
@@ -6603,7 +6645,7 @@
     </row>
     <row r="117" spans="1:5" ht="39" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>45</v>
@@ -6612,7 +6654,7 @@
         <v>45</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>45</v>
@@ -6620,16 +6662,16 @@
     </row>
     <row r="118" spans="1:5" ht="39" customHeight="1">
       <c r="A118" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D118" s="9" t="s">
         <v>492</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>494</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>45</v>
@@ -6637,7 +6679,7 @@
     </row>
     <row r="119" spans="1:5" ht="39" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>45</v>
@@ -6646,7 +6688,7 @@
         <v>45</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>45</v>
@@ -6654,7 +6696,7 @@
     </row>
     <row r="120" spans="1:5" ht="39" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>45</v>
@@ -6663,7 +6705,7 @@
         <v>45</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>45</v>
@@ -6671,7 +6713,7 @@
     </row>
     <row r="121" spans="1:5" ht="39" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>45</v>
@@ -6680,7 +6722,7 @@
         <v>45</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>45</v>
@@ -6688,7 +6730,7 @@
     </row>
     <row r="122" spans="1:5" ht="39" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>45</v>
@@ -6697,7 +6739,7 @@
         <v>45</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>45</v>
@@ -6705,7 +6747,7 @@
     </row>
     <row r="123" spans="1:5" ht="39" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>45</v>
@@ -6714,7 +6756,7 @@
         <v>45</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>45</v>
@@ -6722,7 +6764,7 @@
     </row>
     <row r="124" spans="1:5" ht="39" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>45</v>
@@ -6731,7 +6773,7 @@
         <v>45</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>45</v>
@@ -6739,7 +6781,7 @@
     </row>
     <row r="125" spans="1:5" ht="39" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>45</v>
@@ -6748,7 +6790,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>45</v>
@@ -6756,7 +6798,7 @@
     </row>
     <row r="126" spans="1:5" ht="39" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>45</v>
@@ -6765,9 +6807,26 @@
         <v>45</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E126" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="39" customHeight="1">
+      <c r="A127" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="E127" s="9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6796,10 +6855,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -6807,62 +6866,62 @@
     </row>
     <row r="2" spans="1:4" ht="27.6">
       <c r="A2" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.6">
       <c r="A3" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>511</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="41.4">
       <c r="A4" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>516</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>517</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
@@ -6871,10 +6930,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
@@ -6883,10 +6942,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
@@ -6895,40 +6954,40 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>521</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>522</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
@@ -6937,10 +6996,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
@@ -6949,10 +7008,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
@@ -6961,40 +7020,40 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
@@ -7003,10 +7062,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
@@ -7015,10 +7074,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5" t="s">
@@ -7027,10 +7086,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5" t="s">
@@ -7039,10 +7098,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5" t="s">
@@ -7051,10 +7110,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5" t="s">
@@ -7063,10 +7122,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5" t="s">
@@ -7075,10 +7134,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
@@ -7087,10 +7146,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5" t="s">
@@ -7099,10 +7158,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
@@ -7111,10 +7170,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5" t="s">
@@ -7123,10 +7182,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5" t="s">
@@ -7135,10 +7194,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5" t="s">
@@ -7147,10 +7206,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5" t="s">
@@ -7159,10 +7218,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5" t="s">
@@ -7171,10 +7230,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">

--- a/homepage_content.xlsx
+++ b/homepage_content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768CAE57-234B-4FE0-9BE5-E0F7CD68802C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C14884-2BCB-4B58-906D-FAA3317164E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1743,15 +1743,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>206-08-25</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Congratulations to Zhuolin Li on successfully completing her Ph.D. thesis defense.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>A new research project was granted by the National Natural Science Foundation of China (NSFC). Congratulations to Zhuolin Li.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>206-08-26</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="2" spans="1:5" ht="54.45" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>129</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E2" s="16" t="str">
         <f>IF(ROW()-1&lt;11,"yes","no")</f>
@@ -2877,7 +2877,7 @@
         <v>53</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>54</v>
